--- a/data/CS7/case33_3/case33_3_operational_data.xlsx
+++ b/data/CS7/case33_3/case33_3_operational_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\case33_3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04110F1A-D0A2-448C-BBEF-DB9E1689EC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FB17DC8-D35C-4708-927A-1447AF066603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33435" yWindow="-11490" windowWidth="28800" windowHeight="15285" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-12510" yWindow="-15930" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="23">
   <si>
     <t>Pc</t>
   </si>
@@ -109,6 +109,12 @@
   <si>
     <t>Type</t>
   </si>
+  <si>
+    <t>Pc_</t>
+  </si>
+  <si>
+    <t>Qc_</t>
+  </si>
 </sst>
 </file>
 
@@ -123,12 +129,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -143,10 +155,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -427,14 +441,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59B7BE64-82AA-46B6-895E-9570C0781B75}">
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -447,460 +461,722 @@
       <c r="D1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>4.7</v>
+        <f>E2*0.75</f>
+        <v>3.5250000000000004</v>
       </c>
       <c r="C2" s="1">
-        <v>0.72</v>
+        <f>F2*2.5</f>
+        <v>1.7999999999999998</v>
       </c>
       <c r="D2" s="2">
         <v>2.6917900403768499E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>4.7699999999999996</v>
+        <f t="shared" ref="B3:B33" si="0">E3*0.75</f>
+        <v>3.5774999999999997</v>
       </c>
       <c r="C3" s="1">
-        <v>-0.88</v>
+        <f t="shared" ref="C3:C33" si="1">F3*2.5</f>
+        <v>-2.2000000000000002</v>
       </c>
       <c r="D3" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3" s="4">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="F3" s="4">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>3.48</v>
+        <f t="shared" si="0"/>
+        <v>2.61</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.72</v>
+        <f t="shared" si="1"/>
+        <v>-1.7999999999999998</v>
       </c>
       <c r="D4" s="2">
         <v>3.2301480484522194E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" s="4">
+        <v>3.48</v>
+      </c>
+      <c r="F4" s="4">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>1.26</v>
+        <f t="shared" si="0"/>
+        <v>0.94500000000000006</v>
       </c>
       <c r="C5" s="1">
-        <v>0.48</v>
+        <f t="shared" si="1"/>
+        <v>1.2</v>
       </c>
       <c r="D5" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E5" s="4">
+        <v>1.26</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>2.94</v>
+        <f t="shared" si="0"/>
+        <v>2.2050000000000001</v>
       </c>
       <c r="C6" s="1">
-        <v>0.02</v>
+        <f t="shared" si="1"/>
+        <v>0.05</v>
       </c>
       <c r="D6" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6" s="4">
+        <v>2.94</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>5.2</v>
+        <f t="shared" si="0"/>
+        <v>3.9000000000000004</v>
       </c>
       <c r="C7" s="1">
-        <v>-1.1000000000000001</v>
+        <f t="shared" si="1"/>
+        <v>-2.75</v>
       </c>
       <c r="D7" s="2">
         <v>5.3835800807536999E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E7" s="4">
+        <v>5.2</v>
+      </c>
+      <c r="F7" s="4">
+        <v>-1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="C8" s="1">
-        <v>2.1</v>
+        <f t="shared" si="1"/>
+        <v>5.25</v>
       </c>
       <c r="D8" s="2">
         <v>5.3835800807536999E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8" s="4">
+        <v>4</v>
+      </c>
+      <c r="F8" s="4">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <v>1.44</v>
+        <f t="shared" si="0"/>
+        <v>1.08</v>
       </c>
       <c r="C9" s="1">
-        <v>0.48</v>
+        <f t="shared" si="1"/>
+        <v>1.2</v>
       </c>
       <c r="D9" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E9" s="4">
+        <v>1.44</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <v>1.56</v>
+        <f t="shared" si="0"/>
+        <v>1.17</v>
       </c>
       <c r="C10" s="1">
-        <v>-0.26</v>
+        <f t="shared" si="1"/>
+        <v>-0.65</v>
       </c>
       <c r="D10" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E10" s="4">
+        <v>1.56</v>
+      </c>
+      <c r="F10" s="4">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <v>1.0349999999999999</v>
+        <f t="shared" si="0"/>
+        <v>0.77624999999999988</v>
       </c>
       <c r="C11" s="1">
-        <v>-0.3</v>
+        <f t="shared" si="1"/>
+        <v>-0.75</v>
       </c>
       <c r="D11" s="2">
         <v>1.2113055181695823E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E11" s="4">
+        <v>1.0349999999999999</v>
+      </c>
+      <c r="F11" s="4">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" s="1">
-        <v>2.1</v>
+        <f t="shared" si="0"/>
+        <v>1.5750000000000002</v>
       </c>
       <c r="C12" s="1">
-        <v>1.155</v>
+        <f t="shared" si="1"/>
+        <v>2.8875000000000002</v>
       </c>
       <c r="D12" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E12" s="4">
+        <v>2.1</v>
+      </c>
+      <c r="F12" s="4">
+        <v>1.155</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" s="1">
-        <v>3.1799999999999997</v>
+        <f t="shared" si="0"/>
+        <v>2.3849999999999998</v>
       </c>
       <c r="C13" s="1">
-        <v>-0.87500000000000011</v>
+        <f t="shared" si="1"/>
+        <v>-2.1875000000000004</v>
       </c>
       <c r="D13" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E13" s="4">
+        <v>3.1799999999999997</v>
+      </c>
+      <c r="F13" s="4">
+        <v>-0.87500000000000011</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>2.6999999999999997</v>
       </c>
       <c r="C14" s="1">
-        <v>3.2</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="D14" s="2">
         <v>3.2301480484522194E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E14" s="4">
+        <v>3.5999999999999996</v>
+      </c>
+      <c r="F14" s="4">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C15" s="1">
-        <v>0.37</v>
+        <f t="shared" si="1"/>
+        <v>0.92500000000000004</v>
       </c>
       <c r="D15" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E15" s="4">
+        <v>2.4</v>
+      </c>
+      <c r="F15" s="4">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>2.2799999999999998</v>
+        <f t="shared" si="0"/>
+        <v>1.71</v>
       </c>
       <c r="C16" s="1">
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="D16" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E16" s="4">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" s="1">
-        <v>1.74</v>
+        <f t="shared" si="0"/>
+        <v>1.3049999999999999</v>
       </c>
       <c r="C17" s="1">
-        <v>0.18</v>
+        <f t="shared" si="1"/>
+        <v>0.44999999999999996</v>
       </c>
       <c r="D17" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E17" s="4">
+        <v>1.74</v>
+      </c>
+      <c r="F17" s="4">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" s="1">
-        <v>3.15</v>
+        <f t="shared" si="0"/>
+        <v>2.3624999999999998</v>
       </c>
       <c r="C18" s="1">
-        <v>-0.76</v>
+        <f t="shared" si="1"/>
+        <v>-1.9</v>
       </c>
       <c r="D18" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E18" s="4">
+        <v>3.15</v>
+      </c>
+      <c r="F18" s="4">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" s="1">
-        <v>4.2299999999999995</v>
+        <f t="shared" si="0"/>
+        <v>3.1724999999999994</v>
       </c>
       <c r="C19" s="1">
-        <v>-0.56000000000000005</v>
+        <f t="shared" si="1"/>
+        <v>-1.4000000000000001</v>
       </c>
       <c r="D19" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E19" s="4">
+        <v>4.2299999999999995</v>
+      </c>
+      <c r="F19" s="4">
+        <v>-0.56000000000000005</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" s="1">
-        <v>3.8699999999999997</v>
+        <f t="shared" si="0"/>
+        <v>2.9024999999999999</v>
       </c>
       <c r="C20" s="1">
-        <v>-1.24</v>
+        <f t="shared" si="1"/>
+        <v>-3.1</v>
       </c>
       <c r="D20" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E20" s="4">
+        <v>3.8699999999999997</v>
+      </c>
+      <c r="F20" s="4">
+        <v>-1.24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" s="1">
-        <v>4.05</v>
+        <f t="shared" si="0"/>
+        <v>3.0374999999999996</v>
       </c>
       <c r="C21" s="1">
-        <v>-1.32</v>
+        <f t="shared" si="1"/>
+        <v>-3.3000000000000003</v>
       </c>
       <c r="D21" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E21" s="4">
+        <v>4.05</v>
+      </c>
+      <c r="F21" s="4">
+        <v>-1.32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" s="1">
-        <v>5.22</v>
+        <f t="shared" si="0"/>
+        <v>3.915</v>
       </c>
       <c r="C22" s="1">
-        <v>0.4</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="D22" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E22" s="4">
+        <v>5.22</v>
+      </c>
+      <c r="F22" s="4">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" s="1">
-        <v>2.9699999999999998</v>
+        <f t="shared" si="0"/>
+        <v>2.2275</v>
       </c>
       <c r="C23" s="1">
-        <v>1.9000000000000001</v>
+        <f t="shared" si="1"/>
+        <v>4.75</v>
       </c>
       <c r="D23" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E23" s="4">
+        <v>2.9699999999999998</v>
+      </c>
+      <c r="F23" s="4">
+        <v>1.9000000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" s="1">
-        <v>23.52</v>
+        <f t="shared" si="0"/>
+        <v>17.64</v>
       </c>
       <c r="C24" s="1">
-        <v>7.8000000000000007</v>
+        <f t="shared" si="1"/>
+        <v>19.5</v>
       </c>
       <c r="D24" s="2">
         <v>0.11305518169582769</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E24" s="4">
+        <v>23.52</v>
+      </c>
+      <c r="F24" s="4">
+        <v>7.8000000000000007</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" s="1">
-        <v>13.02</v>
+        <f t="shared" si="0"/>
+        <v>9.7650000000000006</v>
       </c>
       <c r="C25" s="1">
-        <v>-3.4000000000000004</v>
+        <f t="shared" si="1"/>
+        <v>-8.5</v>
       </c>
       <c r="D25" s="2">
         <v>0.11305518169582769</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E25" s="4">
+        <v>13.02</v>
+      </c>
+      <c r="F25" s="4">
+        <v>-3.4000000000000004</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" s="1">
-        <v>2.58</v>
+        <f t="shared" si="0"/>
+        <v>1.9350000000000001</v>
       </c>
       <c r="C26" s="1">
-        <v>0.52500000000000002</v>
+        <f t="shared" si="1"/>
+        <v>1.3125</v>
       </c>
       <c r="D26" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E26" s="4">
+        <v>2.58</v>
+      </c>
+      <c r="F26" s="4">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" s="1">
-        <v>1.44</v>
+        <f t="shared" si="0"/>
+        <v>1.08</v>
       </c>
       <c r="C27" s="1">
-        <v>0.27500000000000002</v>
+        <f t="shared" si="1"/>
+        <v>0.6875</v>
       </c>
       <c r="D27" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E27" s="4">
+        <v>1.44</v>
+      </c>
+      <c r="F27" s="4">
+        <v>0.27500000000000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" s="1">
-        <v>3.54</v>
+        <f t="shared" si="0"/>
+        <v>2.6550000000000002</v>
       </c>
       <c r="C28" s="1">
-        <v>0.18</v>
+        <f t="shared" si="1"/>
+        <v>0.44999999999999996</v>
       </c>
       <c r="D28" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E28" s="4">
+        <v>3.54</v>
+      </c>
+      <c r="F28" s="4">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" s="1">
-        <v>5.2799999999999994</v>
+        <f t="shared" si="0"/>
+        <v>3.9599999999999995</v>
       </c>
       <c r="C29" s="1">
-        <v>-0.84000000000000008</v>
+        <f t="shared" si="1"/>
+        <v>-2.1</v>
       </c>
       <c r="D29" s="2">
         <v>3.2301480484522194E-2</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E29" s="4">
+        <v>5.2799999999999994</v>
+      </c>
+      <c r="F29" s="4">
+        <v>-0.84000000000000008</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" s="1">
-        <v>5.6000000000000005</v>
+        <f t="shared" si="0"/>
+        <v>4.2</v>
       </c>
       <c r="C30" s="1">
-        <v>10.799999999999999</v>
+        <f t="shared" si="1"/>
+        <v>26.999999999999996</v>
       </c>
       <c r="D30" s="2">
         <v>5.3835800807536999E-2</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E30" s="4">
+        <v>5.6000000000000005</v>
+      </c>
+      <c r="F30" s="4">
+        <v>10.799999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" s="1">
-        <v>3.4499999999999997</v>
+        <f t="shared" si="0"/>
+        <v>2.5874999999999999</v>
       </c>
       <c r="C31" s="1">
-        <v>-1.9600000000000002</v>
+        <f t="shared" si="1"/>
+        <v>-4.9000000000000004</v>
       </c>
       <c r="D31" s="2">
         <v>4.0376850605652742E-2</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E31" s="4">
+        <v>3.4499999999999997</v>
+      </c>
+      <c r="F31" s="4">
+        <v>-1.9600000000000002</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" s="1">
-        <v>11.969999999999999</v>
+        <f t="shared" si="0"/>
+        <v>8.9774999999999991</v>
       </c>
       <c r="C32" s="1">
-        <v>-3.3000000000000003</v>
+        <f t="shared" si="1"/>
+        <v>-8.25</v>
       </c>
       <c r="D32" s="2">
         <v>5.6527590847913846E-2</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E32" s="4">
+        <v>11.969999999999999</v>
+      </c>
+      <c r="F32" s="4">
+        <v>-3.3000000000000003</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" s="1">
-        <v>1.8599999999999999</v>
+        <f t="shared" si="0"/>
+        <v>1.395</v>
       </c>
       <c r="C33" s="1">
-        <v>1.1599999999999999</v>
+        <f t="shared" si="1"/>
+        <v>2.9</v>
       </c>
       <c r="D33" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E33" s="4">
+        <v>1.8599999999999999</v>
+      </c>
+      <c r="F33" s="4">
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
     </row>
@@ -69909,95 +70185,95 @@
       </c>
       <c r="E11" s="1">
         <f t="shared" ref="E11:AA19" ca="1" si="0">E2*0.95*RANDBETWEEN(95,105)/100</f>
-        <v>4.6815886000000004</v>
+        <v>4.9711714000000002</v>
       </c>
       <c r="F11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.4513921999999999</v>
+        <v>4.4081748000000003</v>
       </c>
       <c r="G11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.0144719999999987</v>
+        <v>4.1373639999999989</v>
       </c>
       <c r="H11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3.3897216000000001</v>
+        <v>3.2890367999999999</v>
       </c>
       <c r="I11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2.7345408000000004</v>
+        <v>2.7060560000000002</v>
       </c>
       <c r="J11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3.5182945999999999</v>
+        <v>3.6576330000000001</v>
       </c>
       <c r="K11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.61100960000000004</v>
+        <v>0.62915840000000001</v>
       </c>
       <c r="L11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.52136000000000005</v>
+        <v>0.52668000000000004</v>
       </c>
       <c r="M11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.77557999999999983</v>
+        <v>0.80660319999999985</v>
       </c>
       <c r="N11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.43848960000000003</v>
+        <v>0.4430572000000001</v>
       </c>
       <c r="O11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.5650523999999999</v>
+        <v>0.59359039999999996</v>
       </c>
       <c r="P11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.88205980000000028</v>
+        <v>0.94571360000000027</v>
       </c>
       <c r="Q11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.6419116000000002</v>
+        <v>1.6921742</v>
       </c>
       <c r="R11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.7517695999999998</v>
+        <v>1.7338943999999998</v>
       </c>
       <c r="S11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.8106163999999996</v>
+        <v>1.7754587999999996</v>
       </c>
       <c r="T11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.95651699999999995</v>
+        <v>0.98609999999999998</v>
       </c>
       <c r="U11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2.0890271999999994</v>
+        <v>2.0488535999999997</v>
       </c>
       <c r="V11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.2259104000000001</v>
+        <v>1.1316096</v>
       </c>
       <c r="W11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.83706779999999981</v>
+        <v>0.85364339999999983</v>
       </c>
       <c r="X11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.3089024</v>
+        <v>1.3214880000000002</v>
       </c>
       <c r="Y11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.77786</v>
+        <v>0.80897439999999998</v>
       </c>
       <c r="Z11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3.5503400000000003</v>
+        <v>3.3728230000000003</v>
       </c>
       <c r="AA11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.4083382000000002</v>
+        <v>4.3227393999999997</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
@@ -70012,31 +70288,31 @@
       </c>
       <c r="D12" s="1">
         <f t="shared" ref="D12:S19" ca="1" si="1">D3*0.95*RANDBETWEEN(95,105)/100</f>
-        <v>-10.123200000000002</v>
+        <v>-10.017750000000001</v>
       </c>
       <c r="E12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-11.163358799999999</v>
+        <v>-11.614403599999997</v>
       </c>
       <c r="F12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-12.174835200000002</v>
+        <v>-13.316226000000002</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-13.8171838</v>
+        <v>-14.090791400000001</v>
       </c>
       <c r="H12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-14.037504000000002</v>
+        <v>-14.183728</v>
       </c>
       <c r="I12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-16.277262</v>
+        <v>-16.436843</v>
       </c>
       <c r="J12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-14.465631</v>
+        <v>-15.3792498</v>
       </c>
       <c r="K12" s="1">
         <f t="shared" ca="1" si="1"/>
@@ -70044,15 +70320,15 @@
       </c>
       <c r="L12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-15.491991999999993</v>
+        <v>-15.646911919999996</v>
       </c>
       <c r="M12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-21.617438099999994</v>
+        <v>-21.844990079999999</v>
       </c>
       <c r="N12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-21.621112320000002</v>
+        <v>-23.197651760000003</v>
       </c>
       <c r="O12" s="1">
         <f t="shared" ca="1" si="1"/>
@@ -70060,35 +70336,35 @@
       </c>
       <c r="P12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-19.933190319999998</v>
+        <v>-18.749040399999998</v>
       </c>
       <c r="Q12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-19.81679024</v>
+        <v>-19.62624418</v>
       </c>
       <c r="R12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-18.319603920000006</v>
+        <v>-18.499207880000004</v>
       </c>
       <c r="S12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-15.853707159999999</v>
+        <v>-16.834348839999997</v>
       </c>
       <c r="T12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-14.824133639999999</v>
+        <v>-15.89391648</v>
       </c>
       <c r="U12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-13.402899440000001</v>
+        <v>-13.813192280000001</v>
       </c>
       <c r="V12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-8.3336006400000002</v>
+        <v>-8.6808339999999991</v>
       </c>
       <c r="W12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-10.103762239999998</v>
+        <v>-9.6180044399999982</v>
       </c>
       <c r="X12" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70096,7 +70372,7 @@
       </c>
       <c r="Y12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-11.466135199999998</v>
+        <v>-10.4738735</v>
       </c>
       <c r="Z12" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70104,7 +70380,7 @@
       </c>
       <c r="AA12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-9.1215656000000003</v>
+        <v>-9.586951599999999</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
@@ -70119,19 +70395,19 @@
       </c>
       <c r="D13" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>9.9557043599999986</v>
+        <v>9.7525267199999988</v>
       </c>
       <c r="E13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10.868303999999997</v>
+        <v>10.976987039999997</v>
       </c>
       <c r="F13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>11.942160439999999</v>
+        <v>12.307736779999997</v>
       </c>
       <c r="G13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12.850071640000001</v>
+        <v>13.374564360000001</v>
       </c>
       <c r="H13" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70139,79 +70415,79 @@
       </c>
       <c r="I13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16.001895000000001</v>
+        <v>15.697097000000001</v>
       </c>
       <c r="J13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.384006999999997</v>
+        <v>14.093420999999999</v>
       </c>
       <c r="K13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.740353919999997</v>
+        <v>16.06827796</v>
       </c>
       <c r="L13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.41795392</v>
+        <v>15.769637100000002</v>
       </c>
       <c r="M13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>17.480217359999997</v>
+        <v>16.966093319999999</v>
       </c>
       <c r="N13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16.92695788</v>
+        <v>18.136026300000001</v>
       </c>
       <c r="O13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.360225099999997</v>
+        <v>15.521911679999999</v>
       </c>
       <c r="P13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16.092411000000002</v>
+        <v>15.779937000000002</v>
       </c>
       <c r="Q13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.831000639999999</v>
+        <v>15.983221799999999</v>
       </c>
       <c r="R13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.836124160000004</v>
+        <v>14.693469120000005</v>
       </c>
       <c r="S13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12.728147880000002</v>
+        <v>12.858026940000002</v>
       </c>
       <c r="T13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12.099237999999996</v>
+        <v>11.978245619999996</v>
       </c>
       <c r="U13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>11.3544228</v>
+        <v>11.03001072</v>
       </c>
       <c r="V13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8.2099752400000003</v>
+        <v>8.8024476799999984</v>
       </c>
       <c r="W13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9.1893454400000003</v>
+        <v>9.3788164799999993</v>
       </c>
       <c r="X13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9.9660646800000023</v>
+        <v>10.570068600000003</v>
       </c>
       <c r="Y13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10.518517040000001</v>
+        <v>10.626955360000002</v>
       </c>
       <c r="Z13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8.6910369999999997</v>
+        <v>8.1003839999999983</v>
       </c>
       <c r="AA13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9.1520112000000022</v>
+        <v>9.0622856000000009</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
@@ -70226,79 +70502,79 @@
       </c>
       <c r="D14" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>4.8060268200000005</v>
+        <v>5.0512322700000007</v>
       </c>
       <c r="E14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.8220362579999998</v>
+        <v>4.7226128300000001</v>
       </c>
       <c r="F14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.1903591039999997</v>
+        <v>4.0658929919999993</v>
       </c>
       <c r="G14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.430666239999999</v>
+        <v>4.3028585599999989</v>
       </c>
       <c r="H14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3.5592076800000001</v>
+        <v>3.3219271680000002</v>
       </c>
       <c r="I14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2.9920433919999998</v>
+        <v>2.8481951520000002</v>
       </c>
       <c r="J14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3.6241917840000002</v>
+        <v>3.3754727400000002</v>
       </c>
       <c r="K14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.59267931200000001</v>
+        <v>0.60441553599999998</v>
       </c>
       <c r="L14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.53152120000000014</v>
+        <v>0.53700080000000017</v>
       </c>
       <c r="M14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.80683587399999979</v>
+        <v>0.77550244199999985</v>
       </c>
       <c r="N14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.48457668400000004</v>
+        <v>0.47987205600000005</v>
       </c>
       <c r="O14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.59376162799999999</v>
+        <v>0.54764422000000001</v>
       </c>
       <c r="P14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.98345121000000024</v>
+        <v>0.90852159400000021</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.7240071800000001</v>
+        <v>1.7767829100000003</v>
       </c>
       <c r="R14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.7859112319999999</v>
+        <v>1.9147914239999999</v>
       </c>
       <c r="S14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.7403011999999995</v>
+        <v>1.8457739999999996</v>
       </c>
       <c r="T14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.95651699999999995</v>
+        <v>1.0156829999999999</v>
       </c>
       <c r="U14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2.1091139999999995</v>
+        <v>1.9283327999999995</v>
       </c>
       <c r="V14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.2872059200000001</v>
+        <v>1.2624519600000002</v>
       </c>
       <c r="W14" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70306,15 +70582,15 @@
       </c>
       <c r="X14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.3481694720000001</v>
+        <v>1.2434572800000003</v>
       </c>
       <c r="Y14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.78548302800000003</v>
+        <v>0.81721971599999998</v>
       </c>
       <c r="Z14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3.7651355700000004</v>
+        <v>3.5414641500000004</v>
       </c>
       <c r="AA14" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70333,19 +70609,19 @@
       </c>
       <c r="D15" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-10.224432</v>
+        <v>-10.123200000000001</v>
       </c>
       <c r="E15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-11.731675247999998</v>
+        <v>-11.041576703999999</v>
       </c>
       <c r="F15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-13.454461108000002</v>
+        <v>-13.323835272000004</v>
       </c>
       <c r="G15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-13.8171838</v>
+        <v>-13.402668286000001</v>
       </c>
       <c r="H15" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70353,15 +70629,15 @@
       </c>
       <c r="I15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-17.258685150000002</v>
+        <v>-17.426245200000004</v>
       </c>
       <c r="J15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-14.031662069999999</v>
+        <v>-15.18891255</v>
       </c>
       <c r="K15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-17.424095517199998</v>
+        <v>-17.941642908799999</v>
       </c>
       <c r="L15" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70369,7 +70645,7 @@
       </c>
       <c r="M15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-24.140989558199994</v>
+        <v>-24.375368097599996</v>
       </c>
       <c r="N15" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70381,35 +70657,35 @@
       </c>
       <c r="P15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-19.7338584168</v>
+        <v>-20.531186029599997</v>
       </c>
       <c r="Q15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-19.046984157600001</v>
+        <v>-18.658270195200004</v>
       </c>
       <c r="R15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-18.314215801200003</v>
+        <v>-17.574247486000004</v>
       </c>
       <c r="S15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-15.526826599999998</v>
+        <v>-14.750485269999997</v>
       </c>
       <c r="T15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-15.2581598208</v>
+        <v>-13.937742144</v>
       </c>
       <c r="U15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-13.536928434400002</v>
+        <v>-13.675060357200003</v>
       </c>
       <c r="V15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-8.9377866863999991</v>
+        <v>-8.5080854034000009</v>
       </c>
       <c r="W15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-9.2352272935999977</v>
+        <v>-9.4256443511999972</v>
       </c>
       <c r="X15" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70417,15 +70693,15 @@
       </c>
       <c r="Y15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-10.908263622</v>
+        <v>-11.470545251999999</v>
       </c>
       <c r="Z15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-9.383047856000001</v>
+        <v>-9.1097552000000004</v>
       </c>
       <c r="AA15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-9.5888131439999995</v>
+        <v>-9.4007971999999995</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
@@ -70440,39 +70716,39 @@
       </c>
       <c r="D16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>10.882194398399998</v>
+        <v>10.672921429199999</v>
       </c>
       <c r="E16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>11.194353119999995</v>
+        <v>11.642127244799997</v>
       </c>
       <c r="F16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12.429595559999997</v>
+        <v>11.698442879999998</v>
       </c>
       <c r="G16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12.336068774400001</v>
+        <v>12.965460038400002</v>
       </c>
       <c r="H16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.378326265999997</v>
+        <v>13.666527935999998</v>
       </c>
       <c r="I16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.841876050000002</v>
+        <v>14.78575098</v>
       </c>
       <c r="J16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>13.388749949999999</v>
+        <v>14.354948399999998</v>
       </c>
       <c r="K16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16.212564537600002</v>
+        <v>15.740353920000002</v>
       </c>
       <c r="L16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.3145704294</v>
+        <v>15.7786483212</v>
       </c>
       <c r="M16" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70480,59 +70756,59 @@
       </c>
       <c r="N16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>17.968483961800001</v>
+        <v>17.434766616400001</v>
       </c>
       <c r="O16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16.807319991</v>
+        <v>15.846901705799999</v>
       </c>
       <c r="P16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16.092411000000002</v>
+        <v>15.467463</v>
       </c>
       <c r="Q16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.171789995999999</v>
+        <v>13.882569792</v>
       </c>
       <c r="R16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.539401676800003</v>
+        <v>15.429569126400002</v>
       </c>
       <c r="S16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12.461895807000001</v>
+        <v>12.986607209400001</v>
       </c>
       <c r="T16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12.205711294399997</v>
+        <v>12.834871670399997</v>
       </c>
       <c r="U16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>11.249529560799999</v>
+        <v>10.581240676</v>
       </c>
       <c r="V16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8.456274497199999</v>
+        <v>7.9636759827999981</v>
       </c>
       <c r="W16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9.8553361456000008</v>
+        <v>9.5682875200000002</v>
       </c>
       <c r="X16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9.6640627200000022</v>
+        <v>10.268066640000002</v>
       </c>
       <c r="Y16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10.816722420000001</v>
+        <v>9.7865583800000007</v>
       </c>
       <c r="Z16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8.8631701599999992</v>
+        <v>8.9509243200000004</v>
       </c>
       <c r="AA16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8.4386926800000008</v>
+        <v>8.7940060560000024</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.3">
@@ -70547,99 +70823,99 @@
       </c>
       <c r="D17" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>4.6123145145000022</v>
+        <v>4.5191364435000017</v>
       </c>
       <c r="E17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.9214596860000004</v>
+        <v>5.2197299700000004</v>
       </c>
       <c r="F17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.2318478079999995</v>
+        <v>4.1048923737599994</v>
       </c>
       <c r="G17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.6078928895999987</v>
+        <v>4.4749729023999985</v>
       </c>
       <c r="H17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3.2846402304000004</v>
+        <v>3.3537905510400003</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2.6511230632</v>
+        <v>2.8464689731199995</v>
       </c>
       <c r="J17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3.6188620902000004</v>
+        <v>3.8054013732000005</v>
       </c>
       <c r="K17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.61615175999999994</v>
+        <v>0.59150568959999994</v>
       </c>
       <c r="L17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.52056200000000008</v>
+        <v>0.53617886000000003</v>
       </c>
       <c r="M17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.74448234431999982</v>
+        <v>0.78325746641999971</v>
       </c>
       <c r="N17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.48942245084000002</v>
+        <v>0.46566407943999999</v>
       </c>
       <c r="O17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.6234497094</v>
+        <v>0.60563686055999999</v>
       </c>
       <c r="P17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.9351216076800003</v>
+        <v>0.99356670816000037</v>
       </c>
       <c r="Q17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.6545191355</v>
+        <v>1.7764310718000003</v>
       </c>
       <c r="R17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.9911989663999998</v>
+        <v>1.8945388223999999</v>
       </c>
       <c r="S17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.6532861399999998</v>
+        <v>1.8099132479999998</v>
       </c>
       <c r="T17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.94616294999999995</v>
+        <v>0.96489884999999986</v>
       </c>
       <c r="U17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.9283327999999995</v>
+        <v>2.0488535999999997</v>
       </c>
       <c r="V17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.2605954130000003</v>
+        <v>1.2475995840000003</v>
       </c>
       <c r="W17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.88744436351999967</v>
+        <v>0.8789112446399997</v>
       </c>
       <c r="X17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.3476459110400001</v>
+        <v>1.2828552422399999</v>
       </c>
       <c r="Y17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.72359648640000007</v>
+        <v>0.79976453759999999</v>
       </c>
       <c r="Z17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.0320501312000001</v>
+        <v>3.6831227159999997</v>
       </c>
       <c r="AA17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.3573213151999992</v>
+        <v>4.4934876062999995</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.3">
@@ -70654,51 +70930,51 @@
       </c>
       <c r="D18" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-9.232358399999999</v>
+        <v>-10.0017216</v>
       </c>
       <c r="E18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-11.271609551999999</v>
+        <v>-10.708029074399999</v>
       </c>
       <c r="F18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-12.924120213840002</v>
+        <v>-12.417291970160001</v>
       </c>
       <c r="G18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-12.999206519040003</v>
+        <v>-13.662431341440003</v>
       </c>
       <c r="H18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-14.886772991999999</v>
+        <v>-15.817196303999999</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-17.593805250000003</v>
+        <v>-16.923565050000001</v>
       </c>
       <c r="J18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-14.601607931399998</v>
+        <v>-14.4598447476</v>
       </c>
       <c r="K18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-16.399351681831998</v>
+        <v>-17.236053298251999</v>
       </c>
       <c r="L18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-14.705742422015994</v>
+        <v>-14.858927238911996</v>
       </c>
       <c r="M18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-24.855844103369996</v>
+        <v>-23.435510154605996</v>
       </c>
       <c r="N18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-20.745457271040003</v>
+        <v>-22.690343890200005</v>
       </c>
       <c r="O18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-18.776759424000002</v>
+        <v>-18.213456641280001</v>
       </c>
       <c r="P18" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70710,39 +70986,39 @@
       </c>
       <c r="R18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-18.277217385440004</v>
+        <v>-18.452959860300005</v>
       </c>
       <c r="S18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-15.520615869359997</v>
+        <v>-16.154110394639996</v>
       </c>
       <c r="T18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-14.800415026175997</v>
+        <v>-16.021067811839998</v>
       </c>
       <c r="U18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-13.800760406948003</v>
+        <v>-13.943036287432001</v>
       </c>
       <c r="V18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-8.5080854034000009</v>
+        <v>-8.9377866863999991</v>
       </c>
       <c r="W18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-9.225706440719998</v>
+        <v>-8.9543621336399983</v>
       </c>
       <c r="X18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-10.778502273839999</v>
+        <v>-11.328425859239999</v>
       </c>
       <c r="Y18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-11.217518518499997</v>
+        <v>-10.469683950599997</v>
       </c>
       <c r="Z18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-8.8328186419200012</v>
+        <v>-9.0951795916800009</v>
       </c>
       <c r="AA18" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70761,35 +71037,35 @@
       </c>
       <c r="D19" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>10.454231176385997</v>
+        <v>10.657225956509997</v>
       </c>
       <c r="E19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10.531647415295998</v>
+        <v>11.080170718175998</v>
       </c>
       <c r="F19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>11.938504676599997</v>
+        <v>12.174910709799999</v>
       </c>
       <c r="G19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12.960424908288001</v>
+        <v>12.436771376639999</v>
       </c>
       <c r="H19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.798287280699997</v>
+        <v>14.499331982099996</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.194320940799999</v>
+        <v>15.081465999600001</v>
       </c>
       <c r="J19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.354948400000001</v>
+        <v>14.785596851999999</v>
       </c>
       <c r="K19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16.369968076800003</v>
+        <v>15.715169353728001</v>
       </c>
       <c r="L19" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70797,51 +71073,51 @@
       </c>
       <c r="M19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>19.649820808799998</v>
+        <v>18.705117885299998</v>
       </c>
       <c r="N19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>18.317179294128003</v>
+        <v>19.242289359488005</v>
       </c>
       <c r="O19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16.975393190909998</v>
+        <v>16.490381956883997</v>
       </c>
       <c r="P19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.937736369999998</v>
+        <v>15.779936999999997</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.043788911059998</v>
+        <v>14.44799529082</v>
       </c>
       <c r="R19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.684795693568002</v>
+        <v>14.834640547584002</v>
       </c>
       <c r="S19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>13.646431797918002</v>
+        <v>12.983983652388002</v>
       </c>
       <c r="T19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12.571882633231997</v>
+        <v>11.717482842623998</v>
       </c>
       <c r="U19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>11.588129262431998</v>
+        <v>11.247301931183999</v>
       </c>
       <c r="V19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8.5416582396959999</v>
+        <v>8.6253999871440001</v>
       </c>
       <c r="W19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8.9080756811199997</v>
+        <v>9.1893833342079994</v>
       </c>
       <c r="X19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10.576108639200005</v>
+        <v>9.9539846016000038</v>
       </c>
       <c r="Y19" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70849,11 +71125,11 @@
       </c>
       <c r="Z19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8.4279095264000006</v>
+        <v>8.7719058336000018</v>
       </c>
       <c r="AA19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8.9698861771200011</v>
+        <v>9.42291073152</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.3">
@@ -70868,63 +71144,63 @@
       </c>
       <c r="D20" s="1">
         <f ca="1">D11*1.05*RANDBETWEEN(95,105)/100</f>
-        <v>4.7094158727000011</v>
+        <v>4.5667063008000017</v>
       </c>
       <c r="E20" s="1">
         <f t="shared" ref="E20:AA28" ca="1" si="2">E11*1.05*RANDBETWEEN(95,105)/100</f>
-        <v>4.9648247103000012</v>
+        <v>5.4285191688000012</v>
       </c>
       <c r="F20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.8609202823999995</v>
+        <v>4.6748693754000001</v>
       </c>
       <c r="G20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.2994995119999988</v>
+        <v>4.4311168439999991</v>
       </c>
       <c r="H20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>3.5236156032000001</v>
+        <v>3.4534886400000007</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2.9861185536000003</v>
+        <v>2.9550131520000007</v>
       </c>
       <c r="J20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>3.5833830501000001</v>
+        <v>3.7637043570000004</v>
       </c>
       <c r="K20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.63514447920000006</v>
+        <v>0.62758550400000002</v>
       </c>
       <c r="L20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.52553088000000003</v>
+        <v>0.57513456000000007</v>
       </c>
       <c r="M20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.78178463999999992</v>
+        <v>0.84693335999999986</v>
       </c>
       <c r="N20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.44199751680000005</v>
+        <v>0.44660165760000015</v>
       </c>
       <c r="O20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.6111041706</v>
+        <v>0.62326992000000003</v>
       </c>
       <c r="P20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.92616279000000035</v>
+        <v>0.94334931600000038</v>
       </c>
       <c r="Q20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.7584873236000005</v>
+        <v>1.8300863972999999</v>
       </c>
       <c r="R20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.8393580799999998</v>
+        <v>1.8387950111999998</v>
       </c>
       <c r="S20" s="1">
         <f t="shared" ca="1" si="2"/>
@@ -70932,35 +71208,35 @@
       </c>
       <c r="T20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.044516564</v>
+        <v>1.0146968999999999</v>
       </c>
       <c r="U20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2.2592829167999993</v>
+        <v>2.1297833171999998</v>
       </c>
       <c r="V20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.3386941567999999</v>
+        <v>1.18819008</v>
       </c>
       <c r="W20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.87013197809999976</v>
+        <v>0.86047254719999988</v>
       </c>
       <c r="X20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.3193736192000001</v>
+        <v>1.4569405200000003</v>
       </c>
       <c r="Y20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.84942311999999998</v>
+        <v>0.80695196400000002</v>
       </c>
       <c r="Z20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>3.9142498500000005</v>
+        <v>3.7185373575000007</v>
       </c>
       <c r="AA20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.8601928655000002</v>
+        <v>4.7204314248000001</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.3">
@@ -70975,51 +71251,51 @@
       </c>
       <c r="D21" s="1">
         <f t="shared" ref="D21:S28" ca="1" si="3">D12*1.05*RANDBETWEEN(95,105)/100</f>
-        <v>-10.523066400000005</v>
+        <v>-10.729010250000004</v>
       </c>
       <c r="E21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-11.4870962052</v>
+        <v>-12.560977493399998</v>
       </c>
       <c r="F21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-13.294920038400003</v>
+        <v>-13.982037300000004</v>
       </c>
       <c r="G21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-14.072801700300001</v>
+        <v>-14.055564421500003</v>
       </c>
       <c r="H21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-15.181560576000003</v>
+        <v>-15.041843544000001</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-17.945681355000005</v>
+        <v>-18.121619407500003</v>
       </c>
       <c r="J21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-14.429466922500001</v>
+        <v>-15.663765921300001</v>
       </c>
       <c r="K21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-17.73394072128</v>
+        <v>-16.700895630719998</v>
       </c>
       <c r="L21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-15.941259767999995</v>
+        <v>-16.264964940839995</v>
       </c>
       <c r="M21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-23.833225505249999</v>
+        <v>-23.854729167360002</v>
       </c>
       <c r="N21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-21.567059539200002</v>
+        <v>-25.575411065400004</v>
       </c>
       <c r="O21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-22.707525771840004</v>
+        <v>-22.932352759680001</v>
       </c>
       <c r="P21" s="1">
         <f t="shared" ca="1" si="3"/>
@@ -71027,47 +71303,47 @@
       </c>
       <c r="Q21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-20.183400859439999</v>
+        <v>-20.401480825110003</v>
       </c>
       <c r="R21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-19.235584116000005</v>
+        <v>-20.395376687700001</v>
       </c>
       <c r="S21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-16.646392517999999</v>
+        <v>-17.145784293539997</v>
       </c>
       <c r="T21" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-16.187953934880003</v>
+        <v>-16.855498427040001</v>
       </c>
       <c r="U21" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-14.7766966326</v>
+        <v>-14.938967450820003</v>
       </c>
       <c r="V21" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-8.6627778652800007</v>
+        <v>-8.6591319149999997</v>
       </c>
       <c r="W21" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-10.078502834399998</v>
+        <v>-9.8969265687599997</v>
       </c>
       <c r="X21" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-10.999549989539998</v>
+        <v>-10.781737118459999</v>
       </c>
       <c r="Y21" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-11.437469862</v>
+        <v>-11.32749419025</v>
       </c>
       <c r="Z21" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-9.5606442855000004</v>
+        <v>-8.8322142446999994</v>
       </c>
       <c r="AA21" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-9.8649731963999994</v>
+        <v>-9.6636472127999991</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.3">
@@ -71082,99 +71358,99 @@
       </c>
       <c r="D22" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>10.139884890659999</v>
+        <v>9.8305469337599991</v>
       </c>
       <c r="E22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>11.069367623999996</v>
+        <v>11.525836391999997</v>
       </c>
       <c r="F22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>12.28848309276</v>
+        <v>13.052354855189998</v>
       </c>
       <c r="G22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>13.492575222000001</v>
+        <v>14.324158429560001</v>
       </c>
       <c r="H22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>13.788580414349997</v>
+        <v>14.072881041449998</v>
       </c>
       <c r="I22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16.2979300575</v>
+        <v>15.822673776000002</v>
       </c>
       <c r="J22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.254239423499998</v>
+        <v>15.2420348115</v>
       </c>
       <c r="K22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.866276751359997</v>
+        <v>16.028107265100001</v>
       </c>
       <c r="L22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.895794196800002</v>
+        <v>17.220443713200005</v>
       </c>
       <c r="M22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>18.904855074839997</v>
+        <v>16.923678086700001</v>
       </c>
       <c r="N22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>18.484238004960002</v>
+        <v>19.614112443450001</v>
       </c>
       <c r="O22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.32182453725</v>
+        <v>15.809067046079999</v>
       </c>
       <c r="P22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16.052179972499999</v>
+        <v>16.237555173000004</v>
       </c>
       <c r="Q22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16.456325165279999</v>
+        <v>16.782382890000001</v>
       </c>
       <c r="R22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.266371760640006</v>
+        <v>14.965298298720006</v>
       </c>
       <c r="S22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>13.899137484960001</v>
+        <v>13.230909721260002</v>
       </c>
       <c r="T22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>12.831241898999997</v>
+        <v>13.206015796049996</v>
       </c>
       <c r="U22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>12.3990296976</v>
+        <v>11.002435693200001</v>
       </c>
       <c r="V22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>8.87908822206</v>
+        <v>9.3349957646399986</v>
       </c>
       <c r="W22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>9.6488127120000016</v>
+        <v>10.143190023119999</v>
       </c>
       <c r="X22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>10.045793197440002</v>
+        <v>11.098572030000003</v>
       </c>
       <c r="Y22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>11.044442892000001</v>
+        <v>11.381469190560001</v>
       </c>
       <c r="Z22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>9.308100627</v>
+        <v>8.1651870719999984</v>
       </c>
       <c r="AA22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>9.7057078776000036</v>
+        <v>9.4202458812000014</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.3">
@@ -71189,99 +71465,99 @@
       </c>
       <c r="D23" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>5.2481812874400013</v>
+        <v>5.1977180058300005</v>
       </c>
       <c r="E23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>5.164400832318</v>
+        <v>5.2066806450750001</v>
       </c>
       <c r="F23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.4438758297919998</v>
+        <v>4.3972632708479997</v>
       </c>
       <c r="G23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.5126335654399989</v>
+        <v>4.698721547519999</v>
       </c>
       <c r="H23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>3.6997963833600007</v>
+        <v>3.4880235264000006</v>
       </c>
       <c r="I23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>3.0159797391359997</v>
+        <v>2.9008867623120005</v>
       </c>
       <c r="J23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>3.8054013732000005</v>
+        <v>3.72145869585</v>
       </c>
       <c r="K23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.59119761372000001</v>
+        <v>0.63463631279999999</v>
       </c>
       <c r="L23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.55809726000000015</v>
+        <v>0.54693531480000024</v>
       </c>
       <c r="M23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.85564944437699975</v>
+        <v>0.78170646153599987</v>
       </c>
       <c r="N23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.51389357338200004</v>
+        <v>0.51394297197600014</v>
       </c>
       <c r="O23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.6234497094</v>
+        <v>0.58077669531000009</v>
       </c>
       <c r="P23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.0326237705000003</v>
+        <v>0.9348687202260002</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.7740033882200001</v>
+        <v>1.9589031582750005</v>
       </c>
       <c r="R23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.818950589792</v>
+        <v>2.0909522350079999</v>
       </c>
       <c r="S23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.7359504469999996</v>
+        <v>1.9768239539999997</v>
       </c>
       <c r="T23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.00434285</v>
+        <v>1.023808464</v>
       </c>
       <c r="U23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2.2367153969999998</v>
+        <v>2.0652444287999994</v>
       </c>
       <c r="V23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.4056288646400004</v>
+        <v>1.3918532859000001</v>
       </c>
       <c r="W23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.86031938865599988</v>
+        <v>0.85145011660799985</v>
       </c>
       <c r="X23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.4297337250560003</v>
+        <v>1.2795175411200004</v>
       </c>
       <c r="Y23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.83300475119400008</v>
+        <v>0.81517666671</v>
       </c>
       <c r="Z23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>3.9929262719850005</v>
+        <v>3.7185373575000007</v>
       </c>
       <c r="AA23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.7676357390480009</v>
+        <v>4.8148400532960007</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.3">
@@ -71296,19 +71572,19 @@
       </c>
       <c r="D24" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-10.628297064000002</v>
+        <v>-10.4167728</v>
       </c>
       <c r="E24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-11.825528649983999</v>
+        <v>-11.129909317631999</v>
       </c>
       <c r="F24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-14.692271529936001</v>
+        <v>-14.549628117024003</v>
       </c>
       <c r="G24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-14.362962560100001</v>
+        <v>-13.650617649291</v>
       </c>
       <c r="H24" s="1">
         <f t="shared" ca="1" si="2"/>
@@ -71316,79 +71592,79 @@
       </c>
       <c r="I24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-18.121619407500003</v>
+        <v>-18.114581885400003</v>
       </c>
       <c r="J24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-15.322574980439999</v>
+        <v>-15.469907432175001</v>
       </c>
       <c r="K24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-18.478253295990598</v>
+        <v>-18.2735633026128</v>
       </c>
       <c r="L24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-15.280185485375997</v>
+        <v>-16.553534275823996</v>
       </c>
       <c r="M24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-25.348039036109995</v>
+        <v>-25.850077867504798</v>
       </c>
       <c r="N24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-21.342402669000009</v>
+        <v>-21.555826695690008</v>
       </c>
       <c r="O24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-22.015058649292797</v>
+        <v>-21.168325624319994</v>
       </c>
       <c r="P24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-21.5493733911456</v>
+        <v>-20.911012971147599</v>
       </c>
       <c r="Q24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-19.199360030860802</v>
+        <v>-19.787095542009606</v>
       </c>
       <c r="R24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-19.806824388997804</v>
+        <v>-18.268430261697006</v>
       </c>
       <c r="S24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-16.955294647199995</v>
+        <v>-14.713609056824998</v>
       </c>
       <c r="T24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-15.220014421248003</v>
+        <v>-15.220014421247999</v>
       </c>
       <c r="U24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-14.924463598926001</v>
+        <v>-14.215225241309405</v>
       </c>
       <c r="V24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-9.1969825003055981</v>
+        <v>-8.6654849833629015</v>
       </c>
       <c r="W24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-9.7939585448627984</v>
+        <v>-9.5010495060095987</v>
       </c>
       <c r="X24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-10.433182610654999</v>
+        <v>-10.648299777884997</v>
       </c>
       <c r="Y24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-11.911823875224</v>
+        <v>-12.405394690037999</v>
       </c>
       <c r="Z24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-10.147766256264001</v>
+        <v>-9.0869808120000002</v>
       </c>
       <c r="AA24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-9.8668887251759987</v>
+        <v>-9.8708370599999995</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.3">
@@ -71403,99 +71679,99 @@
       </c>
       <c r="D25" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>11.426304118319997</v>
+        <v>10.646239125626998</v>
       </c>
       <c r="E25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>11.283907944959997</v>
+        <v>11.613021926687997</v>
       </c>
       <c r="F25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>13.18158609138</v>
+        <v>11.914864073279999</v>
       </c>
       <c r="G25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>13.4709871016448</v>
+        <v>12.933046388304001</v>
       </c>
       <c r="H25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.097242579299998</v>
+        <v>14.636851419455997</v>
       </c>
       <c r="I25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.802271359875</v>
+        <v>16.301290455450001</v>
       </c>
       <c r="J25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>14.33935119645</v>
+        <v>14.921968861799998</v>
       </c>
       <c r="K25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16.512496981545606</v>
+        <v>16.527371616000003</v>
       </c>
       <c r="L25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.7586929718526</v>
+        <v>15.739201700397002</v>
       </c>
       <c r="M25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>17.051887769174996</v>
+        <v>17.410874880104998</v>
       </c>
       <c r="N25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>18.678239078291099</v>
+        <v>18.855700095636603</v>
       </c>
       <c r="O25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>17.118255410833502</v>
+        <v>16.3064618552682</v>
       </c>
       <c r="P25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>17.234972181</v>
+        <v>16.403244511499999</v>
       </c>
       <c r="Q25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.326790880674</v>
+        <v>15.305533195680001</v>
       </c>
       <c r="R25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.266371760640004</v>
+        <v>16.525068534374405</v>
       </c>
       <c r="S25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>13.477540315270501</v>
+        <v>13.226859442773902</v>
       </c>
       <c r="T25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>12.431516953346398</v>
+        <v>12.937550643763197</v>
       </c>
       <c r="U25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>12.1663662200052</v>
+        <v>10.665890601408</v>
       </c>
       <c r="V25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>8.9678791042806001</v>
+        <v>8.1110039884817979</v>
       </c>
       <c r="W25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>10.865508100524004</v>
+        <v>10.046701896</v>
       </c>
       <c r="X25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>10.045793197440002</v>
+        <v>10.889284671720004</v>
       </c>
       <c r="Y25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>11.13040737018</v>
+        <v>10.686921750960003</v>
       </c>
       <c r="Z25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>8.9340755212799987</v>
+        <v>9.4924552413600001</v>
       </c>
       <c r="AA25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>9.1264461334200018</v>
+        <v>8.9566951680360027</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.3">
@@ -71510,99 +71786,99 @@
       </c>
       <c r="D26" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>4.6976423330182522</v>
+        <v>4.8874460636452515</v>
       </c>
       <c r="E26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.9091560367850011</v>
+        <v>5.2066806450750001</v>
       </c>
       <c r="F26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.4434401983999994</v>
+        <v>4.2239342525990393</v>
       </c>
       <c r="G26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.8382875340799991</v>
+        <v>4.4637854701439981</v>
       </c>
       <c r="H26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>3.2764286298240006</v>
+        <v>3.5566948793779205</v>
       </c>
       <c r="I26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2.7280056320327999</v>
+        <v>2.8393528006872</v>
       </c>
       <c r="J26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>3.6478129869216009</v>
+        <v>4.1554982995344005</v>
       </c>
       <c r="K26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.65342894147999997</v>
+        <v>0.59623773511680001</v>
       </c>
       <c r="L26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.53019239700000009</v>
+        <v>0.57987743709000006</v>
       </c>
       <c r="M26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.76607233230527982</v>
+        <v>0.7977477295487696</v>
       </c>
       <c r="N26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.48819889471290007</v>
+        <v>0.47916833774376</v>
       </c>
       <c r="O26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.63498352902389998</v>
+        <v>0.6549962646956401</v>
       </c>
       <c r="P26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.0211527955865602</v>
+        <v>1.0119476922609605</v>
       </c>
       <c r="Q26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.7025001904295001</v>
+        <v>1.9398627304056004</v>
       </c>
       <c r="R26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2.0907589147199999</v>
+        <v>1.8898024753440001</v>
       </c>
       <c r="S26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.6491529246499999</v>
+        <v>1.824392553984</v>
       </c>
       <c r="T26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.0431446523750001</v>
+        <v>0.98274947872499996</v>
       </c>
       <c r="U26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2.0045019455999995</v>
+        <v>2.2158351683999999</v>
       </c>
       <c r="V26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.2706801763040003</v>
+        <v>1.3361791544640005</v>
       </c>
       <c r="W26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.93181658169599968</v>
+        <v>0.93208537494071975</v>
       </c>
       <c r="X26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.3725773603942399</v>
+        <v>1.3604679843955199</v>
       </c>
       <c r="Y26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.75977631072000007</v>
+        <v>0.83975276448000002</v>
       </c>
       <c r="Z26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.4453352696480009</v>
+        <v>3.9832972173540004</v>
       </c>
       <c r="AA26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.5294355071503993</v>
+        <v>4.8125252263473</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.3">
@@ -71617,99 +71893,99 @@
       </c>
       <c r="D27" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-10.178675135999999</v>
+        <v>-10.606825756800001</v>
       </c>
       <c r="E27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-12.42694953108</v>
+        <v>-11.355864833401199</v>
       </c>
       <c r="F27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-13.841732749022645</v>
+        <v>-13.690064397101402</v>
       </c>
       <c r="G27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-14.195133518791685</v>
+        <v>-15.062830553937603</v>
       </c>
       <c r="H27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-15.787422758016</v>
+        <v>-16.940217241584001</v>
       </c>
       <c r="I27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-19.027700377875007</v>
+        <v>-17.947440735524999</v>
       </c>
       <c r="J27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-15.638322094529398</v>
+        <v>-15.031008615130201</v>
       </c>
       <c r="K27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-17.391512458582834</v>
+        <v>-17.192963165006372</v>
       </c>
       <c r="L27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-15.286619247685627</v>
+        <v>-16.069929808883323</v>
       </c>
       <c r="M27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-27.142581760880038</v>
+        <v>-24.115139949089571</v>
       </c>
       <c r="N27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-21.782730134592001</v>
+        <v>-22.633618030474505</v>
       </c>
       <c r="O27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-20.504221291008001</v>
+        <v>-18.359164294410242</v>
       </c>
       <c r="P27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-21.564045215880633</v>
+        <v>-20.496518224995452</v>
       </c>
       <c r="Q27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-18.995611720329215</v>
+        <v>-19.984966497429696</v>
       </c>
       <c r="R27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-20.150632167447604</v>
+        <v>-18.406827460649257</v>
       </c>
       <c r="S27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-15.644780796314876</v>
+        <v>-17.640288550946874</v>
       </c>
       <c r="T27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-16.16205320858419</v>
+        <v>-17.158563626480639</v>
       </c>
       <c r="U27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-15.215338348660175</v>
+        <v>-14.054580577731459</v>
       </c>
       <c r="V27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-8.7548198800986015</v>
+        <v>-8.9154422196839995</v>
       </c>
       <c r="W27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-10.171341350893798</v>
+        <v>-9.778163449934878</v>
       </c>
       <c r="X27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-11.20425311365668</v>
+        <v>-11.41905326611392</v>
       </c>
       <c r="Y27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-11.778394444424997</v>
+        <v>-11.432894874055199</v>
       </c>
       <c r="Z27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-9.3672041697561603</v>
+        <v>-10.027435499827201</v>
       </c>
       <c r="AA27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-10.465949826347398</v>
+        <v>-10.166922688451759</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.3">
@@ -71724,99 +72000,99 @@
       </c>
       <c r="D28" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>10.537865025797087</v>
+        <v>10.854384636705431</v>
       </c>
       <c r="E28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>10.615900594618365</v>
+        <v>11.51783746154395</v>
       </c>
       <c r="F28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>12.535429910429999</v>
+        <v>13.1671659326487</v>
       </c>
       <c r="G28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>13.744530615239425</v>
+        <v>12.928023846017279</v>
       </c>
       <c r="H28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16.159729710524399</v>
+        <v>14.463083652144746</v>
       </c>
       <c r="I28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.351158097475199</v>
+        <v>15.518828513588401</v>
       </c>
       <c r="J28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>14.620514945400002</v>
+        <v>15.369627927653999</v>
       </c>
       <c r="K28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>17.876005139865601</v>
+        <v>16.005899986771968</v>
       </c>
       <c r="L28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.273197885346031</v>
+        <v>16.052442675414703</v>
       </c>
       <c r="M28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>19.807019375270396</v>
+        <v>19.836777517360648</v>
       </c>
       <c r="N28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>18.656047111069373</v>
+        <v>20.002359789187782</v>
       </c>
       <c r="O28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>18.358887735969162</v>
+        <v>16.449156001991788</v>
       </c>
       <c r="P28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>17.236661884154998</v>
+        <v>16.403244511499999</v>
       </c>
       <c r="Q28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.322099005914609</v>
+        <v>15.928914808129051</v>
       </c>
       <c r="R28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16.035796897376262</v>
+        <v>14.797553946215041</v>
       </c>
       <c r="S28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>14.185465853935764</v>
+        <v>14.042178320057623</v>
       </c>
       <c r="T28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>12.936467229595726</v>
+        <v>11.934256275212542</v>
       </c>
       <c r="U28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>12.045860368298063</v>
+        <v>12.163957038575496</v>
       </c>
       <c r="V28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>8.6996789171303774</v>
+        <v>9.5095034858262597</v>
       </c>
       <c r="W28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>8.8858054919172016</v>
+        <v>9.8418295509367688</v>
       </c>
       <c r="X28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>10.771766649025205</v>
+        <v>9.9290996400960037</v>
       </c>
       <c r="Y28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>11.143387437084005</v>
+        <v>11.477689060196523</v>
       </c>
       <c r="Z28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>8.9377980527472012</v>
+        <v>8.9341860915216031</v>
       </c>
       <c r="AA28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>9.3241966811162413</v>
+        <v>9.5972345800531187</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.3">
@@ -71831,99 +72107,99 @@
       </c>
       <c r="D29" s="1">
         <f ca="1">D20*0.95*RANDBETWEEN(95,105)/100</f>
-        <v>4.6081634314369504</v>
+        <v>4.4685221153328012</v>
       </c>
       <c r="E29" s="1">
         <f t="shared" ref="E29:AA37" ca="1" si="4">E20*0.95*RANDBETWEEN(95,105)/100</f>
-        <v>4.5279201357936003</v>
+        <v>5.1570932103600011</v>
       </c>
       <c r="F29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.8487679816939995</v>
+        <v>4.5299484247625994</v>
       </c>
       <c r="G29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.0845245363999982</v>
+        <v>4.2095610017999991</v>
       </c>
       <c r="H29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>3.2470117783488002</v>
+        <v>3.3464304921600005</v>
       </c>
       <c r="I29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>2.9219170046976006</v>
+        <v>2.947625619120001</v>
       </c>
       <c r="J29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>3.3701717586190498</v>
+        <v>3.3967431821925005</v>
       </c>
       <c r="K29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.5792517650304001</v>
+        <v>0.60216829108799996</v>
       </c>
       <c r="L29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.48427670592000005</v>
+        <v>0.55184161032000001</v>
       </c>
       <c r="M29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.75012236207999994</v>
+        <v>0.82067842583999995</v>
       </c>
       <c r="N29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.42409661736960003</v>
+        <v>0.41154342747840011</v>
       </c>
       <c r="O29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.60957641017349995</v>
+        <v>0.59802748824000007</v>
       </c>
       <c r="P29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.85345901098500032</v>
+        <v>0.88722003169800034</v>
       </c>
       <c r="Q29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.6872685869942003</v>
+        <v>1.6516529735632497</v>
       </c>
       <c r="R29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.6774945689599996</v>
+        <v>1.7293867080335996</v>
       </c>
       <c r="S29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.7694262348622996</v>
+        <v>1.8423922651658995</v>
       </c>
       <c r="T29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.002213643158</v>
+        <v>0.94468281389999986</v>
       </c>
       <c r="U29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>2.1033923955407996</v>
+        <v>2.1244588589069995</v>
       </c>
       <c r="V29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.208171476512</v>
+        <v>1.1400683817599999</v>
       </c>
       <c r="W29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.82662537919499979</v>
+        <v>0.80927443064159987</v>
       </c>
       <c r="X29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.3035411357696001</v>
+        <v>1.3287297542400003</v>
       </c>
       <c r="Y29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.78274340507999995</v>
+        <v>0.72827414751000008</v>
       </c>
       <c r="Z29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>3.6441666103500001</v>
+        <v>3.4266321749362505</v>
       </c>
       <c r="AA29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.7095268866694999</v>
+        <v>4.5292539520956003</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.3">
@@ -71938,99 +72214,99 @@
       </c>
       <c r="D30" s="1">
         <f t="shared" ref="D30:S37" ca="1" si="5">D21*0.95*RANDBETWEEN(95,105)/100</f>
-        <v>-9.5970365568000027</v>
+        <v>-10.090634140125003</v>
       </c>
       <c r="E30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-10.367104325192999</v>
+        <v>-12.052257904917296</v>
       </c>
       <c r="F30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-12.503872296115201</v>
+        <v>-12.618788663250003</v>
       </c>
       <c r="G30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-13.23546999913215</v>
+        <v>-13.219258338420753</v>
       </c>
       <c r="H30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-14.710932198144</v>
+        <v>-14.718443907803998</v>
       </c>
       <c r="I30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-17.389365232995004</v>
+        <v>-17.043383052753754</v>
       </c>
       <c r="J30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-13.433833704847499</v>
+        <v>-14.731771848982651</v>
       </c>
       <c r="K30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-16.0048815009552</v>
+        <v>-15.231216815216637</v>
       </c>
       <c r="L30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-14.538428908415995</v>
+        <v>-15.142682359922034</v>
       </c>
       <c r="M30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-22.415148587687622</v>
+        <v>-22.435372781902082</v>
       </c>
       <c r="N30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-21.308254824729602</v>
+        <v>-25.268506132615201</v>
       </c>
       <c r="O30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-22.219313967745443</v>
+        <v>-21.785735121695996</v>
       </c>
       <c r="P30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-19.078081371759897</v>
+        <v>-18.511405687450196</v>
       </c>
       <c r="Q30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-19.174230816467997</v>
+        <v>-19.962848987370137</v>
       </c>
       <c r="R30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-18.091066861098003</v>
+        <v>-19.375607853315</v>
       </c>
       <c r="S30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-16.446635807783998</v>
+        <v>-15.474070324919847</v>
       </c>
       <c r="T30" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-15.224770675754641</v>
+        <v>-15.372214565460482</v>
       </c>
       <c r="U30" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-13.616725946940898</v>
+        <v>-14.475859459844582</v>
       </c>
       <c r="V30" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-8.1473425822958401</v>
+        <v>-8.2261753192499985</v>
       </c>
       <c r="W30" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-9.4788319157531991</v>
+        <v>-9.0259970307091173</v>
       </c>
       <c r="X30" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-10.240581040261738</v>
+        <v>-10.037797257286257</v>
       </c>
       <c r="Y30" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-10.648284441522001</v>
+        <v>-10.97634187035225</v>
       </c>
       <c r="Z30" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-9.0826120712250002</v>
+        <v>-8.5584156031142999</v>
       </c>
       <c r="AA30" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-9.7465935180431984</v>
+        <v>-9.6394880947679979</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.3">
@@ -72045,99 +72321,99 @@
       </c>
       <c r="D31" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>9.4402328332044583</v>
+        <v>9.2456293912012786</v>
       </c>
       <c r="E31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>10.410740250371996</v>
+        <v>10.730553680951997</v>
       </c>
       <c r="F31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>11.32383716997834</v>
+        <v>11.779750256808972</v>
       </c>
       <c r="G31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>12.177049137854999</v>
+        <v>13.063632487758721</v>
       </c>
       <c r="H31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>13.492125935441472</v>
+        <v>12.700775139908624</v>
       </c>
       <c r="I31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>15.94752456126375</v>
+        <v>15.181855488072001</v>
       </c>
       <c r="J31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>14.201696903278496</v>
+        <v>14.1903344095065</v>
       </c>
       <c r="K31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>15.525151801205757</v>
+        <v>14.922167863808102</v>
       </c>
       <c r="L31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>14.949994442090402</v>
+        <v>16.686609958090802</v>
       </c>
       <c r="M31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>18.677996813941917</v>
+        <v>15.273619473246752</v>
       </c>
       <c r="N31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>17.735626365759121</v>
+        <v>18.447072753064724</v>
       </c>
       <c r="O31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>13.827946644868122</v>
+        <v>14.568055282962719</v>
       </c>
       <c r="P31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>15.554562393352498</v>
+        <v>16.042704510924004</v>
       </c>
       <c r="Q31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>16.258849263296639</v>
+        <v>15.146100558225001</v>
       </c>
       <c r="R31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>14.793114236060164</v>
+        <v>14.643544385297526</v>
       </c>
       <c r="S31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>13.204180610711999</v>
+        <v>12.946445162252912</v>
       </c>
       <c r="T31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>12.067783006009497</v>
+        <v>12.294800706122546</v>
       </c>
       <c r="U31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>11.896868994847198</v>
+        <v>9.9296982131130012</v>
       </c>
       <c r="V31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>8.2664311347378607</v>
+        <v>9.1342933557002386</v>
       </c>
       <c r="W31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>8.7997171933440015</v>
+        <v>9.7323908271836395</v>
       </c>
       <c r="X31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>9.7343736083193626</v>
+        <v>10.016461257075003</v>
       </c>
       <c r="Y31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>10.177454124978</v>
+        <v>10.488023859101041</v>
       </c>
       <c r="Z31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>8.9311225516064994</v>
+        <v>7.4466506096639975</v>
       </c>
       <c r="AA31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>8.759401359534003</v>
+        <v>8.6807565795258004</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.3">
@@ -72152,99 +72428,99 @@
       </c>
       <c r="D32" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>5.0356299452986812</v>
+        <v>4.8390754634277302</v>
       </c>
       <c r="E32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.9552425986091206</v>
+        <v>4.9463466128212499</v>
       </c>
       <c r="F32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.1372483975363519</v>
+        <v>4.2191741083786551</v>
       </c>
       <c r="G32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.1155218116812788</v>
+        <v>4.3298719060396795</v>
       </c>
       <c r="H32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>3.58510269547584</v>
+        <v>3.1479412325760006</v>
       </c>
       <c r="I32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>3.0084397897881594</v>
+        <v>2.8660761211642565</v>
       </c>
       <c r="J32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>3.7597365567216001</v>
+        <v>3.4646780458363495</v>
       </c>
       <c r="K32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.57287048769467996</v>
+        <v>0.60290449715999994</v>
       </c>
       <c r="L32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.55140009288000014</v>
+        <v>0.50919677807880026</v>
       </c>
       <c r="M32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.79660963271498675</v>
+        <v>0.76489977261297581</v>
       </c>
       <c r="N32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.51260883944854496</v>
+        <v>0.51265811454606014</v>
       </c>
       <c r="O32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.59819999616929986</v>
+        <v>0.52966834612272007</v>
       </c>
       <c r="P32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.93194295287625029</v>
+        <v>0.89700653705684719</v>
       </c>
       <c r="Q32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.70215625099709</v>
+        <v>1.8981771603684754</v>
       </c>
       <c r="R32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.7107230296993761</v>
+        <v>2.0459967619553279</v>
       </c>
       <c r="S32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.6491529246499994</v>
+        <v>1.8404231011739995</v>
       </c>
       <c r="T32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.97320822164999998</v>
+        <v>0.93371331916800004</v>
       </c>
       <c r="U32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>2.0823820346069999</v>
+        <v>1.9227425632127992</v>
       </c>
       <c r="V32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.3620543698361605</v>
+        <v>1.30903801538895</v>
       </c>
       <c r="W32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.78461128245427181</v>
+        <v>0.80078883466982376</v>
       </c>
       <c r="X32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.3989944499672962</v>
+        <v>1.2520079139859202</v>
       </c>
       <c r="Y32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.77552742336161418</v>
+        <v>0.78990619004199003</v>
       </c>
       <c r="Z32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>3.8312127579696078</v>
+        <v>3.6032626994175008</v>
       </c>
       <c r="AA32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.3027912544908204</v>
+        <v>4.4368751091122647</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.3">
@@ -72259,99 +72535,99 @@
       </c>
       <c r="D33" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-10.298819855015999</v>
+        <v>-10.2917715264</v>
       </c>
       <c r="E33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-11.2342522174848</v>
+        <v>-11.102084544337918</v>
       </c>
       <c r="F33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-13.957657953439201</v>
+        <v>-13.26926084272589</v>
       </c>
       <c r="G33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-13.78126257641595</v>
+        <v>-13.357129369831243</v>
       </c>
       <c r="H33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-17.225852592312002</v>
+        <v>-16.222404868487999</v>
       </c>
       <c r="I33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-18.076315358981251</v>
+        <v>-17.553029846952601</v>
       </c>
       <c r="J33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-14.265317306789639</v>
+        <v>-14.990340301777573</v>
       </c>
       <c r="K33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-17.203253818567244</v>
+        <v>-17.880681691606625</v>
       </c>
       <c r="L33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-14.225852686885053</v>
+        <v>-15.883116137653124</v>
       </c>
       <c r="M33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-25.284668938519722</v>
+        <v>-25.785452672836037</v>
       </c>
       <c r="N33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-21.289046662327511</v>
+        <v>-19.863694300078343</v>
       </c>
       <c r="O33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-21.33259183116472</v>
+        <v>-21.115404810259193</v>
       </c>
       <c r="P33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-19.65302853272479</v>
+        <v>-20.064116945816121</v>
       </c>
       <c r="Q33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-18.968967710490475</v>
+        <v>-18.045831134312763</v>
       </c>
       <c r="R33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-18.628318337852431</v>
+        <v>-18.049209098556638</v>
       </c>
       <c r="S33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-16.107529914839994</v>
+        <v>-13.418811459824397</v>
       </c>
       <c r="T33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-14.314423563183745</v>
+        <v>-15.181964385194879</v>
       </c>
       <c r="U33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-14.036458014789906</v>
+        <v>-12.964285420074175</v>
       </c>
       <c r="V33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-9.1739900440548343</v>
+        <v>-8.3968549488786515</v>
       </c>
       <c r="W33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-9.0251327990910681</v>
+        <v>-9.2065169713233015</v>
       </c>
       <c r="X33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-9.8124082453210253</v>
+        <v>-9.8124082453210235</v>
       </c>
       <c r="Y33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-11.203070354648172</v>
+        <v>-11.313719957314657</v>
       </c>
       <c r="Z33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-10.122396840623342</v>
+        <v>-8.5463054536859993</v>
       </c>
       <c r="AA33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-9.5610151746955427</v>
+        <v>-9.2835222549300003</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.3">
@@ -72366,99 +72642,99 @@
       </c>
       <c r="D34" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>10.746439023279956</v>
+        <v>10.518484256119473</v>
       </c>
       <c r="E34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>11.255698175097598</v>
+        <v>11.473665663567742</v>
       </c>
       <c r="F34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>12.898181990415328</v>
+        <v>11.432312078312158</v>
       </c>
       <c r="G34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>13.05338650149381</v>
+        <v>12.286394068888802</v>
       </c>
       <c r="H34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>14.916075668348398</v>
+        <v>13.487858583028702</v>
       </c>
       <c r="I34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>14.711914636043623</v>
+        <v>15.021639154697175</v>
       </c>
       <c r="J34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>14.167278982092601</v>
+        <v>14.742905235458398</v>
       </c>
       <c r="K34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>15.059397247169592</v>
+        <v>15.072962913792002</v>
       </c>
       <c r="L34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>15.270173489725169</v>
+        <v>14.354151950762066</v>
       </c>
       <c r="M34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>16.199293380716245</v>
+        <v>17.036541070182739</v>
       </c>
       <c r="N34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>17.744327124376543</v>
+        <v>17.733785939946223</v>
       </c>
       <c r="O34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>16.750212919500584</v>
+        <v>15.181315987254694</v>
       </c>
       <c r="P34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>15.718294629072</v>
+        <v>16.050574754502748</v>
       </c>
       <c r="Q34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>13.978033283174689</v>
+        <v>14.10404883981912</v>
       </c>
       <c r="R34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>14.212992109155842</v>
+        <v>14.9138743522729</v>
       </c>
       <c r="S34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>12.163480134531628</v>
+        <v>13.068137129460615</v>
       </c>
       <c r="T34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>11.455642872508704</v>
+        <v>12.905206767153789</v>
       </c>
       <c r="U34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>11.21130647173479</v>
+        <v>10.537899914191105</v>
       </c>
       <c r="V34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>8.1787057431039081</v>
+        <v>7.4742901753859758</v>
       </c>
       <c r="W34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>9.8061210607229121</v>
+        <v>9.9261414732479984</v>
       </c>
       <c r="X34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>9.829808643695042</v>
+        <v>10.862061460040705</v>
       </c>
       <c r="Y34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>10.99684248173784</v>
+        <v>9.6449468802414025</v>
       </c>
       <c r="Z34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>8.0630031579551993</v>
+        <v>8.6571191801203202</v>
       </c>
       <c r="AA34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>8.8435263032839817</v>
+        <v>8.0834173891524923</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.3">
@@ -72473,99 +72749,99 @@
       </c>
       <c r="D35" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>4.5966430228583599</v>
+        <v>4.410920072439839</v>
       </c>
       <c r="E35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.5704242702468356</v>
+        <v>5.0947370112058872</v>
       </c>
       <c r="F35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.0102047790559991</v>
+        <v>3.932482789169705</v>
       </c>
       <c r="G35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.366554499507199</v>
+        <v>4.0709723487713259</v>
       </c>
       <c r="H35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>3.2371114862661123</v>
+        <v>3.2774943313467535</v>
       </c>
       <c r="I35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>2.5138571899182249</v>
+        <v>2.6164636058332547</v>
       </c>
       <c r="J35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>3.2921512206967445</v>
+        <v>4.0661550860944109</v>
       </c>
       <c r="K35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.63938021923817989</v>
+        <v>0.56076158987735036</v>
       </c>
       <c r="L35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.51375643269300009</v>
+        <v>0.56190123654021007</v>
       </c>
       <c r="M35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.74232409000381605</v>
+        <v>0.78817475679418436</v>
       </c>
       <c r="N35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.47770261847657275</v>
+        <v>0.44610572243944058</v>
       </c>
       <c r="O35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.60926669609843198</v>
+        <v>0.62224645146085811</v>
       </c>
       <c r="P35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.0088989620395215</v>
+        <v>0.96135030764791241</v>
       </c>
       <c r="Q35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.6497226845261854</v>
+        <v>1.8060122020076139</v>
       </c>
       <c r="R35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>2.04580759805352</v>
+        <v>1.7953123515768001</v>
       </c>
       <c r="S35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.5980291839858498</v>
+        <v>1.8198315725990399</v>
       </c>
       <c r="T35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.98107754555868754</v>
+        <v>0.88693140454931241</v>
       </c>
       <c r="U35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.9614051537695993</v>
+        <v>1.9997912394809998</v>
       </c>
       <c r="V35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.2192176291636883</v>
+        <v>1.2312890908385763</v>
       </c>
       <c r="W35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.84981672250675155</v>
+        <v>0.8854811061936837</v>
       </c>
       <c r="X35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.2778695225270373</v>
+        <v>1.357066814434531</v>
       </c>
       <c r="Y35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.70013387032848007</v>
+        <v>0.82169808004367995</v>
       </c>
       <c r="Z35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.1808378211039443</v>
+        <v>3.7462910329214374</v>
       </c>
       <c r="AA35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.1738748198390923</v>
+        <v>4.6633369443305339</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.3">
@@ -72580,99 +72856,99 @@
       </c>
       <c r="D36" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-9.7664387929919982</v>
+        <v>-10.378779003028802</v>
       </c>
       <c r="E36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-11.687546033980741</v>
+        <v>-10.895952307648452</v>
       </c>
       <c r="F36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-13.675631956034373</v>
+        <v>-12.875505565473867</v>
       </c>
       <c r="G36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-13.350523074423579</v>
+        <v>-14.166592135978314</v>
       </c>
       <c r="H36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-14.548110071511742</v>
+        <v>-16.576002570889944</v>
       </c>
       <c r="I36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-17.172499591032192</v>
+        <v>-16.197565263811313</v>
       </c>
       <c r="J36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-14.55927787000687</v>
+        <v>-14.7078419299049</v>
       </c>
       <c r="K36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-15.861059362227543</v>
+        <v>-17.149980757093857</v>
       </c>
       <c r="L36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-14.812734051007372</v>
+        <v>-15.419097651623549</v>
       </c>
       <c r="M36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-26.816870779749475</v>
+        <v>-22.451195292602389</v>
       </c>
       <c r="N36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-21.314401436698272</v>
+        <v>-22.362014614108812</v>
       </c>
       <c r="O36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-20.063380533251326</v>
+        <v>-18.313266383674215</v>
       </c>
       <c r="P36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-19.461550807332269</v>
+        <v>-19.276975390608222</v>
       </c>
       <c r="Q36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-18.045831134312753</v>
+        <v>-18.985718172558212</v>
       </c>
       <c r="R36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-18.760238547893717</v>
+        <v>-18.185945531121465</v>
       </c>
       <c r="S36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-15.605668844324089</v>
+        <v>-16.255525899697545</v>
       </c>
       <c r="T36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-16.121648075562732</v>
+        <v>-16.463641799608173</v>
       </c>
       <c r="U36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-14.454571431227166</v>
+        <v>-12.951296002379541</v>
       </c>
       <c r="V36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-8.3170788860936717</v>
+        <v>-8.8931536141347891</v>
       </c>
       <c r="W36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-9.5661465405156143</v>
+        <v>-9.2892552774381336</v>
       </c>
       <c r="X36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-10.856921267133323</v>
+        <v>-10.631138590752059</v>
       </c>
       <c r="Y36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-10.63000098609356</v>
+        <v>-10.318187623834817</v>
       </c>
       <c r="Z36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-8.6318786424303013</v>
+        <v>-9.4308030875874813</v>
       </c>
       <c r="AA36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-9.4455197182785255</v>
+        <v>-9.3688192574082958</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.3">
@@ -72687,99 +72963,99 @@
       </c>
       <c r="D37" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>9.810752339017089</v>
+        <v>10.31166540487016</v>
       </c>
       <c r="E37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>10.085105564887446</v>
+        <v>11.051365044351419</v>
       </c>
       <c r="F37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>12.385004751504837</v>
+        <v>12.884071865096752</v>
       </c>
       <c r="G37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>13.318450166167002</v>
+        <v>12.895703786402235</v>
       </c>
       <c r="H37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>15.044708360498214</v>
+        <v>14.014728058928258</v>
       </c>
       <c r="I37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>14.291928188749411</v>
+        <v>14.005742733513532</v>
       </c>
       <c r="J37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>13.472804522186101</v>
+        <v>14.893169461896726</v>
       </c>
       <c r="K37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>17.831315127015937</v>
+        <v>15.205604987433368</v>
       </c>
       <c r="L37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>14.074251851346366</v>
+        <v>15.402318747060406</v>
       </c>
       <c r="M37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>18.252168354311667</v>
+        <v>17.902691709417983</v>
       </c>
       <c r="N37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>17.723244755515903</v>
+        <v>19.572309053720243</v>
       </c>
       <c r="O37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>16.91771504869558</v>
+        <v>14.84536329179759</v>
       </c>
       <c r="P37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>16.866073653645664</v>
+        <v>15.583082285924997</v>
       </c>
       <c r="Q37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>15.138233817843634</v>
+        <v>15.586443139754277</v>
       </c>
       <c r="R37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>14.929326911457299</v>
+        <v>14.338829773882374</v>
       </c>
       <c r="S37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>13.880478338076143</v>
+        <v>13.873672180216932</v>
       </c>
       <c r="T37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>12.4125403067971</v>
+        <v>11.450918896066435</v>
       </c>
       <c r="U37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>12.015745717377319</v>
+        <v>11.093528819180852</v>
       </c>
       <c r="V37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>7.9341071724229035</v>
+        <v>9.3050491608809942</v>
       </c>
       <c r="W37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>8.188269760801699</v>
+        <v>8.8822511697204316</v>
       </c>
       <c r="X37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>10.744837232402642</v>
+        <v>9.4326446580912027</v>
       </c>
       <c r="Y37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>11.115528968491294</v>
+        <v>11.448994837546032</v>
       </c>
       <c r="Z37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>8.0663627426043476</v>
+        <v>8.9118506262928001</v>
       </c>
       <c r="AA37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>8.6808271101192194</v>
+        <v>8.7526779370084427</v>
       </c>
     </row>
   </sheetData>

--- a/data/CS7/case33_3/case33_3_operational_data.xlsx
+++ b/data/CS7/case33_3/case33_3_operational_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\case33_3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FB17DC8-D35C-4708-927A-1447AF066603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF241D13-61A4-40A5-A6D3-480A3249967E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-12510" yWindow="-15930" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15195" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -741,8 +741,7 @@
         <v>2.6999999999999997</v>
       </c>
       <c r="C14" s="1">
-        <f t="shared" si="1"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D14" s="2">
         <v>3.2301480484522194E-2</v>
@@ -961,8 +960,7 @@
         <v>17.64</v>
       </c>
       <c r="C24" s="1">
-        <f t="shared" si="1"/>
-        <v>19.5</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2">
         <v>0.11305518169582769</v>
@@ -983,8 +981,7 @@
         <v>9.7650000000000006</v>
       </c>
       <c r="C25" s="1">
-        <f t="shared" si="1"/>
-        <v>-8.5</v>
+        <v>4.25</v>
       </c>
       <c r="D25" s="2">
         <v>0.11305518169582769</v>
@@ -1093,8 +1090,7 @@
         <v>4.2</v>
       </c>
       <c r="C30" s="1">
-        <f t="shared" si="1"/>
-        <v>26.999999999999996</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2">
         <v>5.3835800807536999E-2</v>
@@ -70185,63 +70181,63 @@
       </c>
       <c r="E11" s="1">
         <f t="shared" ref="E11:AA19" ca="1" si="0">E2*0.95*RANDBETWEEN(95,105)/100</f>
-        <v>4.9711714000000002</v>
+        <v>5.0676990000000002</v>
       </c>
       <c r="F11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.4081748000000003</v>
+        <v>4.3217400000000001</v>
       </c>
       <c r="G11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.1373639999999989</v>
+        <v>3.9735079999999994</v>
       </c>
       <c r="H11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3.2890367999999999</v>
+        <v>3.2554752000000002</v>
       </c>
       <c r="I11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2.7060560000000002</v>
+        <v>2.9054496000000007</v>
       </c>
       <c r="J11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3.6576330000000001</v>
+        <v>3.4137907999999997</v>
       </c>
       <c r="K11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.62915840000000001</v>
+        <v>0.63520800000000011</v>
       </c>
       <c r="L11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.52668000000000004</v>
+        <v>0.51072000000000006</v>
       </c>
       <c r="M11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.80660319999999985</v>
+        <v>0.79884739999999976</v>
       </c>
       <c r="N11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.4430572000000001</v>
+        <v>0.43392200000000003</v>
       </c>
       <c r="O11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.59359039999999996</v>
+        <v>0.58217519999999989</v>
       </c>
       <c r="P11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.94571360000000027</v>
+        <v>0.93662020000000024</v>
       </c>
       <c r="Q11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.6921742</v>
+        <v>1.7424368000000001</v>
       </c>
       <c r="R11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.7338943999999998</v>
+        <v>1.8768959999999999</v>
       </c>
       <c r="S11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.7754587999999996</v>
+        <v>1.7930375999999995</v>
       </c>
       <c r="T11" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70249,31 +70245,31 @@
       </c>
       <c r="U11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2.0488535999999997</v>
+        <v>1.9885931999999997</v>
       </c>
       <c r="V11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.1316096</v>
+        <v>1.1433971999999999</v>
       </c>
       <c r="W11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.85364339999999983</v>
+        <v>0.87021899999999985</v>
       </c>
       <c r="X11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.3214880000000002</v>
+        <v>1.2837312000000001</v>
       </c>
       <c r="Y11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.80897439999999998</v>
+        <v>0.78563860000000008</v>
       </c>
       <c r="Z11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3.3728230000000003</v>
+        <v>3.5148366000000006</v>
       </c>
       <c r="AA11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.3227393999999997</v>
+        <v>4.3655387999999995</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
@@ -70292,23 +70288,23 @@
       </c>
       <c r="E12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-11.614403599999997</v>
+        <v>-11.050597599999998</v>
       </c>
       <c r="F12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-13.316226000000002</v>
+        <v>-12.682120000000003</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-14.090791400000001</v>
+        <v>-12.996361000000002</v>
       </c>
       <c r="H12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-14.183728</v>
+        <v>-15.353520000000001</v>
       </c>
       <c r="I12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-16.436843</v>
+        <v>-15.798519000000001</v>
       </c>
       <c r="J12" s="1">
         <f t="shared" ca="1" si="1"/>
@@ -70316,23 +70312,23 @@
       </c>
       <c r="K12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-16.39754112</v>
+        <v>-17.080772</v>
       </c>
       <c r="L12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-15.646911919999996</v>
+        <v>-16.266591599999995</v>
       </c>
       <c r="M12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-21.844990079999999</v>
+        <v>-23.665405919999998</v>
       </c>
       <c r="N12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-23.197651760000003</v>
+        <v>-21.621112320000002</v>
       </c>
       <c r="O12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-21.412094080000003</v>
+        <v>-19.559124400000002</v>
       </c>
       <c r="P12" s="1">
         <f t="shared" ca="1" si="1"/>
@@ -70340,47 +70336,47 @@
       </c>
       <c r="Q12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-19.62624418</v>
+        <v>-18.673513880000002</v>
       </c>
       <c r="R12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-18.499207880000004</v>
+        <v>-17.062376200000003</v>
       </c>
       <c r="S12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-16.834348839999997</v>
+        <v>-15.690266879999999</v>
       </c>
       <c r="T12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-15.89391648</v>
+        <v>-16.046742600000002</v>
       </c>
       <c r="U12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-13.813192280000001</v>
+        <v>-13.676428000000001</v>
       </c>
       <c r="V12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-8.6808339999999991</v>
+        <v>-8.2467922999999992</v>
       </c>
       <c r="W12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-9.6180044399999982</v>
+        <v>-9.7151559999999986</v>
       </c>
       <c r="X12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-10.372041479999998</v>
+        <v>-9.8585740799999986</v>
       </c>
       <c r="Y12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-10.4738735</v>
+        <v>-10.914878699999999</v>
       </c>
       <c r="Z12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-8.6717861999999997</v>
+        <v>-9.1097552000000004</v>
       </c>
       <c r="AA12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-9.586951599999999</v>
+        <v>-9.1215656000000003</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
@@ -70395,19 +70391,19 @@
       </c>
       <c r="D13" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>9.7525267199999988</v>
+        <v>9.6509378999999988</v>
       </c>
       <c r="E13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10.976987039999997</v>
+        <v>10.542254879999996</v>
       </c>
       <c r="F13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12.307736779999997</v>
+        <v>11.5765841</v>
       </c>
       <c r="G13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>13.374564360000001</v>
+        <v>12.718948460000002</v>
       </c>
       <c r="H13" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70419,75 +70415,75 @@
       </c>
       <c r="J13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.093420999999999</v>
+        <v>14.384006999999997</v>
       </c>
       <c r="K13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16.06827796</v>
+        <v>16.560164019999998</v>
       </c>
       <c r="L13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.769637100000002</v>
+        <v>14.267766900000002</v>
       </c>
       <c r="M13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16.966093319999999</v>
+        <v>16.794718639999999</v>
       </c>
       <c r="N13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>18.136026300000001</v>
+        <v>16.92695788</v>
       </c>
       <c r="O13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.521911679999999</v>
+        <v>16.168657999999997</v>
       </c>
       <c r="P13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.779937000000002</v>
+        <v>15.936174000000001</v>
       </c>
       <c r="Q13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.983221799999999</v>
+        <v>15.678779480000001</v>
       </c>
       <c r="R13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.693469120000005</v>
+        <v>14.836124160000004</v>
       </c>
       <c r="S13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12.858026940000002</v>
+        <v>12.728147880000002</v>
       </c>
       <c r="T13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>11.978245619999996</v>
+        <v>12.220230379999997</v>
       </c>
       <c r="U13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>11.03001072</v>
+        <v>10.597461279999999</v>
       </c>
       <c r="V13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8.8024476799999984</v>
+        <v>8.633169839999999</v>
       </c>
       <c r="W13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9.3788164799999993</v>
+        <v>9.8524940799999996</v>
       </c>
       <c r="X13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10.570068600000003</v>
+        <v>10.469401280000001</v>
       </c>
       <c r="Y13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10.626955360000002</v>
+        <v>11.386023600000001</v>
       </c>
       <c r="Z13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8.1003839999999983</v>
+        <v>8.6910369999999997</v>
       </c>
       <c r="AA13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9.0622856000000009</v>
+        <v>8.7033832000000011</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
@@ -70502,79 +70498,79 @@
       </c>
       <c r="D14" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>5.0512322700000007</v>
+        <v>4.7569857300000002</v>
       </c>
       <c r="E14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.7226128300000001</v>
+        <v>5.2197299700000004</v>
       </c>
       <c r="F14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.0658929919999993</v>
+        <v>4.2318478080000004</v>
       </c>
       <c r="G14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.3028585599999989</v>
+        <v>4.0898457599999993</v>
       </c>
       <c r="H14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3.3219271680000002</v>
+        <v>3.5592076800000001</v>
       </c>
       <c r="I14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2.8481951520000002</v>
+        <v>2.7618862080000004</v>
       </c>
       <c r="J14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3.3754727400000002</v>
+        <v>3.5531292000000003</v>
       </c>
       <c r="K14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.60441553599999998</v>
+        <v>0.56920686399999998</v>
       </c>
       <c r="L14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.53700080000000017</v>
+        <v>0.55343960000000014</v>
       </c>
       <c r="M14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.77550244199999985</v>
+        <v>0.81466923199999985</v>
       </c>
       <c r="N14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.47987205600000005</v>
+        <v>0.48928131200000002</v>
       </c>
       <c r="O14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.54764422000000001</v>
+        <v>0.60529097999999992</v>
       </c>
       <c r="P14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.90852159400000021</v>
+        <v>0.98345121000000024</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.7767829100000003</v>
+        <v>1.7064152700000002</v>
       </c>
       <c r="R14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.9147914239999999</v>
+        <v>1.8595570559999999</v>
       </c>
       <c r="S14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.8457739999999996</v>
+        <v>1.6699859999999997</v>
       </c>
       <c r="T14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.0156829999999999</v>
+        <v>0.96637799999999996</v>
       </c>
       <c r="U14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.9283327999999995</v>
+        <v>2.0689403999999998</v>
       </c>
       <c r="V14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.2624519600000002</v>
+        <v>1.2129440400000002</v>
       </c>
       <c r="W14" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70582,19 +70578,19 @@
       </c>
       <c r="X14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.2434572800000003</v>
+        <v>1.3743475200000004</v>
       </c>
       <c r="Y14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.81721971599999998</v>
+        <v>0.75374633999999996</v>
       </c>
       <c r="Z14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3.5414641500000004</v>
+        <v>3.6160212900000004</v>
       </c>
       <c r="AA14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.4956489760000009</v>
+        <v>4.3659667940000011</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.3">
@@ -70609,31 +70605,31 @@
       </c>
       <c r="D15" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-10.123200000000001</v>
+        <v>-9.7182720000000007</v>
       </c>
       <c r="E15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-11.041576703999999</v>
+        <v>-11.386625975999999</v>
       </c>
       <c r="F15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-13.323835272000004</v>
+        <v>-13.585086944000004</v>
       </c>
       <c r="G15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-13.402668286000001</v>
+        <v>-13.679011961999999</v>
       </c>
       <c r="H15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-16.121196000000001</v>
+        <v>-15.660590399999998</v>
       </c>
       <c r="I15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-17.426245200000004</v>
+        <v>-16.085764800000003</v>
       </c>
       <c r="J15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-15.18891255</v>
+        <v>-14.899599929999999</v>
       </c>
       <c r="K15" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70641,43 +70637,43 @@
       </c>
       <c r="L15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-15.158914171999996</v>
+        <v>-15.478049207199994</v>
       </c>
       <c r="M15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-24.375368097599996</v>
+        <v>-23.203475400599995</v>
       </c>
       <c r="N15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-20.326097780000005</v>
+        <v>-21.823810248000004</v>
       </c>
       <c r="O15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-20.160310118399998</v>
+        <v>-18.776759423999998</v>
       </c>
       <c r="P15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-20.531186029599997</v>
+        <v>-20.132522223199999</v>
       </c>
       <c r="Q15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-18.658270195200004</v>
+        <v>-19.435698120000001</v>
       </c>
       <c r="R15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-17.574247486000004</v>
+        <v>-18.869192037600001</v>
       </c>
       <c r="S15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-14.750485269999997</v>
+        <v>-16.303167929999997</v>
       </c>
       <c r="T15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-13.937742144</v>
+        <v>-14.5245944448</v>
       </c>
       <c r="U15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-13.675060357200003</v>
+        <v>-14.503851894000002</v>
       </c>
       <c r="V15" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70685,23 +70681,23 @@
       </c>
       <c r="W15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-9.4256443511999972</v>
+        <v>-9.6160614087999985</v>
       </c>
       <c r="X15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-10.243674629999997</v>
+        <v>-10.782815399999997</v>
       </c>
       <c r="Y15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-11.470545251999999</v>
+        <v>-11.245632599999999</v>
       </c>
       <c r="Z15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-9.1097552000000004</v>
+        <v>-9.474145408</v>
       </c>
       <c r="AA15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-9.4007971999999995</v>
+        <v>-9.5888131439999995</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
@@ -70720,23 +70716,23 @@
       </c>
       <c r="E16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>11.642127244799997</v>
+        <v>10.970466057599998</v>
       </c>
       <c r="F16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>11.698442879999998</v>
+        <v>11.942160439999999</v>
       </c>
       <c r="G16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12.965460038400002</v>
+        <v>12.8395817856</v>
       </c>
       <c r="H16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>13.666527935999998</v>
+        <v>14.663045597999997</v>
       </c>
       <c r="I16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.78575098</v>
+        <v>15.841876050000002</v>
       </c>
       <c r="J16" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70744,27 +70740,27 @@
       </c>
       <c r="K16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.740353920000002</v>
+        <v>15.110739763200002</v>
       </c>
       <c r="L16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.7786483212</v>
+        <v>16.088033582400001</v>
       </c>
       <c r="M16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>17.094624329999998</v>
+        <v>18.534171642</v>
       </c>
       <c r="N16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>17.434766616400001</v>
+        <v>18.3242955254</v>
       </c>
       <c r="O16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.846901705799999</v>
+        <v>15.6868319916</v>
       </c>
       <c r="P16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.467463</v>
+        <v>16.092411000000002</v>
       </c>
       <c r="Q16" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70772,27 +70768,27 @@
       </c>
       <c r="R16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.429569126400002</v>
+        <v>14.984485401600002</v>
       </c>
       <c r="S16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12.986607209400001</v>
+        <v>13.773674313000001</v>
       </c>
       <c r="T16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12.834871670399997</v>
+        <v>12.079879219199997</v>
       </c>
       <c r="U16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10.581240676</v>
+        <v>11.583674003199999</v>
       </c>
       <c r="V16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>7.9636759827999981</v>
+        <v>8.2920749923999981</v>
       </c>
       <c r="W16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9.5682875200000002</v>
+        <v>9.0898731440000002</v>
       </c>
       <c r="X16" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70800,15 +70796,15 @@
       </c>
       <c r="Y16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9.7865583800000007</v>
+        <v>10.301640400000002</v>
       </c>
       <c r="Z16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8.9509243200000004</v>
+        <v>8.3366451999999995</v>
       </c>
       <c r="AA16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8.7940060560000024</v>
+        <v>9.2381477760000017</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.3">
@@ -70823,99 +70819,99 @@
       </c>
       <c r="D17" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>4.5191364435000017</v>
+        <v>4.565725479000001</v>
       </c>
       <c r="E17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>5.2197299700000004</v>
+        <v>5.0705948279999999</v>
       </c>
       <c r="F17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.1048923737599994</v>
+        <v>4.401121720319999</v>
       </c>
       <c r="G17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.4749729023999985</v>
+        <v>4.5635862271999992</v>
       </c>
       <c r="H17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3.3537905510400003</v>
+        <v>3.5958166732800003</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2.8464689731199995</v>
+        <v>2.7906558559999994</v>
       </c>
       <c r="J17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3.8054013732000005</v>
+        <v>3.7307856600000004</v>
       </c>
       <c r="K17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.59150568959999994</v>
+        <v>0.60999024239999999</v>
       </c>
       <c r="L17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.53617886000000003</v>
+        <v>0.54659010000000008</v>
       </c>
       <c r="M17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.78325746641999971</v>
+        <v>0.73672731989999973</v>
       </c>
       <c r="N17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.46566407943999999</v>
+        <v>0.46091240515999998</v>
       </c>
       <c r="O17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.60563686055999999</v>
+        <v>0.56407354659999998</v>
       </c>
       <c r="P17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.99356670816000037</v>
+        <v>1.0227892584000002</v>
       </c>
       <c r="Q17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.7764310718000003</v>
+        <v>1.7938470627000001</v>
       </c>
       <c r="R17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.8945388223999999</v>
+        <v>1.9332028799999998</v>
       </c>
       <c r="S17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.8099132479999998</v>
+        <v>1.6532861399999998</v>
       </c>
       <c r="T17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.96489884999999986</v>
+        <v>0.98363474999999989</v>
       </c>
       <c r="U17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2.0488535999999997</v>
+        <v>1.9685063999999997</v>
       </c>
       <c r="V17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.2475995840000003</v>
+        <v>1.2995829000000003</v>
       </c>
       <c r="W17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.8789112446399997</v>
+        <v>0.89597748239999975</v>
       </c>
       <c r="X17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.2828552422399999</v>
+        <v>1.2698971084800001</v>
       </c>
       <c r="Y17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.79976453759999999</v>
+        <v>0.78453092736000007</v>
       </c>
       <c r="Z17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3.6831227159999997</v>
+        <v>3.8382015672000001</v>
       </c>
       <c r="AA17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.4934876062999995</v>
+        <v>4.5842651336999998</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.3">
@@ -70930,27 +70926,27 @@
       </c>
       <c r="D18" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-10.0017216</v>
+        <v>-9.7132103999999995</v>
       </c>
       <c r="E18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-10.708029074399999</v>
+        <v>-11.835190029599998</v>
       </c>
       <c r="F18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-12.417291970160001</v>
+        <v>-13.3042413966</v>
       </c>
       <c r="G18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-13.662431341440003</v>
+        <v>-12.866561554560002</v>
       </c>
       <c r="H18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-15.817196303999999</v>
+        <v>-15.972266855999999</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-16.923565050000001</v>
+        <v>-17.426245200000004</v>
       </c>
       <c r="J18" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70958,19 +70954,19 @@
       </c>
       <c r="K18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-17.236053298251999</v>
+        <v>-17.068712974967998</v>
       </c>
       <c r="L18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-14.858927238911996</v>
+        <v>-16.084405774079993</v>
       </c>
       <c r="M18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-23.435510154605996</v>
+        <v>-22.962065505017996</v>
       </c>
       <c r="N18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-22.690343890200005</v>
+        <v>-20.745457271040003</v>
       </c>
       <c r="O18" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70978,43 +70974,43 @@
       </c>
       <c r="P18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-20.333847445431999</v>
+        <v>-20.937823112127997</v>
       </c>
       <c r="Q18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-18.844852897151998</v>
+        <v>-18.6582701952</v>
       </c>
       <c r="R18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-18.452959860300005</v>
+        <v>-17.398505011140006</v>
       </c>
       <c r="S18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-16.154110394639996</v>
+        <v>-15.678989500679997</v>
       </c>
       <c r="T18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-16.021067811839998</v>
+        <v>-15.715904615423996</v>
       </c>
       <c r="U18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-13.943036287432001</v>
+        <v>-14.085312167916001</v>
       </c>
       <c r="V18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-8.9377866863999991</v>
+        <v>-8.2502646336000005</v>
       </c>
       <c r="W18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-8.9543621336399983</v>
+        <v>-9.0448102359999982</v>
       </c>
       <c r="X18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-11.328425859239999</v>
+        <v>-10.668517556759998</v>
       </c>
       <c r="Y18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-10.469683950599997</v>
+        <v>-10.897017989399997</v>
       </c>
       <c r="Z18" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -71022,7 +71018,7 @@
       </c>
       <c r="AA18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-9.4929250125599989</v>
+        <v>-9.5859929048399994</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.3">
@@ -71037,79 +71033,79 @@
       </c>
       <c r="D19" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>10.657225956509997</v>
+        <v>9.7437494459519982</v>
       </c>
       <c r="E19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>11.080170718175998</v>
+        <v>10.751056736447998</v>
       </c>
       <c r="F19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12.174910709799999</v>
+        <v>12.056707693199998</v>
       </c>
       <c r="G19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12.436771376639999</v>
+        <v>12.567684759551998</v>
       </c>
       <c r="H19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.499331982099996</v>
+        <v>14.200376683499996</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.081465999600001</v>
+        <v>14.4900359604</v>
       </c>
       <c r="J19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.785596851999999</v>
+        <v>15.07269582</v>
       </c>
       <c r="K19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.715169353728001</v>
+        <v>16.697367438336002</v>
       </c>
       <c r="L19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.84275790607</v>
+        <v>13.961009911650001</v>
       </c>
       <c r="M19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>18.705117885299998</v>
+        <v>19.460880224099995</v>
       </c>
       <c r="N19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>19.242289359488005</v>
+        <v>18.687223320272004</v>
       </c>
       <c r="O19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16.490381956883997</v>
+        <v>15.358689077489998</v>
       </c>
       <c r="P19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.779936999999997</v>
+        <v>14.990940149999998</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.44799529082</v>
+        <v>15.341685721179999</v>
       </c>
       <c r="R19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.834640547584002</v>
+        <v>15.583864817664002</v>
       </c>
       <c r="S19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12.983983652388002</v>
+        <v>13.116473281494002</v>
       </c>
       <c r="T19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>11.717482842623998</v>
+        <v>11.961597068511997</v>
       </c>
       <c r="U19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>11.247301931183999</v>
+        <v>11.474520152016</v>
       </c>
       <c r="V19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8.6253999871440001</v>
+        <v>8.3741747447999995</v>
       </c>
       <c r="W19" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -71121,7 +71117,7 @@
       </c>
       <c r="Y19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10.612749940080002</v>
+        <v>9.8844239638000015</v>
       </c>
       <c r="Z19" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -71129,7 +71125,7 @@
       </c>
       <c r="AA19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9.42291073152</v>
+        <v>8.6980714444800018</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.3">
@@ -71144,99 +71140,99 @@
       </c>
       <c r="D20" s="1">
         <f ca="1">D11*1.05*RANDBETWEEN(95,105)/100</f>
-        <v>4.5667063008000017</v>
+        <v>4.661846015400001</v>
       </c>
       <c r="E20" s="1">
         <f t="shared" ref="E20:AA28" ca="1" si="2">E11*1.05*RANDBETWEEN(95,105)/100</f>
-        <v>5.4285191688000012</v>
+        <v>5.3742947894999995</v>
       </c>
       <c r="F20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.6748693754000001</v>
+        <v>4.4470704599999999</v>
       </c>
       <c r="G20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.4311168439999991</v>
+        <v>3.9635742299999999</v>
       </c>
       <c r="H20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>3.4534886400000007</v>
+        <v>3.2815190016000009</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2.9550131520000007</v>
+        <v>3.1422437424000007</v>
       </c>
       <c r="J20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>3.7637043570000004</v>
+        <v>3.5127907332000001</v>
       </c>
       <c r="K20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.62758550400000002</v>
+        <v>0.6402896640000002</v>
       </c>
       <c r="L20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.57513456000000007</v>
+        <v>0.53089344000000005</v>
       </c>
       <c r="M20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.84693335999999986</v>
+        <v>0.82201397459999981</v>
       </c>
       <c r="N20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.44660165760000015</v>
+        <v>0.437393376</v>
       </c>
       <c r="O20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.62326992000000003</v>
+        <v>0.58071976199999997</v>
       </c>
       <c r="P20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.94334931600000038</v>
+        <v>0.96378218580000019</v>
       </c>
       <c r="Q20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.8300863972999999</v>
+        <v>1.7563762944000001</v>
       </c>
       <c r="R20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.8387950111999998</v>
+        <v>2.0692778399999998</v>
       </c>
       <c r="S20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.9201586921999996</v>
+        <v>1.8638625851999995</v>
       </c>
       <c r="T20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.0146968999999999</v>
+        <v>1.0768211999999999</v>
       </c>
       <c r="U20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2.1297833171999998</v>
+        <v>2.0253821741999998</v>
       </c>
       <c r="V20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.18819008</v>
+        <v>1.2125727306</v>
       </c>
       <c r="W20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.86047254719999988</v>
+        <v>0.94114184849999982</v>
       </c>
       <c r="X20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.4569405200000003</v>
+        <v>1.3479177600000001</v>
       </c>
       <c r="Y20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.80695196400000002</v>
+        <v>0.80842211940000008</v>
       </c>
       <c r="Z20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>3.7185373575000007</v>
+        <v>3.8382015672000009</v>
       </c>
       <c r="AA20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.7204314248000001</v>
+        <v>4.7671683695999993</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.3">
@@ -71251,75 +71247,75 @@
       </c>
       <c r="D21" s="1">
         <f t="shared" ref="D21:S28" ca="1" si="3">D12*1.05*RANDBETWEEN(95,105)/100</f>
-        <v>-10.729010250000004</v>
+        <v>-10.939383000000003</v>
       </c>
       <c r="E21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-12.560977493399998</v>
+        <v>-11.255033655599998</v>
       </c>
       <c r="F21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-13.982037300000004</v>
+        <v>-13.183063740000005</v>
       </c>
       <c r="G21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-14.055564421500003</v>
+        <v>-13.646179050000002</v>
       </c>
       <c r="H21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-15.041843544000001</v>
+        <v>-15.959984040000002</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-18.121619407500003</v>
+        <v>-17.417867197500005</v>
       </c>
       <c r="J21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-15.663765921300001</v>
+        <v>-16.794140781599999</v>
       </c>
       <c r="K21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-16.700895630719998</v>
+        <v>-17.217418175999999</v>
       </c>
       <c r="L21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-16.264964940839995</v>
+        <v>-17.079921179999996</v>
       </c>
       <c r="M21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-23.854729167360002</v>
+        <v>-25.842623264639997</v>
       </c>
       <c r="N21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-25.575411065400004</v>
+        <v>-23.837276332800002</v>
       </c>
       <c r="O21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-22.932352759680001</v>
+        <v>-19.715597395200003</v>
       </c>
       <c r="P21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-19.8833573442</v>
+        <v>-18.899032723200001</v>
       </c>
       <c r="Q21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-20.401480825110003</v>
+        <v>-20.195405261220003</v>
       </c>
       <c r="R21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-20.395376687700001</v>
+        <v>-17.915495010000004</v>
       </c>
       <c r="S21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-17.145784293539997</v>
+        <v>-16.969023630720002</v>
       </c>
       <c r="T21" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-16.855498427040001</v>
+        <v>-17.017570527300006</v>
       </c>
       <c r="U21" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-14.938967450820003</v>
+        <v>-14.073044412000002</v>
       </c>
       <c r="V21" s="1">
         <f t="shared" ca="1" si="2"/>
@@ -71327,23 +71323,23 @@
       </c>
       <c r="W21" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-9.8969265687599997</v>
+        <v>-10.302922938</v>
       </c>
       <c r="X21" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-10.781737118459999</v>
+        <v>-9.8339276447999993</v>
       </c>
       <c r="Y21" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-11.32749419025</v>
+        <v>-12.033653766750001</v>
       </c>
       <c r="Z21" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-8.8322142446999994</v>
+        <v>-9.0869808120000002</v>
       </c>
       <c r="AA21" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-9.6636472127999991</v>
+        <v>-9.5776438800000001</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.3">
@@ -71358,99 +71354,99 @@
       </c>
       <c r="D22" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>9.8305469337599991</v>
+        <v>10.640159034749999</v>
       </c>
       <c r="E22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>11.525836391999997</v>
+        <v>11.401448652719996</v>
       </c>
       <c r="F22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>13.052354855189998</v>
+        <v>11.54764263975</v>
       </c>
       <c r="G22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>14.324158429560001</v>
+        <v>13.087797965340004</v>
       </c>
       <c r="H22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>14.072881041449998</v>
+        <v>14.357181668549996</v>
       </c>
       <c r="I22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.822673776000002</v>
+        <v>16.976410405500001</v>
       </c>
       <c r="J22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.2420348115</v>
+        <v>15.858367717499998</v>
       </c>
       <c r="K22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16.028107265100001</v>
+        <v>17.040408776579998</v>
       </c>
       <c r="L22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>17.220443713200005</v>
+        <v>15.280778349900002</v>
       </c>
       <c r="M22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16.923678086700001</v>
+        <v>17.987143663439998</v>
       </c>
       <c r="N22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>19.614112443450001</v>
+        <v>17.417839658520002</v>
       </c>
       <c r="O22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.809067046079999</v>
+        <v>17.656174535999995</v>
       </c>
       <c r="P22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16.237555173000004</v>
+        <v>17.234972181</v>
       </c>
       <c r="Q22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16.782382890000001</v>
+        <v>16.462718454000001</v>
       </c>
       <c r="R22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>14.965298298720006</v>
+        <v>16.045268279040005</v>
       </c>
       <c r="S22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>13.230909721260002</v>
+        <v>13.364555274000002</v>
       </c>
       <c r="T22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>13.206015796049996</v>
+        <v>13.087866736979997</v>
       </c>
       <c r="U22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>11.002435693200001</v>
+        <v>11.683701061199999</v>
       </c>
       <c r="V22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>9.3349957646399986</v>
+        <v>9.3367731819599999</v>
       </c>
       <c r="W22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>10.143190023119999</v>
+        <v>10.655472347520002</v>
       </c>
       <c r="X22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>11.098572030000003</v>
+        <v>10.992871344000003</v>
       </c>
       <c r="Y22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>11.381469190560001</v>
+        <v>12.194431275600003</v>
       </c>
       <c r="Z22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>8.1651870719999984</v>
+        <v>8.8518211845000003</v>
       </c>
       <c r="AA22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>9.4202458812000014</v>
+        <v>8.7730102656000017</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.3">
@@ -71465,79 +71461,79 @@
       </c>
       <c r="D23" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>5.1977180058300005</v>
+        <v>4.7450932656750009</v>
       </c>
       <c r="E23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>5.2066806450750001</v>
+        <v>5.5355236331850008</v>
       </c>
       <c r="F23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.3972632708479997</v>
+        <v>4.6211778063360001</v>
       </c>
       <c r="G23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.698721547519999</v>
+        <v>4.4661115699199989</v>
       </c>
       <c r="H23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>3.4880235264000006</v>
+        <v>3.6997963833600007</v>
       </c>
       <c r="I23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2.9008867623120005</v>
+        <v>2.8999805184000009</v>
       </c>
       <c r="J23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>3.72145869585</v>
+        <v>3.8427092298000001</v>
       </c>
       <c r="K23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.63463631279999999</v>
+        <v>0.62755056756000005</v>
       </c>
       <c r="L23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.54693531480000024</v>
+        <v>0.60435604320000014</v>
       </c>
       <c r="M23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.78170646153599987</v>
+        <v>0.88106477440799991</v>
       </c>
       <c r="N23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.51394297197600014</v>
+        <v>0.53429519270400005</v>
       </c>
       <c r="O23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.58077669531000009</v>
+        <v>0.65462219486999984</v>
       </c>
       <c r="P23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.9348687202260002</v>
+        <v>0.99131881968000035</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.9589031582750005</v>
+        <v>1.8275707541700004</v>
       </c>
       <c r="R23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2.0909522350079999</v>
+        <v>1.8939588615360001</v>
       </c>
       <c r="S23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.9768239539999997</v>
+        <v>1.6833458880000001</v>
       </c>
       <c r="T23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.023808464</v>
+        <v>1.0552847759999999</v>
       </c>
       <c r="U23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2.0652444287999994</v>
+        <v>2.0854919231999998</v>
       </c>
       <c r="V23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.3918532859000001</v>
+        <v>1.2353835047400001</v>
       </c>
       <c r="W23" s="1">
         <f t="shared" ca="1" si="2"/>
@@ -71545,19 +71541,19 @@
       </c>
       <c r="X23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.2795175411200004</v>
+        <v>1.4863568428800005</v>
       </c>
       <c r="Y23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.81517666671</v>
+        <v>0.79143365700000001</v>
       </c>
       <c r="Z23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>3.7185373575000007</v>
+        <v>3.6069812367750007</v>
       </c>
       <c r="AA23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.8148400532960007</v>
+        <v>4.7217930877110019</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.3">
@@ -71572,99 +71568,99 @@
       </c>
       <c r="D24" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-10.4167728</v>
+        <v>-10.408269312</v>
       </c>
       <c r="E24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-11.129909317631999</v>
+        <v>-12.195076420295999</v>
       </c>
       <c r="F24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-14.549628117024003</v>
+        <v>-13.979054465376004</v>
       </c>
       <c r="G24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-13.650617649291</v>
+        <v>-14.219332934499</v>
       </c>
       <c r="H24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-17.604346032000002</v>
+        <v>-16.279183720799999</v>
       </c>
       <c r="I24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-18.114581885400003</v>
+        <v>-17.396754631200007</v>
       </c>
       <c r="J24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-15.469907432175001</v>
+        <v>-15.801025725765001</v>
       </c>
       <c r="K24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-18.2735633026128</v>
+        <v>-17.896788801528</v>
       </c>
       <c r="L24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-16.553534275823996</v>
+        <v>-16.089432150884392</v>
       </c>
       <c r="M24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-25.850077867504798</v>
+        <v>-23.145466712098496</v>
       </c>
       <c r="N24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-21.555826695690008</v>
+        <v>-22.227550737588004</v>
       </c>
       <c r="O24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-21.168325624319994</v>
+        <v>-20.307065317056001</v>
       </c>
       <c r="P24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-20.911012971147599</v>
+        <v>-21.139148334359998</v>
       </c>
       <c r="Q24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-19.787095542009606</v>
+        <v>-20.407483026000001</v>
       </c>
       <c r="R24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-18.268430261697006</v>
+        <v>-19.020145573900802</v>
       </c>
       <c r="S24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-14.713609056824998</v>
+        <v>-17.631876116294997</v>
       </c>
       <c r="T24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-15.220014421247999</v>
+        <v>-14.6407912003584</v>
       </c>
       <c r="U24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-14.215225241309405</v>
+        <v>-15.076754043813002</v>
       </c>
       <c r="V24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-8.6654849833629015</v>
+        <v>-9.2014943637771012</v>
       </c>
       <c r="W24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-9.5010495060095987</v>
+        <v>-9.8949271896551991</v>
       </c>
       <c r="X24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-10.648299777884997</v>
+        <v>-10.755858361499998</v>
       </c>
       <c r="Y24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-12.405394690037999</v>
+        <v>-12.0440725146</v>
       </c>
       <c r="Z24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-9.0869808120000002</v>
+        <v>-9.7488956248320005</v>
       </c>
       <c r="AA24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-9.8708370599999995</v>
+        <v>-9.5648411111399998</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.3">
@@ -71679,67 +71675,67 @@
       </c>
       <c r="D25" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>10.646239125626998</v>
+        <v>11.6548302006864</v>
       </c>
       <c r="E25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>11.613021926687997</v>
+        <v>11.749369147689597</v>
       </c>
       <c r="F25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>11.914864073279999</v>
+        <v>12.915446515859999</v>
       </c>
       <c r="G25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>12.933046388304001</v>
+        <v>13.886007701126402</v>
       </c>
       <c r="H25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>14.636851419455997</v>
+        <v>15.704121835457997</v>
       </c>
       <c r="I25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16.301290455450001</v>
+        <v>17.132988948075003</v>
       </c>
       <c r="J25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>14.921968861799998</v>
+        <v>15.07269582</v>
       </c>
       <c r="K25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16.527371616000003</v>
+        <v>15.231625681305601</v>
       </c>
       <c r="L25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.739201700397002</v>
+        <v>16.554586556289603</v>
       </c>
       <c r="M25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>17.410874880104998</v>
+        <v>20.044706630823001</v>
       </c>
       <c r="N25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>18.855700095636603</v>
+        <v>20.0101307137368</v>
       </c>
       <c r="O25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16.3064618552682</v>
+        <v>17.294732270739001</v>
       </c>
       <c r="P25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16.403244511499999</v>
+        <v>16.897031550000001</v>
       </c>
       <c r="Q25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.305533195680001</v>
+        <v>14.139397333152001</v>
       </c>
       <c r="R25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16.525068534374405</v>
+        <v>16.363058058547203</v>
       </c>
       <c r="S25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>13.226859442773902</v>
+        <v>14.8962287695095</v>
       </c>
       <c r="T25" s="1">
         <f t="shared" ca="1" si="2"/>
@@ -71747,31 +71743,31 @@
       </c>
       <c r="U25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>10.665890601408</v>
+        <v>11.919600549292797</v>
       </c>
       <c r="V25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>8.1110039884817979</v>
+        <v>9.0549458917007968</v>
       </c>
       <c r="W25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>10.046701896</v>
+        <v>9.7352541372240005</v>
       </c>
       <c r="X25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>10.889284671720004</v>
+        <v>11.320543470600002</v>
       </c>
       <c r="Y25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>10.686921750960003</v>
+        <v>11.033056868400003</v>
       </c>
       <c r="Z25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>9.4924552413600001</v>
+        <v>9.1911513329999988</v>
       </c>
       <c r="AA25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>8.9566951680360027</v>
+        <v>9.6030546131520023</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.3">
@@ -71786,99 +71782,99 @@
       </c>
       <c r="D26" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>4.8874460636452515</v>
+        <v>4.9378321055385017</v>
       </c>
       <c r="E26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>5.2066806450750001</v>
+        <v>5.0579183409300006</v>
       </c>
       <c r="F26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.2239342525990393</v>
+        <v>4.5749660282726392</v>
       </c>
       <c r="G26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.4637854701439981</v>
+        <v>4.6000949170175991</v>
       </c>
       <c r="H26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>3.5566948793779205</v>
+        <v>3.5868271315968001</v>
       </c>
       <c r="I26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2.8393528006872</v>
+        <v>2.8422829893360002</v>
       </c>
       <c r="J26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.1554982995344005</v>
+        <v>3.8389784441400008</v>
       </c>
       <c r="K26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.59623773511680001</v>
+        <v>0.64048975452000012</v>
       </c>
       <c r="L26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.57987743709000006</v>
+        <v>0.59687638920000008</v>
       </c>
       <c r="M26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.7977477295487696</v>
+        <v>0.79677059647184978</v>
       </c>
       <c r="N26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.47916833774376</v>
+        <v>0.50815592668889997</v>
       </c>
       <c r="O26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.6549962646956401</v>
+        <v>0.59819999616930009</v>
       </c>
       <c r="P26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.0119476922609605</v>
+        <v>1.0524501468936003</v>
       </c>
       <c r="Q26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.9398627304056004</v>
+        <v>1.8081978392016</v>
       </c>
       <c r="R26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.8898024753440001</v>
+        <v>1.9486685030399999</v>
       </c>
       <c r="S26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.824392553984</v>
+        <v>1.66651242912</v>
       </c>
       <c r="T26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.98274947872499996</v>
+        <v>1.0224883226249999</v>
       </c>
       <c r="U26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2.2158351683999999</v>
+        <v>2.1496089887999998</v>
       </c>
       <c r="V26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.3361791544640005</v>
+        <v>1.2963339427500002</v>
       </c>
       <c r="W26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.93208537494071975</v>
+        <v>0.9407763565199998</v>
       </c>
       <c r="X26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.3604679843955199</v>
+        <v>1.4000615620992003</v>
       </c>
       <c r="Y26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.83975276448000002</v>
+        <v>0.84023262320256009</v>
       </c>
       <c r="Z26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>3.9832972173540004</v>
+        <v>4.1107138784711994</v>
       </c>
       <c r="AA26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.8125252263473</v>
+        <v>5.0060175260003996</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.3">
@@ -71893,99 +71889,99 @@
       </c>
       <c r="D27" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-10.606825756800001</v>
+        <v>-9.6889273739999986</v>
       </c>
       <c r="E27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-11.355864833401199</v>
+        <v>-11.805602054525998</v>
       </c>
       <c r="F27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-13.690064397101402</v>
+        <v>-14.667926139751501</v>
       </c>
       <c r="G27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-15.062830553937603</v>
+        <v>-13.239691839642241</v>
       </c>
       <c r="H27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-16.940217241584001</v>
+        <v>-17.609424208740002</v>
       </c>
       <c r="I27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-17.947440735524999</v>
+        <v>-17.565655161600002</v>
       </c>
       <c r="J27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-15.031008615130201</v>
+        <v>-15.638322094529402</v>
       </c>
       <c r="K27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-17.192963165006372</v>
+        <v>-17.026041192530577</v>
       </c>
       <c r="L27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-16.069929808883323</v>
+        <v>-16.888626062783995</v>
       </c>
       <c r="M27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-24.115139949089571</v>
+        <v>-24.110168780268896</v>
       </c>
       <c r="N27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-22.633618030474505</v>
+        <v>-21.564902833246084</v>
       </c>
       <c r="O27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-18.359164294410242</v>
+        <v>-19.889094652277763</v>
       </c>
       <c r="P27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-20.496518224995452</v>
+        <v>-21.325172839702365</v>
       </c>
       <c r="Q27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-19.984966497429696</v>
+        <v>-19.003448193811202</v>
       </c>
       <c r="R27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-18.406827460649257</v>
+        <v>-17.720377353846096</v>
       </c>
       <c r="S27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-17.640288550946874</v>
+        <v>-16.627568365471134</v>
       </c>
       <c r="T27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-17.158563626480639</v>
+        <v>-15.676614853885438</v>
       </c>
       <c r="U27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-14.054580577731459</v>
+        <v>-15.233265109601156</v>
       </c>
       <c r="V27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-8.9154422196839995</v>
+        <v>-9.0092889798912008</v>
       </c>
       <c r="W27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-9.778163449934878</v>
+        <v>-9.9719032851899971</v>
       </c>
       <c r="X27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-11.41905326611392</v>
+        <v>-11.538001737635939</v>
       </c>
       <c r="Y27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-11.432894874055199</v>
+        <v>-11.098612822203897</v>
       </c>
       <c r="Z27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-10.027435499827201</v>
+        <v>-9.2634404141260802</v>
       </c>
       <c r="AA27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-10.166922688451759</v>
+        <v>-9.6626808480787183</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.3">
@@ -72000,99 +71996,99 @@
       </c>
       <c r="D28" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>10.854384636705431</v>
+        <v>9.9240088107021105</v>
       </c>
       <c r="E28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>11.51783746154395</v>
+        <v>11.740153956201214</v>
       </c>
       <c r="F28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>13.1671659326487</v>
+        <v>13.165924800974398</v>
       </c>
       <c r="G28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>12.928023846017279</v>
+        <v>13.591951067455486</v>
       </c>
       <c r="H28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>14.463083652144746</v>
+        <v>14.164875741791247</v>
       </c>
       <c r="I28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.518828513588401</v>
+        <v>15.670973891172601</v>
       </c>
       <c r="J28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.369627927653999</v>
+        <v>16.459383835440001</v>
       </c>
       <c r="K28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16.005899986771968</v>
+        <v>16.655624019740163</v>
       </c>
       <c r="L28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16.052442675414703</v>
+        <v>15.098832219449475</v>
       </c>
       <c r="M28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>19.836777517360648</v>
+        <v>20.842602720011097</v>
       </c>
       <c r="N28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>20.002359789187782</v>
+        <v>20.014016176011317</v>
       </c>
       <c r="O28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16.449156001991788</v>
+        <v>15.804091060737207</v>
       </c>
       <c r="P28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16.403244511499999</v>
+        <v>15.897892029074999</v>
       </c>
       <c r="Q28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.928914808129051</v>
+        <v>15.62550690702183</v>
       </c>
       <c r="R28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>14.797553946215041</v>
+        <v>17.181210961474562</v>
       </c>
       <c r="S28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>14.042178320057623</v>
+        <v>14.460911792847138</v>
       </c>
       <c r="T28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>11.934256275212542</v>
+        <v>13.187660768034478</v>
       </c>
       <c r="U28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>12.163957038575496</v>
+        <v>11.686798774828297</v>
       </c>
       <c r="V28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>9.5095034858262597</v>
+        <v>8.9687411516808009</v>
       </c>
       <c r="W28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>9.8418295509367688</v>
+        <v>9.6488525009183999</v>
       </c>
       <c r="X28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>9.9290996400960037</v>
+        <v>10.660717508313603</v>
       </c>
       <c r="Y28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>11.477689060196523</v>
+        <v>10.586218065229803</v>
       </c>
       <c r="Z28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>8.9341860915216031</v>
+        <v>8.8420810802688017</v>
       </c>
       <c r="AA28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>9.5972345800531187</v>
+        <v>8.8589857662028813</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.3">
@@ -72107,99 +72103,99 @@
       </c>
       <c r="D29" s="1">
         <f ca="1">D20*0.95*RANDBETWEEN(95,105)/100</f>
-        <v>4.4685221153328012</v>
+        <v>4.5616163260689007</v>
       </c>
       <c r="E29" s="1">
         <f t="shared" ref="E29:AA37" ca="1" si="4">E20*0.95*RANDBETWEEN(95,105)/100</f>
-        <v>5.1570932103600011</v>
+        <v>5.2587474515257489</v>
       </c>
       <c r="F29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.5299484247625994</v>
+        <v>4.01348109015</v>
       </c>
       <c r="G29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.2095610017999991</v>
+        <v>3.9160113392399993</v>
       </c>
       <c r="H29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>3.3464304921600005</v>
+        <v>3.0862686210048009</v>
       </c>
       <c r="I29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>2.947625619120001</v>
+        <v>3.0746855019384007</v>
       </c>
       <c r="J29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>3.3967431821925005</v>
+        <v>3.4706372444015998</v>
       </c>
       <c r="K29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.60216829108799996</v>
+        <v>0.57786142176000022</v>
       </c>
       <c r="L29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.55184161032000001</v>
+        <v>0.49930528032000004</v>
       </c>
       <c r="M29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.82067842583999995</v>
+        <v>0.78872240862869991</v>
       </c>
       <c r="N29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.41154342747840011</v>
+        <v>0.41136847012799999</v>
       </c>
       <c r="O29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.59802748824000007</v>
+        <v>0.57926796259499991</v>
       </c>
       <c r="P29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.88722003169800034</v>
+        <v>0.94306086880530016</v>
       </c>
       <c r="Q29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.6516529735632497</v>
+        <v>1.66855747968</v>
       </c>
       <c r="R29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.7293867080335996</v>
+        <v>1.9068395295599996</v>
       </c>
       <c r="S29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.8423922651658995</v>
+        <v>1.8237895396181996</v>
       </c>
       <c r="T29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.94468281389999986</v>
+        <v>0.9718311329999999</v>
       </c>
       <c r="U29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>2.1244588589069995</v>
+        <v>1.9625953267997998</v>
       </c>
       <c r="V29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.1400683817599999</v>
+        <v>1.1173857712479001</v>
       </c>
       <c r="W29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.80927443064159987</v>
+        <v>0.92984814631799972</v>
       </c>
       <c r="X29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.3287297542400003</v>
+        <v>1.22930099712</v>
       </c>
       <c r="Y29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.72827414751000008</v>
+        <v>0.73728097289280004</v>
       </c>
       <c r="Z29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>3.4266321749362505</v>
+        <v>3.7556802335052009</v>
       </c>
       <c r="AA29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.5292539520956003</v>
+        <v>4.4835218516088</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.3">
@@ -72214,99 +72210,99 @@
       </c>
       <c r="D30" s="1">
         <f t="shared" ref="D30:S37" ca="1" si="5">D21*0.95*RANDBETWEEN(95,105)/100</f>
-        <v>-10.090634140125003</v>
+        <v>-10.704186265500002</v>
       </c>
       <c r="E30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-12.052257904917296</v>
+        <v>-10.585359153091799</v>
       </c>
       <c r="F30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-12.618788663250003</v>
+        <v>-12.774388764060005</v>
       </c>
       <c r="G30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-13.219258338420753</v>
+        <v>-13.352786200425001</v>
       </c>
       <c r="H30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-14.718443907803998</v>
+        <v>-15.61684438314</v>
       </c>
       <c r="I30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-17.043383052753754</v>
+        <v>-15.885094884120003</v>
       </c>
       <c r="J30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-14.731771848982651</v>
+        <v>-15.4758007302444</v>
       </c>
       <c r="K30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-15.231216815216637</v>
+        <v>-17.010809157888001</v>
       </c>
       <c r="L30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-15.142682359922034</v>
+        <v>-16.388184372209995</v>
       </c>
       <c r="M30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-22.435372781902082</v>
+        <v>-25.041501943436156</v>
       </c>
       <c r="N30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-25.268506132615201</v>
+        <v>-22.192504265836803</v>
       </c>
       <c r="O30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-21.785735121695996</v>
+        <v>-18.917115700694399</v>
       </c>
       <c r="P30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-18.511405687450196</v>
+        <v>-17.4154586544288</v>
       </c>
       <c r="Q30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-19.962848987370137</v>
+        <v>-18.993778648177411</v>
       </c>
       <c r="R30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-19.375607853315</v>
+        <v>-17.360114664690006</v>
       </c>
       <c r="S30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-15.474070324919847</v>
+        <v>-16.604189622659522</v>
       </c>
       <c r="T30" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-15.372214565460482</v>
+        <v>-16.813359680972404</v>
       </c>
       <c r="U30" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-14.475859459844582</v>
+        <v>-12.70092258183</v>
       </c>
       <c r="V30" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-8.2261753192499985</v>
+        <v>-7.8148665532874988</v>
       </c>
       <c r="W30" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-9.0259970307091173</v>
+        <v>-10.081410094832998</v>
       </c>
       <c r="X30" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-10.037797257286257</v>
+        <v>-9.8093428256879989</v>
       </c>
       <c r="Y30" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-10.97634187035225</v>
+        <v>-11.889249921549002</v>
       </c>
       <c r="Z30" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-8.5584156031142999</v>
+        <v>-8.2010001828299988</v>
       </c>
       <c r="AA30" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-9.6394880947679979</v>
+        <v>-9.3717245365800004</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.3">
@@ -72321,99 +72317,99 @@
       </c>
       <c r="D31" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>9.2456293912012786</v>
+        <v>9.7038250396919992</v>
       </c>
       <c r="E31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>10.730553680951997</v>
+        <v>11.264631268887356</v>
       </c>
       <c r="F31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>11.779750256808972</v>
+        <v>10.75085529760725</v>
       </c>
       <c r="G31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>13.063632487758721</v>
+        <v>11.811737663719352</v>
       </c>
       <c r="H31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>12.700775139908624</v>
+        <v>14.04850226267617</v>
       </c>
       <c r="I31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>15.181855488072001</v>
+        <v>16.127589885224999</v>
       </c>
       <c r="J31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>14.1903344095065</v>
+        <v>14.312176865043748</v>
       </c>
       <c r="K31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>14.922167863808102</v>
+        <v>15.864620570995976</v>
       </c>
       <c r="L31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>16.686609958090802</v>
+        <v>14.807074221053101</v>
       </c>
       <c r="M31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>15.273619473246752</v>
+        <v>17.942175804281398</v>
       </c>
       <c r="N31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>18.447072753064724</v>
+        <v>16.050539245326181</v>
       </c>
       <c r="O31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>14.568055282962719</v>
+        <v>15.934697518739995</v>
       </c>
       <c r="P31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>16.042704510924004</v>
+        <v>15.882026864791499</v>
       </c>
       <c r="Q31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>15.146100558225001</v>
+        <v>16.421561657864999</v>
       </c>
       <c r="R31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>14.643544385297526</v>
+        <v>14.480854621833602</v>
       </c>
       <c r="S31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>12.946445162252912</v>
+        <v>13.204180610712001</v>
       </c>
       <c r="T31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>12.294800706122546</v>
+        <v>12.682142868133617</v>
       </c>
       <c r="U31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>9.9296982131130012</v>
+        <v>10.877525687977197</v>
       </c>
       <c r="V31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>9.1342933557002386</v>
+        <v>9.0473332133192397</v>
       </c>
       <c r="W31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>9.7323908271836395</v>
+        <v>9.8190177682396822</v>
       </c>
       <c r="X31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>10.016461257075003</v>
+        <v>10.547660054568002</v>
       </c>
       <c r="Y31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>10.488023859101041</v>
+        <v>12.048098100292803</v>
       </c>
       <c r="Z31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>7.4466506096639975</v>
+        <v>7.9887686190112506</v>
       </c>
       <c r="AA31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>8.6807565795258004</v>
+        <v>8.2510161547968011</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.3">
@@ -72428,99 +72424,99 @@
       </c>
       <c r="D32" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>4.8390754634277302</v>
+        <v>4.6430737604629879</v>
       </c>
       <c r="E32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.9463466128212499</v>
+        <v>5.3639224005562651</v>
       </c>
       <c r="F32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.2191741083786551</v>
+        <v>4.2145141593784317</v>
       </c>
       <c r="G32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.3298719060396795</v>
+        <v>4.2428059914239986</v>
       </c>
       <c r="H32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>3.1479412325760006</v>
+        <v>3.5499546298339202</v>
       </c>
       <c r="I32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>2.8660761211642565</v>
+        <v>2.7825313074048008</v>
       </c>
       <c r="J32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>3.4646780458363495</v>
+        <v>3.4680450798944999</v>
       </c>
       <c r="K32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.60290449715999994</v>
+        <v>0.60809649996564008</v>
       </c>
       <c r="L32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.50919677807880026</v>
+        <v>0.5683968586296001</v>
       </c>
       <c r="M32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.76489977261297581</v>
+        <v>0.87049199711510383</v>
       </c>
       <c r="N32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.51265811454606014</v>
+        <v>0.48220141141536005</v>
       </c>
       <c r="O32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.52966834612272007</v>
+        <v>0.6405478176802949</v>
       </c>
       <c r="P32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.89700653705684719</v>
+        <v>0.95117040748296033</v>
       </c>
       <c r="Q32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.8981771603684754</v>
+        <v>1.684106449967655</v>
       </c>
       <c r="R32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>2.0459967619553279</v>
+        <v>1.70929787253624</v>
       </c>
       <c r="S32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.8404231011739995</v>
+        <v>1.51921966392</v>
       </c>
       <c r="T32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.93371331916800004</v>
+        <v>1.0225709479439999</v>
       </c>
       <c r="U32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.9227425632127992</v>
+        <v>1.8821564606879997</v>
       </c>
       <c r="V32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.30903801538895</v>
+        <v>1.1853504727980302</v>
       </c>
       <c r="W32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.80078883466982376</v>
+        <v>0.8412327152087038</v>
       </c>
       <c r="X32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.2520079139859202</v>
+        <v>1.3979186107286403</v>
       </c>
       <c r="Y32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.78990619004199003</v>
+        <v>0.78193645311599991</v>
       </c>
       <c r="Z32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>3.6032626994175008</v>
+        <v>3.3580995314375253</v>
       </c>
       <c r="AA32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.4368751091122647</v>
+        <v>4.6202745363252156</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.3">
@@ -72535,99 +72531,99 @@
       </c>
       <c r="D33" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-10.2917715264</v>
+        <v>-9.4923416125439992</v>
       </c>
       <c r="E33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-11.102084544337918</v>
+        <v>-11.932882277259635</v>
       </c>
       <c r="F33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-13.26926084272589</v>
+        <v>-13.147300724686131</v>
       </c>
       <c r="G33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-13.357129369831243</v>
+        <v>-13.778533613529532</v>
       </c>
       <c r="H33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-16.222404868487999</v>
+        <v>-16.083833516150399</v>
       </c>
       <c r="I33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-17.553029846952601</v>
+        <v>-16.361647730643607</v>
       </c>
       <c r="J33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-14.990340301777573</v>
+        <v>-15.010974439476751</v>
       </c>
       <c r="K33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-17.880681691606625</v>
+        <v>-17.512007842295148</v>
       </c>
       <c r="L33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-15.883116137653124</v>
+        <v>-14.673562121606565</v>
       </c>
       <c r="M33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-25.785452672836037</v>
+        <v>-20.888783707668889</v>
       </c>
       <c r="N33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-19.863694300078343</v>
+        <v>-21.116173200708598</v>
       </c>
       <c r="O33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-21.115404810259193</v>
+        <v>-19.870463412739294</v>
       </c>
       <c r="P33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-20.064116945816121</v>
+        <v>-19.88136900846558</v>
       </c>
       <c r="Q33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-18.045831134312763</v>
+        <v>-20.356464318435002</v>
       </c>
       <c r="R33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-18.049209098556638</v>
+        <v>-18.972595209966048</v>
       </c>
       <c r="S33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-13.418811459824397</v>
+        <v>-17.587796426004257</v>
       </c>
       <c r="T33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-15.181964385194879</v>
+        <v>-13.35240157472686</v>
       </c>
       <c r="U33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-12.964285420074175</v>
+        <v>-14.036458014789906</v>
       </c>
       <c r="V33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-8.3968549488786515</v>
+        <v>-9.0910764314117767</v>
       </c>
       <c r="W33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-9.2065169713233015</v>
+        <v>-9.4941826384741628</v>
       </c>
       <c r="X33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-9.8124082453210235</v>
+        <v>-10.524607406727748</v>
       </c>
       <c r="Y33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-11.313719957314657</v>
+        <v>-11.441868888869999</v>
       </c>
       <c r="Z33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-8.5463054536859993</v>
+        <v>-9.0762218267185908</v>
       </c>
       <c r="AA33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-9.2835222549300003</v>
+        <v>-9.5409290083621485</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.3">
@@ -72642,99 +72638,99 @@
       </c>
       <c r="D34" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>10.518484256119473</v>
+        <v>11.072088690652079</v>
       </c>
       <c r="E34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>11.473665663567742</v>
+        <v>11.161900690305117</v>
       </c>
       <c r="F34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>11.432312078312158</v>
+        <v>12.88315789957035</v>
       </c>
       <c r="G34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>12.286394068888802</v>
+        <v>12.664039023427279</v>
       </c>
       <c r="H34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>13.487858583028702</v>
+        <v>15.66486153086935</v>
       </c>
       <c r="I34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>15.021639154697175</v>
+        <v>15.788049315651115</v>
       </c>
       <c r="J34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>14.742905235458398</v>
+        <v>13.603107977549998</v>
       </c>
       <c r="K34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>15.072962913792002</v>
+        <v>15.193546617102335</v>
       </c>
       <c r="L34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>14.354151950762066</v>
+        <v>14.940514367051367</v>
       </c>
       <c r="M34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>17.036541070182739</v>
+        <v>19.04247129928185</v>
       </c>
       <c r="N34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>17.733785939946223</v>
+        <v>18.819527936269459</v>
       </c>
       <c r="O34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>15.181315987254694</v>
+        <v>15.937095787485987</v>
       </c>
       <c r="P34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>16.050574754502748</v>
+        <v>15.891658172774999</v>
       </c>
       <c r="Q34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>14.10404883981912</v>
+        <v>13.70107601582429</v>
       </c>
       <c r="R34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>14.9138743522729</v>
+        <v>16.322150413400834</v>
       </c>
       <c r="S34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>13.068137129460615</v>
+        <v>13.585360637792665</v>
       </c>
       <c r="T34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>12.905206767153789</v>
+        <v>11.921952918227786</v>
       </c>
       <c r="U34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>10.537899914191105</v>
+        <v>10.757439495736749</v>
       </c>
       <c r="V34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>7.4742901753859758</v>
+        <v>8.5161766111445996</v>
       </c>
       <c r="W34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>9.9261414732479984</v>
+        <v>9.7109160018809391</v>
       </c>
       <c r="X34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>10.862061460040705</v>
+        <v>11.292242111923501</v>
       </c>
       <c r="Y34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>9.6449468802414025</v>
+        <v>11.005474226229001</v>
       </c>
       <c r="Z34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>8.6571191801203202</v>
+        <v>8.8189097040134978</v>
       </c>
       <c r="AA34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>8.0834173891524923</v>
+        <v>9.0316728636694581</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.3">
@@ -72749,99 +72745,99 @@
       </c>
       <c r="D35" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>4.410920072439839</v>
+        <v>4.6909405002615765</v>
       </c>
       <c r="E35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>5.0947370112058872</v>
+        <v>4.70892197540583</v>
       </c>
       <c r="F35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>3.932482789169705</v>
+        <v>4.5635286132019575</v>
       </c>
       <c r="G35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.0709723487713259</v>
+        <v>4.1952865643200505</v>
       </c>
       <c r="H35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>3.2774943313467535</v>
+        <v>3.5437852060176378</v>
       </c>
       <c r="I35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>2.6164636058332547</v>
+        <v>2.56516039787574</v>
       </c>
       <c r="J35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.0661550860944109</v>
+        <v>3.5740889314943405</v>
       </c>
       <c r="K35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.56076158987735036</v>
+        <v>0.59629596145812003</v>
       </c>
       <c r="L35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.56190123654021007</v>
+        <v>0.53868094125300003</v>
       </c>
       <c r="M35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.78817475679418436</v>
+        <v>0.71908546331584444</v>
       </c>
       <c r="N35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.44610572243944058</v>
+        <v>0.4972305742650886</v>
       </c>
       <c r="O35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.62224645146085811</v>
+        <v>0.53987549654279332</v>
       </c>
       <c r="P35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.96135030764791241</v>
+        <v>1.039820745130877</v>
       </c>
       <c r="Q35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.8060122020076139</v>
+        <v>1.7349658267139352</v>
       </c>
       <c r="R35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.7953123515768001</v>
+        <v>1.9437968317823999</v>
       </c>
       <c r="S35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.8198315725990399</v>
+        <v>1.61485054381728</v>
       </c>
       <c r="T35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.88693140454931241</v>
+        <v>0.96165026742881243</v>
       </c>
       <c r="U35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.9997912394809998</v>
+        <v>1.9808646831791998</v>
       </c>
       <c r="V35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.2312890908385763</v>
+        <v>1.182256555788</v>
       </c>
       <c r="W35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.8854811061936837</v>
+        <v>0.93842441562869983</v>
       </c>
       <c r="X35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.357066814434531</v>
+        <v>1.290156729474413</v>
       </c>
       <c r="Y35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.82169808004367995</v>
+        <v>0.75830994244031047</v>
       </c>
       <c r="Z35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>3.7462910329214374</v>
+        <v>3.9051781845476392</v>
       </c>
       <c r="AA35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.6633369443305339</v>
+        <v>4.8508309826943865</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.3">
@@ -72856,99 +72852,99 @@
       </c>
       <c r="D36" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-10.378779003028802</v>
+        <v>-8.9283465751409992</v>
       </c>
       <c r="E36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-10.895952307648452</v>
+        <v>-10.991015512763704</v>
       </c>
       <c r="F36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-12.875505565473867</v>
+        <v>-13.934529832763923</v>
       </c>
       <c r="G36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-14.166592135978314</v>
+        <v>-11.94882188527712</v>
       </c>
       <c r="H36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-16.576002570889944</v>
+        <v>-16.39437393833694</v>
       </c>
       <c r="I36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-16.197565263811313</v>
+        <v>-17.021119851590402</v>
       </c>
       <c r="J36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-14.7078419299049</v>
+        <v>-14.559277870006872</v>
       </c>
       <c r="K36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-17.149980757093857</v>
+        <v>-15.527749567587884</v>
       </c>
       <c r="L36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-15.419097651623549</v>
+        <v>-16.204636707241242</v>
       </c>
       <c r="M36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-22.451195292602389</v>
+        <v>-22.675613737842895</v>
       </c>
       <c r="N36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-22.362014614108812</v>
+        <v>-19.872057960836266</v>
       </c>
       <c r="O36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-18.313266383674215</v>
+        <v>-18.327800722073956</v>
       </c>
       <c r="P36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-19.276975390608222</v>
+        <v>-20.258914197717246</v>
       </c>
       <c r="Q36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-18.985718172558212</v>
+        <v>-18.233808541961846</v>
       </c>
       <c r="R36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-18.185945531121465</v>
+        <v>-16.160984146707637</v>
       </c>
       <c r="S36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-16.255525899697545</v>
+        <v>-16.112113746141528</v>
       </c>
       <c r="T36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-16.463641799608173</v>
+        <v>-14.29707274674352</v>
       </c>
       <c r="U36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-12.951296002379541</v>
+        <v>-13.748021761415043</v>
       </c>
       <c r="V36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-8.8931536141347891</v>
+        <v>-8.9011775121325059</v>
       </c>
       <c r="W36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-9.2892552774381336</v>
+        <v>-9.7575073645584123</v>
       </c>
       <c r="X36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-10.631138590752059</v>
+        <v>-11.180323683769224</v>
       </c>
       <c r="Y36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-10.318187623834817</v>
+        <v>-10.965429468337449</v>
       </c>
       <c r="Z36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-9.4308030875874813</v>
+        <v>-9.240281813090764</v>
       </c>
       <c r="AA36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-9.3688192574082958</v>
+        <v>-8.904160401504539</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.3">
@@ -72963,99 +72959,99 @@
       </c>
       <c r="D37" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>10.31166540487016</v>
+        <v>9.8991987886753563</v>
       </c>
       <c r="E37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>11.051365044351419</v>
+        <v>10.818551870639418</v>
       </c>
       <c r="F37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>12.884071865096752</v>
+        <v>12.007323418488649</v>
       </c>
       <c r="G37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>12.895703786402235</v>
+        <v>12.266735838378576</v>
       </c>
       <c r="H37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>14.014728058928258</v>
+        <v>12.783800356966601</v>
       </c>
       <c r="I37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>14.005742733513532</v>
+        <v>15.48292220447853</v>
       </c>
       <c r="J37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>14.893169461896726</v>
+        <v>15.32368635079464</v>
       </c>
       <c r="K37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>15.205604987433368</v>
+        <v>16.297528103315749</v>
       </c>
       <c r="L37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>15.402318747060406</v>
+        <v>13.91357389022269</v>
       </c>
       <c r="M37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>17.902691709417983</v>
+        <v>19.206458406490228</v>
       </c>
       <c r="N37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>19.572309053720243</v>
+        <v>19.203448520882858</v>
       </c>
       <c r="O37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>14.84536329179759</v>
+        <v>15.314164237854351</v>
       </c>
       <c r="P37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>15.583082285924997</v>
+        <v>14.347847556240186</v>
       </c>
       <c r="Q37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>15.586443139754277</v>
+        <v>14.992673877287446</v>
       </c>
       <c r="R37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>14.338829773882374</v>
+        <v>15.669264396864801</v>
       </c>
       <c r="S37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>13.873672180216932</v>
+        <v>14.287380851332973</v>
       </c>
       <c r="T37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>11.450918896066435</v>
+        <v>13.029408838818062</v>
       </c>
       <c r="U37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>11.093528819180852</v>
+        <v>11.657581777891226</v>
       </c>
       <c r="V37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>9.3050491608809942</v>
+        <v>8.52030409409676</v>
       </c>
       <c r="W37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>8.8822511697204316</v>
+        <v>9.1664098758724801</v>
       </c>
       <c r="X37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>9.4326446580912027</v>
+        <v>10.431512081884859</v>
       </c>
       <c r="Y37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>11.448994837546032</v>
+        <v>10.258045305207677</v>
       </c>
       <c r="Z37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>8.9118506262928001</v>
+        <v>8.4839767965179131</v>
       </c>
       <c r="AA37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>8.7526779370084427</v>
+        <v>8.7526779370084462</v>
       </c>
     </row>
   </sheetData>

--- a/data/CS7/case33_3/case33_3_operational_data.xlsx
+++ b/data/CS7/case33_3/case33_3_operational_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\case33_3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D556740-5EA6-4C8C-BC63-CB7C5131072F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52A4044D-2846-49FF-A7A4-32B58EBE9183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-15195" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -477,8 +477,8 @@
         <v>3.5250000000000004</v>
       </c>
       <c r="C2" s="1">
-        <f>F2*4</f>
-        <v>2.88</v>
+        <f>F2*3</f>
+        <v>2.16</v>
       </c>
       <c r="D2" s="2">
         <v>2.6917900403768499E-2</v>
@@ -499,8 +499,8 @@
         <v>3.5774999999999997</v>
       </c>
       <c r="C3" s="1">
-        <f t="shared" ref="C3:C33" si="1">F3*4</f>
-        <v>-3.52</v>
+        <f t="shared" ref="C3:C33" si="1">F3*3</f>
+        <v>-2.64</v>
       </c>
       <c r="D3" s="2">
         <v>2.4226110363391645E-2</v>
@@ -522,7 +522,7 @@
       </c>
       <c r="C4" s="1">
         <f t="shared" si="1"/>
-        <v>-2.88</v>
+        <v>-2.16</v>
       </c>
       <c r="D4" s="2">
         <v>3.2301480484522194E-2</v>
@@ -544,7 +544,7 @@
       </c>
       <c r="C5" s="1">
         <f t="shared" si="1"/>
-        <v>1.92</v>
+        <v>1.44</v>
       </c>
       <c r="D5" s="2">
         <v>1.6150740242261097E-2</v>
@@ -566,7 +566,7 @@
       </c>
       <c r="C6" s="1">
         <f t="shared" si="1"/>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="D6" s="2">
         <v>1.6150740242261097E-2</v>
@@ -588,7 +588,7 @@
       </c>
       <c r="C7" s="1">
         <f t="shared" si="1"/>
-        <v>-4.4000000000000004</v>
+        <v>-3.3000000000000003</v>
       </c>
       <c r="D7" s="2">
         <v>5.3835800807536999E-2</v>
@@ -610,7 +610,7 @@
       </c>
       <c r="C8" s="1">
         <f t="shared" si="1"/>
-        <v>8.4</v>
+        <v>6.3000000000000007</v>
       </c>
       <c r="D8" s="2">
         <v>5.3835800807536999E-2</v>
@@ -632,7 +632,7 @@
       </c>
       <c r="C9" s="1">
         <f t="shared" si="1"/>
-        <v>1.92</v>
+        <v>1.44</v>
       </c>
       <c r="D9" s="2">
         <v>1.6150740242261097E-2</v>
@@ -654,7 +654,7 @@
       </c>
       <c r="C10" s="1">
         <f t="shared" si="1"/>
-        <v>-1.04</v>
+        <v>-0.78</v>
       </c>
       <c r="D10" s="2">
         <v>1.6150740242261097E-2</v>
@@ -676,7 +676,7 @@
       </c>
       <c r="C11" s="1">
         <f t="shared" si="1"/>
-        <v>-1.2</v>
+        <v>-0.89999999999999991</v>
       </c>
       <c r="D11" s="2">
         <v>1.2113055181695823E-2</v>
@@ -698,7 +698,7 @@
       </c>
       <c r="C12" s="1">
         <f t="shared" si="1"/>
-        <v>4.62</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="D12" s="2">
         <v>1.6150740242261097E-2</v>
@@ -720,7 +720,7 @@
       </c>
       <c r="C13" s="1">
         <f t="shared" si="1"/>
-        <v>-3.5000000000000004</v>
+        <v>-2.6250000000000004</v>
       </c>
       <c r="D13" s="2">
         <v>1.6150740242261097E-2</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C14" s="1">
         <f t="shared" si="1"/>
-        <v>12.8</v>
+        <v>9.6000000000000014</v>
       </c>
       <c r="D14" s="2">
         <v>3.2301480484522194E-2</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="C15" s="1">
         <f t="shared" si="1"/>
-        <v>1.48</v>
+        <v>1.1099999999999999</v>
       </c>
       <c r="D15" s="2">
         <v>1.6150740242261097E-2</v>
@@ -786,7 +786,7 @@
       </c>
       <c r="C16" s="1">
         <f t="shared" si="1"/>
-        <v>3.2</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="D16" s="2">
         <v>1.6150740242261097E-2</v>
@@ -808,7 +808,7 @@
       </c>
       <c r="C17" s="1">
         <f t="shared" si="1"/>
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
       <c r="D17" s="2">
         <v>1.6150740242261097E-2</v>
@@ -830,7 +830,7 @@
       </c>
       <c r="C18" s="1">
         <f t="shared" si="1"/>
-        <v>-3.04</v>
+        <v>-2.2800000000000002</v>
       </c>
       <c r="D18" s="2">
         <v>2.4226110363391645E-2</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="C19" s="1">
         <f t="shared" si="1"/>
-        <v>-2.2400000000000002</v>
+        <v>-1.6800000000000002</v>
       </c>
       <c r="D19" s="2">
         <v>2.4226110363391645E-2</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="C20" s="1">
         <f t="shared" si="1"/>
-        <v>-4.96</v>
+        <v>-3.7199999999999998</v>
       </c>
       <c r="D20" s="2">
         <v>2.4226110363391645E-2</v>
@@ -896,7 +896,7 @@
       </c>
       <c r="C21" s="1">
         <f t="shared" si="1"/>
-        <v>-5.28</v>
+        <v>-3.96</v>
       </c>
       <c r="D21" s="2">
         <v>2.4226110363391645E-2</v>
@@ -918,7 +918,7 @@
       </c>
       <c r="C22" s="1">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="D22" s="2">
         <v>2.4226110363391645E-2</v>
@@ -940,7 +940,7 @@
       </c>
       <c r="C23" s="1">
         <f t="shared" si="1"/>
-        <v>7.6000000000000005</v>
+        <v>5.7</v>
       </c>
       <c r="D23" s="2">
         <v>2.4226110363391645E-2</v>
@@ -957,12 +957,12 @@
         <v>23</v>
       </c>
       <c r="B24" s="1">
-        <f t="shared" si="0"/>
-        <v>17.64</v>
+        <f>E24*0.4</f>
+        <v>9.4079999999999995</v>
       </c>
       <c r="C24" s="1">
-        <f t="shared" si="1"/>
-        <v>31.200000000000003</v>
+        <f>F24*0.4</f>
+        <v>3.1200000000000006</v>
       </c>
       <c r="D24" s="2">
         <v>0.11305518169582769</v>
@@ -983,8 +983,8 @@
         <v>9.7650000000000006</v>
       </c>
       <c r="C25" s="1">
-        <f t="shared" si="1"/>
-        <v>-13.600000000000001</v>
+        <f>F25*2.5</f>
+        <v>-8.5</v>
       </c>
       <c r="D25" s="2">
         <v>0.11305518169582769</v>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="C26" s="1">
         <f t="shared" si="1"/>
-        <v>2.1</v>
+        <v>1.5750000000000002</v>
       </c>
       <c r="D26" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="C27" s="1">
         <f t="shared" si="1"/>
-        <v>1.1000000000000001</v>
+        <v>0.82500000000000007</v>
       </c>
       <c r="D27" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="C28" s="1">
         <f t="shared" si="1"/>
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
       <c r="D28" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C29" s="1">
         <f t="shared" si="1"/>
-        <v>-3.3600000000000003</v>
+        <v>-2.5200000000000005</v>
       </c>
       <c r="D29" s="2">
         <v>3.2301480484522194E-2</v>
@@ -1093,7 +1093,8 @@
         <v>4.2</v>
       </c>
       <c r="C30" s="1">
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>32.4</v>
       </c>
       <c r="D30" s="2">
         <v>5.3835800807536999E-2</v>
@@ -1115,7 +1116,7 @@
       </c>
       <c r="C31" s="1">
         <f t="shared" si="1"/>
-        <v>-7.8400000000000007</v>
+        <v>-5.8800000000000008</v>
       </c>
       <c r="D31" s="2">
         <v>4.0376850605652742E-2</v>
@@ -1137,7 +1138,7 @@
       </c>
       <c r="C32" s="1">
         <f t="shared" si="1"/>
-        <v>-13.200000000000001</v>
+        <v>-9.9</v>
       </c>
       <c r="D32" s="2">
         <v>5.6527590847913846E-2</v>
@@ -1159,7 +1160,7 @@
       </c>
       <c r="C33" s="1">
         <f t="shared" si="1"/>
-        <v>4.6399999999999997</v>
+        <v>3.4799999999999995</v>
       </c>
       <c r="D33" s="2">
         <v>1.6150740242261097E-2</v>
@@ -70184,39 +70185,39 @@
       </c>
       <c r="E11" s="1">
         <f t="shared" ref="E11:AA19" ca="1" si="0">E2*0.95*RANDBETWEEN(95,105)/100</f>
-        <v>5.0194352000000002</v>
+        <v>4.7781162000000004</v>
       </c>
       <c r="F11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.5378270000000001</v>
+        <v>4.4081748000000003</v>
       </c>
       <c r="G11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.0144719999999987</v>
+        <v>3.9325439999999992</v>
       </c>
       <c r="H11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3.4904063999999999</v>
+        <v>3.2890367999999999</v>
       </c>
       <c r="I11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2.7060560000000002</v>
+        <v>2.9909040000000005</v>
       </c>
       <c r="J11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3.5879637999999998</v>
+        <v>3.6576330000000001</v>
       </c>
       <c r="K11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.60496000000000005</v>
+        <v>0.59891040000000006</v>
       </c>
       <c r="L11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.52136000000000005</v>
+        <v>0.51072000000000006</v>
       </c>
       <c r="M11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.75231259999999978</v>
+        <v>0.79109159999999989</v>
       </c>
       <c r="N11" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70224,19 +70225,19 @@
       </c>
       <c r="O11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.59929799999999989</v>
+        <v>0.55934479999999998</v>
       </c>
       <c r="P11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.95480700000000029</v>
+        <v>0.90934000000000026</v>
       </c>
       <c r="Q11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.6586658000000001</v>
+        <v>1.6754199999999999</v>
       </c>
       <c r="R11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.8232703999999997</v>
+        <v>1.6981439999999999</v>
       </c>
       <c r="S11" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70244,11 +70245,11 @@
       </c>
       <c r="T11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.97623899999999997</v>
+        <v>0.95651699999999995</v>
       </c>
       <c r="U11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2.0287667999999996</v>
+        <v>1.9283327999999995</v>
       </c>
       <c r="V11" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70256,23 +70257,23 @@
       </c>
       <c r="W11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.87021899999999985</v>
+        <v>0.78734099999999985</v>
       </c>
       <c r="X11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.2963168000000003</v>
+        <v>1.2837312000000001</v>
       </c>
       <c r="Y11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.80119580000000001</v>
+        <v>0.78563860000000008</v>
       </c>
       <c r="Z11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3.5858434000000003</v>
+        <v>3.7278570000000002</v>
       </c>
       <c r="AA11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.3655387999999995</v>
+        <v>4.1515418000000004</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
@@ -70287,35 +70288,35 @@
       </c>
       <c r="D12" s="1">
         <f t="shared" ref="D12:S19" ca="1" si="1">D3*0.95*RANDBETWEEN(95,105)/100</f>
-        <v>-11.072250000000002</v>
+        <v>-10.334100000000001</v>
       </c>
       <c r="E12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-10.825075199999999</v>
+        <v>-11.614403599999997</v>
       </c>
       <c r="F12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-12.555298800000001</v>
+        <v>-13.316226000000002</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-13.269968600000002</v>
+        <v>-13.133164800000001</v>
       </c>
       <c r="H12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-15.207296000000001</v>
+        <v>-14.476176000000001</v>
       </c>
       <c r="I12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-15.958100000000002</v>
+        <v>-16.117681000000001</v>
       </c>
       <c r="J12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-14.465631</v>
+        <v>-15.074710200000002</v>
       </c>
       <c r="K12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-16.909964280000001</v>
+        <v>-16.226733400000001</v>
       </c>
       <c r="L12" s="1">
         <f t="shared" ca="1" si="1"/>
@@ -70323,35 +70324,35 @@
       </c>
       <c r="M12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-22.300094039999994</v>
+        <v>-21.844990079999999</v>
       </c>
       <c r="N12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-23.422871680000004</v>
+        <v>-23.197651760000003</v>
       </c>
       <c r="O12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-19.559124400000002</v>
+        <v>-20.588552</v>
       </c>
       <c r="P12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-20.130548640000001</v>
+        <v>-20.722623599999999</v>
       </c>
       <c r="Q12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-19.62624418</v>
+        <v>-19.054606</v>
       </c>
       <c r="R12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-17.960396000000003</v>
+        <v>-17.780792040000005</v>
       </c>
       <c r="S12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-15.853707159999999</v>
+        <v>-16.180587719999998</v>
       </c>
       <c r="T12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-14.824133639999999</v>
+        <v>-14.518481400000001</v>
       </c>
       <c r="U12" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70359,7 +70360,7 @@
       </c>
       <c r="V12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-8.6808339999999991</v>
+        <v>-9.1148756999999989</v>
       </c>
       <c r="W12" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70367,19 +70368,19 @@
       </c>
       <c r="X12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-10.16665452</v>
+        <v>-10.680121919999999</v>
       </c>
       <c r="Y12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-11.355883899999998</v>
+        <v>-10.804627399999999</v>
       </c>
       <c r="Z12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-8.8469738000000007</v>
+        <v>-8.3214110000000012</v>
       </c>
       <c r="AA12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-9.1215656000000003</v>
+        <v>-8.8423339999999993</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
@@ -70394,15 +70395,15 @@
       </c>
       <c r="D13" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>10.565237279999998</v>
+        <v>10.666826099999998</v>
       </c>
       <c r="E13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10.868303999999997</v>
+        <v>10.324888799999997</v>
       </c>
       <c r="F13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>11.5765841</v>
+        <v>11.820301659999998</v>
       </c>
       <c r="G13" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70410,51 +70411,51 @@
       </c>
       <c r="H13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>13.677693399999999</v>
+        <v>14.375534899999998</v>
       </c>
       <c r="I13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.477905</v>
+        <v>15.849496000000002</v>
       </c>
       <c r="J13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.093420999999999</v>
+        <v>14.674592999999998</v>
       </c>
       <c r="K13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16.06827796</v>
+        <v>17.052050080000001</v>
       </c>
       <c r="L13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.41795392</v>
+        <v>15.319076040000002</v>
       </c>
       <c r="M13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>17.137467999999998</v>
+        <v>17.82296672</v>
       </c>
       <c r="N13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>17.963302240000001</v>
+        <v>17.272406</v>
       </c>
       <c r="O13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16.492031159999996</v>
+        <v>16.006971419999999</v>
       </c>
       <c r="P13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.779937000000002</v>
+        <v>16.092411000000002</v>
       </c>
       <c r="Q13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.222116000000002</v>
+        <v>15.831000639999999</v>
       </c>
       <c r="R13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>13.980193920000003</v>
+        <v>14.408159040000003</v>
       </c>
       <c r="S13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12.858026940000002</v>
+        <v>13.117785060000003</v>
       </c>
       <c r="T13" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70462,31 +70463,31 @@
       </c>
       <c r="U13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>11.03001072</v>
+        <v>10.489323919999999</v>
       </c>
       <c r="V13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8.8870865999999982</v>
+        <v>8.3792530799999998</v>
       </c>
       <c r="W13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8.9998743999999995</v>
+        <v>9.4735519999999998</v>
       </c>
       <c r="X13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10.469401280000001</v>
+        <v>10.167399320000001</v>
       </c>
       <c r="Y13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10.843831999999999</v>
+        <v>10.73539368</v>
       </c>
       <c r="Z13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8.1847629999999985</v>
+        <v>8.3535209999999989</v>
       </c>
       <c r="AA13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8.9725600000000014</v>
+        <v>8.5239320000000003</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
@@ -70501,31 +70502,31 @@
       </c>
       <c r="D14" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>5.0512322700000007</v>
+        <v>5.1493144500000003</v>
       </c>
       <c r="E14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.8220362579999998</v>
+        <v>4.7723245440000008</v>
       </c>
       <c r="F14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.3563139199999998</v>
+        <v>4.1488703999999998</v>
       </c>
       <c r="G14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.1750508799999997</v>
+        <v>4.3880636799999992</v>
       </c>
       <c r="H14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3.2541327360000003</v>
+        <v>3.5592076800000001</v>
       </c>
       <c r="I14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2.8769648000000001</v>
+        <v>2.905734448</v>
       </c>
       <c r="J14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3.482066616</v>
+        <v>3.4465353240000001</v>
       </c>
       <c r="K14" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70533,67 +70534,67 @@
       </c>
       <c r="L14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.55343960000000014</v>
+        <v>0.57535800000000004</v>
       </c>
       <c r="M14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.76766908399999978</v>
+        <v>0.79116915799999987</v>
       </c>
       <c r="N14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.46105354400000004</v>
+        <v>0.49398594000000001</v>
       </c>
       <c r="O14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.570702924</v>
+        <v>0.58223227599999994</v>
       </c>
       <c r="P14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.91788779600000026</v>
+        <v>0.88978919000000023</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.6712314500000003</v>
+        <v>1.7415990900000002</v>
       </c>
       <c r="R14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.896379968</v>
+        <v>1.7859112319999999</v>
       </c>
       <c r="S14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.8457739999999996</v>
+        <v>1.7578799999999994</v>
       </c>
       <c r="T14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.0156829999999999</v>
+        <v>1.005822</v>
       </c>
       <c r="U14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.9082459999999994</v>
+        <v>2.0488535999999997</v>
       </c>
       <c r="V14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.2500749800000002</v>
+        <v>1.2624519600000002</v>
       </c>
       <c r="W14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.81883463999999972</v>
+        <v>0.87055051199999978</v>
       </c>
       <c r="X14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.2958133760000001</v>
+        <v>1.3089024000000002</v>
       </c>
       <c r="Y14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.80928554400000008</v>
+        <v>0.79341720000000004</v>
       </c>
       <c r="Z14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3.6160212900000004</v>
+        <v>3.7651355700000004</v>
       </c>
       <c r="AA14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.3227394000000006</v>
+        <v>4.5388763700000005</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.3">
@@ -70608,31 +70609,31 @@
       </c>
       <c r="D15" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-10.325664000000002</v>
+        <v>-10.123200000000001</v>
       </c>
       <c r="E15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-11.731675247999998</v>
+        <v>-10.926560279999999</v>
       </c>
       <c r="F15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-12.670706092000003</v>
+        <v>-13.193209436000004</v>
       </c>
       <c r="G15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-13.955355638</v>
+        <v>-13.8171838</v>
       </c>
       <c r="H15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-15.660590399999998</v>
+        <v>-15.199984799999999</v>
       </c>
       <c r="I15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-15.918204750000003</v>
+        <v>-17.593805250000003</v>
       </c>
       <c r="J15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-14.754943619999999</v>
+        <v>-14.61028731</v>
       </c>
       <c r="K15" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70640,47 +70641,47 @@
       </c>
       <c r="L15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-15.318481689599993</v>
+        <v>-16.754589347999996</v>
       </c>
       <c r="M15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-22.969096861199997</v>
+        <v>-23.906611018799996</v>
       </c>
       <c r="N15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-22.251728096000008</v>
+        <v>-22.037769172000004</v>
       </c>
       <c r="O15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-20.555610316799999</v>
+        <v>-19.765009919999997</v>
       </c>
       <c r="P15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-19.135862707199998</v>
+        <v>-20.132522223199999</v>
       </c>
       <c r="Q15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-18.463913214000002</v>
+        <v>-19.046984157600001</v>
       </c>
       <c r="R15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-18.499207880000004</v>
+        <v>-18.869192037600001</v>
       </c>
       <c r="S15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-16.147899663999997</v>
+        <v>-15.682094865999998</v>
       </c>
       <c r="T15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-14.377881369599999</v>
+        <v>-15.2581598208</v>
       </c>
       <c r="U15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-13.260664588800003</v>
+        <v>-13.122532666000001</v>
       </c>
       <c r="V15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-9.0237269429999998</v>
+        <v>-8.3362048901999994</v>
       </c>
       <c r="W15" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70688,19 +70689,19 @@
       </c>
       <c r="X15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-10.998471707999997</v>
+        <v>-11.106299861999997</v>
       </c>
       <c r="Y15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-10.795807295999998</v>
+        <v>-11.358088925999999</v>
       </c>
       <c r="Z15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-8.7453649919999989</v>
+        <v>-9.474145408</v>
       </c>
       <c r="AA15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-8.9307573399999995</v>
+        <v>-9.5888131439999995</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
@@ -70715,43 +70716,43 @@
       </c>
       <c r="D16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>9.9404660369999984</v>
+        <v>10.777557913799999</v>
       </c>
       <c r="E16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>11.082409588799997</v>
+        <v>11.194353119999995</v>
       </c>
       <c r="F16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12.064019219999999</v>
+        <v>12.307736779999997</v>
       </c>
       <c r="G16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12.587825279999999</v>
+        <v>12.0843122688</v>
       </c>
       <c r="H16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>13.524168269999997</v>
+        <v>14.235966599999998</v>
       </c>
       <c r="I16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.333125950000001</v>
+        <v>15.691001040000002</v>
       </c>
       <c r="J16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>13.388749949999999</v>
+        <v>14.0788917</v>
       </c>
       <c r="K16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.582950380800003</v>
+        <v>15.897757459200001</v>
       </c>
       <c r="L16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.9333409518</v>
+        <v>14.850492537600001</v>
       </c>
       <c r="M16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>17.9943414</v>
+        <v>18.714115056000001</v>
       </c>
       <c r="N16" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70767,43 +70768,43 @@
       </c>
       <c r="Q16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.039450607999999</v>
+        <v>13.73795969</v>
       </c>
       <c r="R16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.577930368000002</v>
+        <v>14.836124160000002</v>
       </c>
       <c r="S16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>13.773674313000001</v>
+        <v>12.5930736576</v>
       </c>
       <c r="T16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12.331543369599997</v>
+        <v>12.205711294399997</v>
       </c>
       <c r="U16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10.9153851184</v>
+        <v>11.138148079999999</v>
       </c>
       <c r="V16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8.2920749923999981</v>
+        <v>7.799476477999999</v>
       </c>
       <c r="W16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9.9510190208000004</v>
+        <v>9.8553361456000008</v>
       </c>
       <c r="X16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9.6640627200000022</v>
+        <v>10.167399320000001</v>
       </c>
       <c r="Y16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10.198623996000002</v>
+        <v>10.404656804000002</v>
       </c>
       <c r="Z16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8.4243993600000007</v>
+        <v>8.3366451999999995</v>
       </c>
       <c r="AA16" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70822,23 +70823,23 @@
       </c>
       <c r="D17" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>4.6589035500000016</v>
+        <v>4.8452596920000017</v>
       </c>
       <c r="E17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.9711714000000002</v>
+        <v>4.8220362579999998</v>
       </c>
       <c r="F17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.3588032422399996</v>
+        <v>4.2318478079999995</v>
       </c>
       <c r="G17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.5635862271999992</v>
+        <v>4.2534395903999993</v>
       </c>
       <c r="H17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3.4575160320000005</v>
+        <v>3.3192153907200002</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70850,35 +70851,35 @@
       </c>
       <c r="K17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.59150568959999994</v>
+        <v>0.62847479519999994</v>
       </c>
       <c r="L17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.53097324000000012</v>
+        <v>0.50494514000000013</v>
       </c>
       <c r="M17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.81427756409999974</v>
+        <v>0.76774741757999976</v>
       </c>
       <c r="N17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.46091240515999998</v>
+        <v>0.48467077656000002</v>
       </c>
       <c r="O17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.60563686055999999</v>
+        <v>0.56407354659999998</v>
       </c>
       <c r="P17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.0130484083200002</v>
+        <v>0.92538075760000027</v>
       </c>
       <c r="Q17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.74159909</v>
+        <v>1.6893511173</v>
       </c>
       <c r="R17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.9332028799999998</v>
+        <v>1.9911989663999998</v>
       </c>
       <c r="S17" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70886,35 +70887,35 @@
       </c>
       <c r="T17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.90869114999999989</v>
+        <v>0.92742704999999992</v>
       </c>
       <c r="U17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2.0890271999999994</v>
+        <v>1.9082459999999994</v>
       </c>
       <c r="V17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.2346037550000002</v>
+        <v>1.3645620450000004</v>
       </c>
       <c r="W17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.88744436351999967</v>
+        <v>0.87037812575999962</v>
       </c>
       <c r="X17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.3606040448000001</v>
+        <v>1.2439808409600002</v>
       </c>
       <c r="Y17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.77691412224</v>
+        <v>0.73121329152000003</v>
       </c>
       <c r="Z17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3.7606621415999997</v>
+        <v>3.7994318543999999</v>
       </c>
       <c r="AA17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.4480988426000003</v>
+        <v>4.4027100788999993</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.3">
@@ -70929,27 +70930,27 @@
       </c>
       <c r="D18" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-9.5208695999999993</v>
+        <v>-9.1361879999999989</v>
       </c>
       <c r="E18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-11.046177360959998</v>
+        <v>-11.609757838559998</v>
       </c>
       <c r="F18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-12.797413152920001</v>
+        <v>-12.670706092</v>
       </c>
       <c r="G18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-13.529786376960002</v>
+        <v>-12.733916590080003</v>
       </c>
       <c r="H18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-16.282407959999997</v>
+        <v>-14.731702439999999</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-17.258685150000002</v>
+        <v>-16.923565050000001</v>
       </c>
       <c r="J18" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -70957,71 +70958,71 @@
       </c>
       <c r="K18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-15.897330711979999</v>
+        <v>-17.403393621535997</v>
       </c>
       <c r="L18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-16.084405774079993</v>
+        <v>-15.012112055807993</v>
       </c>
       <c r="M18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-24.855844103369996</v>
+        <v>-23.908954804193996</v>
       </c>
       <c r="N18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-21.177654297520004</v>
+        <v>-22.042048350480005</v>
       </c>
       <c r="O18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-18.588991829760001</v>
+        <v>-19.527829800959999</v>
       </c>
       <c r="P18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-20.937823112127997</v>
+        <v>-19.327221334272</v>
       </c>
       <c r="Q18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-17.725356685439998</v>
+        <v>-17.911939387392</v>
       </c>
       <c r="R18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-17.749989960860006</v>
+        <v>-16.695535111700003</v>
       </c>
       <c r="S18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-15.995736763319996</v>
+        <v>-16.312484025959996</v>
       </c>
       <c r="T18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-15.868486213631998</v>
+        <v>-15.258159820799996</v>
       </c>
       <c r="U18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-14.796691570336002</v>
+        <v>-14.227588048400001</v>
       </c>
       <c r="V18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-8.6799659165999987</v>
+        <v>-8.9377866863999991</v>
       </c>
       <c r="W18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-9.3161545430799979</v>
+        <v>-8.592569724199997</v>
       </c>
       <c r="X18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-10.55853283968</v>
+        <v>-11.548395293399999</v>
       </c>
       <c r="Y18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-11.003851499099996</v>
+        <v>-10.469683950599997</v>
       </c>
       <c r="Z18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-8.3080967424000001</v>
+        <v>-9.0077259417600004</v>
       </c>
       <c r="AA18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-9.67906079712</v>
+        <v>-9.4929250125599989</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.3">
@@ -71036,79 +71037,79 @@
       </c>
       <c r="D19" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>9.6422520558899976</v>
+        <v>9.7437494459519982</v>
       </c>
       <c r="E19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>11.409284699903997</v>
+        <v>11.189875378751998</v>
       </c>
       <c r="F19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>11.583895626799999</v>
+        <v>11.938504676599997</v>
       </c>
       <c r="G19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12.436771376639999</v>
+        <v>12.567684759551998</v>
       </c>
       <c r="H19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.097242579299996</v>
+        <v>15.695153176499996</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.046463430999999</v>
+        <v>14.933608489799999</v>
       </c>
       <c r="J19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.354948400000001</v>
+        <v>14.067849432000001</v>
       </c>
       <c r="K19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>17.188466480640002</v>
+        <v>16.369968076800003</v>
       </c>
       <c r="L19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.107967910720001</v>
+        <v>13.961009911650001</v>
       </c>
       <c r="M19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>18.327236715899996</v>
+        <v>19.271939639399999</v>
       </c>
       <c r="N19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>19.427311372560006</v>
+        <v>17.577091241840002</v>
       </c>
       <c r="O19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16.975393190909998</v>
+        <v>16.490381956883997</v>
       </c>
       <c r="P19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.937736369999998</v>
+        <v>14.990940149999998</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.192737316119999</v>
+        <v>14.150098480699999</v>
       </c>
       <c r="R19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.385105985536002</v>
+        <v>15.434019963648002</v>
       </c>
       <c r="S19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>13.381452539706002</v>
+        <v>12.719004394176002</v>
       </c>
       <c r="T19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12.449825520287998</v>
+        <v>11.961597068511997</v>
       </c>
       <c r="U19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>11.701738372847998</v>
+        <v>11.247301931183999</v>
       </c>
       <c r="V19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8.2904329973519992</v>
+        <v>8.4579164922479997</v>
       </c>
       <c r="W19" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -71116,19 +71117,19 @@
       </c>
       <c r="X19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10.265046620400003</v>
+        <v>10.576108639200005</v>
       </c>
       <c r="Y19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10.196563667920001</v>
+        <v>10.924889644200002</v>
       </c>
       <c r="Z19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8.4279095264000006</v>
+        <v>8.2559113728000018</v>
       </c>
       <c r="AA19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9.1510959988800007</v>
+        <v>8.7886763553600016</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.3">
@@ -71143,99 +71144,99 @@
       </c>
       <c r="D20" s="1">
         <f ca="1">D11*1.05*RANDBETWEEN(95,105)/100</f>
-        <v>4.7579665518000009</v>
+        <v>4.9502076246000009</v>
       </c>
       <c r="E20" s="1">
         <f t="shared" ref="E20:AA28" ca="1" si="2">E11*1.05*RANDBETWEEN(95,105)/100</f>
-        <v>5.0595906816000005</v>
+        <v>4.9668517899000006</v>
       </c>
       <c r="F20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.8123655335000004</v>
+        <v>4.4897260338000002</v>
       </c>
       <c r="G20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.0465877759999991</v>
+        <v>4.0878794879999996</v>
       </c>
       <c r="H20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>3.5916281855999999</v>
+        <v>3.2808142080000007</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2.7277044480000008</v>
+        <v>3.2974716600000007</v>
       </c>
       <c r="J20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>3.6543411302999997</v>
+        <v>3.994135236</v>
       </c>
       <c r="K20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.63520800000000011</v>
+        <v>0.64772159760000003</v>
       </c>
       <c r="L20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.52553088000000003</v>
+        <v>0.55770624000000002</v>
       </c>
       <c r="M20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.81362607689999977</v>
+        <v>0.8472591035999999</v>
       </c>
       <c r="N20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.49854212100000006</v>
+        <v>0.4890460806000001</v>
       </c>
       <c r="O20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.6355555289999999</v>
+        <v>0.56969267880000007</v>
       </c>
       <c r="P20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.97247092950000036</v>
+        <v>0.94525893000000027</v>
       </c>
       <c r="Q20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.7938470627000003</v>
+        <v>1.8295586399999999</v>
       </c>
       <c r="R20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.8570009023999998</v>
+        <v>1.8365427359999997</v>
       </c>
       <c r="S20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.8828740573999996</v>
+        <v>1.8455894225999998</v>
       </c>
       <c r="T20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.97379840250000005</v>
+        <v>1.0244297070000001</v>
       </c>
       <c r="U20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2.1728092427999997</v>
+        <v>1.9235119679999995</v>
       </c>
       <c r="V20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.2877009992000001</v>
+        <v>1.1993293620000001</v>
       </c>
       <c r="W20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.95941644749999999</v>
+        <v>0.86804345249999992</v>
       </c>
       <c r="X20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.3339099872000002</v>
+        <v>1.4153136480000001</v>
       </c>
       <c r="Y20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.83284303410000005</v>
+        <v>0.80017291410000013</v>
       </c>
       <c r="Z20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>3.5768787915</v>
+        <v>4.0708198440000007</v>
       </c>
       <c r="AA20" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.5379775825999999</v>
+        <v>4.1411629455000005</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.3">
@@ -71250,99 +71251,99 @@
       </c>
       <c r="D21" s="1">
         <f t="shared" ref="D21:S28" ca="1" si="3">D12*1.05*RANDBETWEEN(95,105)/100</f>
-        <v>-11.509603875000003</v>
+        <v>-11.284837200000002</v>
       </c>
       <c r="E21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-11.4799922496</v>
+        <v>-12.560977493399998</v>
       </c>
       <c r="F21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-13.446725014800002</v>
+        <v>-13.982037300000004</v>
       </c>
       <c r="G21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-13.236793678500003</v>
+        <v>-13.651924809600002</v>
       </c>
       <c r="H21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-15.328954368000002</v>
+        <v>-14.895985104000001</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-16.253324850000002</v>
+        <v>-16.415858098499999</v>
       </c>
       <c r="J21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-15.644579926500001</v>
+        <v>-15.195307881600002</v>
       </c>
       <c r="K21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-17.577907869059999</v>
+        <v>-16.186166566500003</v>
       </c>
       <c r="L21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-16.578910158719992</v>
+        <v>-17.763118027199994</v>
       </c>
       <c r="M21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-23.415098741999994</v>
+        <v>-22.707867188159998</v>
       </c>
       <c r="N21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-23.856194806080008</v>
+        <v>-24.357534348000005</v>
       </c>
       <c r="O21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-20.9478222324</v>
+        <v>-20.537080620000001</v>
       </c>
       <c r="P21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-21.982559114880004</v>
+        <v>-22.411517423399999</v>
       </c>
       <c r="Q21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-21.019707516780002</v>
+        <v>-20.007336300000002</v>
       </c>
       <c r="R21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-18.481247484000004</v>
+        <v>-17.736340059900005</v>
       </c>
       <c r="S21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-16.479928592819999</v>
+        <v>-17.499305619179999</v>
       </c>
       <c r="T21" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-15.720993725220001</v>
+        <v>-15.549293579400002</v>
       </c>
       <c r="U21" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-14.187926407200001</v>
+        <v>-14.48661959472</v>
       </c>
       <c r="V21" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-9.5706194849999981</v>
+        <v>-9.3792070953</v>
       </c>
       <c r="W21" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-10.30088275524</v>
+        <v>-10.502860848479999</v>
       </c>
       <c r="X21" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-10.781737118460001</v>
+        <v>-10.653421615199999</v>
       </c>
       <c r="Y21" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-11.6852045331</v>
+        <v>-11.9121017085</v>
       </c>
       <c r="Z21" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-9.2893224900000018</v>
+        <v>-8.3006074725000012</v>
       </c>
       <c r="AA21" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-9.3860910024000006</v>
+        <v>-9.2844506999999989</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.3">
@@ -71357,99 +71358,99 @@
       </c>
       <c r="D22" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>11.537239109759998</v>
+        <v>11.424170753099997</v>
       </c>
       <c r="E22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>11.639953583999997</v>
+        <v>10.841133239999998</v>
       </c>
       <c r="F22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>12.3985215711</v>
+        <v>12.907769412719999</v>
       </c>
       <c r="G22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>13.897352478660002</v>
+        <v>14.606401074510002</v>
       </c>
       <c r="H22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>14.936041192800001</v>
+        <v>14.490539179200001</v>
       </c>
       <c r="I22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>14.593728240000001</v>
+        <v>16.808390508000002</v>
       </c>
       <c r="J22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.390015732</v>
+        <v>15.408322649999997</v>
       </c>
       <c r="K22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16.534258020840003</v>
+        <v>18.7998852132</v>
       </c>
       <c r="L22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>14.836074583680002</v>
+        <v>16.728431035680003</v>
       </c>
       <c r="M22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>18.174284814</v>
+        <v>19.27553850768</v>
       </c>
       <c r="N22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>19.804540719600002</v>
+        <v>18.861467352000002</v>
       </c>
       <c r="O22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>17.489799045179996</v>
+        <v>15.96695399145</v>
       </c>
       <c r="P22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.906176496000002</v>
+        <v>16.897031550000001</v>
       </c>
       <c r="Q22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.343892928000002</v>
+        <v>16.788776178719999</v>
       </c>
       <c r="R22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>13.945243435200005</v>
+        <v>15.431138331840001</v>
       </c>
       <c r="S22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>14.040965418480003</v>
+        <v>14.462358028650005</v>
       </c>
       <c r="T22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>12.672439400249996</v>
+        <v>12.551749501199998</v>
       </c>
       <c r="U22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>11.581511256000001</v>
+        <v>10.683376412519999</v>
       </c>
       <c r="V22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>9.4247553392999972</v>
+        <v>9.0621622060199982</v>
       </c>
       <c r="W22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>9.8278628448000003</v>
+        <v>10.046701896</v>
       </c>
       <c r="X22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>11.322657484320002</v>
+        <v>10.355496207420002</v>
       </c>
       <c r="Y22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>11.613744071999999</v>
+        <v>11.159441730360001</v>
       </c>
       <c r="Z22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>8.6799411614999986</v>
+        <v>9.1220449319999997</v>
       </c>
       <c r="AA22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>9.8922474000000022</v>
+        <v>9.0396298860000019</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.3">
@@ -71464,99 +71465,99 @@
       </c>
       <c r="D23" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>5.0386041893250004</v>
+        <v>5.3527123707750004</v>
       </c>
       <c r="E23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>5.2656635937359999</v>
+        <v>5.0610501789120015</v>
       </c>
       <c r="F23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.3454231352000008</v>
+        <v>4.5305664767999998</v>
       </c>
       <c r="G23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.4276414582400001</v>
+        <v>4.6535415326399994</v>
       </c>
       <c r="H23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>3.5876813414400006</v>
+        <v>3.5503096608000004</v>
       </c>
       <c r="I23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>3.0812293008</v>
+        <v>2.9289803235840002</v>
       </c>
       <c r="J23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>3.6927316462679998</v>
+        <v>3.5102962274940008</v>
       </c>
       <c r="K23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.56778384683999983</v>
+        <v>0.5560769633999999</v>
       </c>
       <c r="L23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.60435604320000014</v>
+        <v>0.6041259000000001</v>
       </c>
       <c r="M23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.78993148743599972</v>
+        <v>0.87226399669499988</v>
       </c>
       <c r="N23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.49862940783600007</v>
+        <v>0.54461949885000005</v>
       </c>
       <c r="O23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.61122283160399993</v>
+        <v>0.63579764539200001</v>
       </c>
       <c r="P23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.9926956513740004</v>
+        <v>0.9716497954800003</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.6846013016000003</v>
+        <v>1.8286790445000003</v>
       </c>
       <c r="R23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.9712869767360002</v>
+        <v>1.9127109294719999</v>
       </c>
       <c r="S23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.9768239539999997</v>
+        <v>1.8826894799999996</v>
       </c>
       <c r="T23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.1197905075000001</v>
+        <v>1.0138685760000001</v>
       </c>
       <c r="U23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.9235119679999997</v>
+        <v>2.0867573916</v>
       </c>
       <c r="V23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.2732013671300002</v>
+        <v>1.3255745580000002</v>
       </c>
       <c r="W23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.8511786082799998</v>
+        <v>0.91407803759999984</v>
       </c>
       <c r="X23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.3606040448000001</v>
+        <v>1.3606040448000005</v>
       </c>
       <c r="Y23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.8752423158360001</v>
+        <v>0.85808070180000018</v>
       </c>
       <c r="Z23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>3.9107270251350008</v>
+        <v>3.7952566545600006</v>
       </c>
       <c r="AA23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.4934876063000004</v>
+        <v>4.8611365922700012</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.3">
@@ -71571,99 +71572,99 @@
       </c>
       <c r="D24" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-10.516688784000003</v>
+        <v>-10.948240800000001</v>
       </c>
       <c r="E24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-12.564624190607999</v>
+        <v>-11.472888293999999</v>
       </c>
       <c r="F24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-13.171198982634003</v>
+        <v>-14.268456005034004</v>
       </c>
       <c r="G24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-14.946185888298002</v>
+        <v>-14.943284279700002</v>
       </c>
       <c r="H24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-16.114747521599998</v>
+        <v>-16.438783561200001</v>
       </c>
       <c r="I24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-17.215538437125005</v>
+        <v>-19.397170288125004</v>
       </c>
       <c r="J24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-15.647617709010001</v>
+        <v>-14.727169608480001</v>
       </c>
       <c r="K24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-19.027112304782403</v>
+        <v>-19.215499555324801</v>
       </c>
       <c r="L24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-15.280185485375993</v>
+        <v>-16.888626062783995</v>
       </c>
       <c r="M24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-23.152849636089599</v>
+        <v>-25.101941569739996</v>
       </c>
       <c r="N24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-23.130671355792011</v>
+        <v>-23.602450783212007</v>
       </c>
       <c r="O24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-21.3675569243136</v>
+        <v>-20.130662603519998</v>
       </c>
       <c r="P24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-20.494508959411199</v>
+        <v>-20.504973884329196</v>
       </c>
       <c r="Q24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-18.417753430965</v>
+        <v>-19.199360030860802</v>
       </c>
       <c r="R24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-19.229926591260003</v>
+        <v>-20.803284221454</v>
       </c>
       <c r="S24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-16.446635807783998</v>
+        <v>-16.466199609299998</v>
       </c>
       <c r="T24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-15.3987109468416</v>
+        <v>-16.181278489958402</v>
       </c>
       <c r="U24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-14.619882709152002</v>
+        <v>-14.329805671272002</v>
       </c>
       <c r="V24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-9.6644115559530004</v>
+        <v>-9.1906658914454979</v>
       </c>
       <c r="W24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-9.9928967657903982</v>
+        <v>-9.6989880373847992</v>
       </c>
       <c r="X24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-12.125815058069998</v>
+        <v>-11.311766409446996</v>
       </c>
       <c r="Y24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-11.902377543839998</v>
+        <v>-12.522293040914999</v>
       </c>
       <c r="Z24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-9.1826332415999996</v>
+        <v>-10.246288258751999</v>
       </c>
       <c r="AA24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-9.7523870152800001</v>
+        <v>-9.8668887251759987</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.3">
@@ -71678,99 +71679,99 @@
       </c>
       <c r="D25" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>10.541864232238497</v>
+        <v>11.316435809489999</v>
       </c>
       <c r="E25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>12.101991270969597</v>
+        <v>11.871611483759995</v>
       </c>
       <c r="F25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>12.287203575569999</v>
+        <v>12.276967438049999</v>
       </c>
       <c r="G25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>13.74590520576</v>
+        <v>12.688527882240001</v>
       </c>
       <c r="H25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>13.632361616159999</v>
+        <v>15.396197877899999</v>
       </c>
       <c r="I25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.651773537400002</v>
+        <v>15.981284559240002</v>
       </c>
       <c r="J25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>14.0581874475</v>
+        <v>14.33935119645</v>
       </c>
       <c r="K25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16.034855941843205</v>
+        <v>16.692645332160001</v>
       </c>
       <c r="L25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>17.399208319365599</v>
+        <v>16.2167378510592</v>
       </c>
       <c r="M25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>18.3272367159</v>
+        <v>19.060326184536002</v>
       </c>
       <c r="N25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>17.932902805440001</v>
+        <v>17.215586693222402</v>
       </c>
       <c r="O25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>18.177116570266502</v>
+        <v>17.31153959073</v>
       </c>
       <c r="P25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.896333565000003</v>
+        <v>16.3638727875</v>
       </c>
       <c r="Q25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.791423138399999</v>
+        <v>13.847863367519999</v>
       </c>
       <c r="R25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>17.174668230720002</v>
+        <v>15.422151064320003</v>
       </c>
       <c r="S25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>14.751605189223001</v>
+        <v>13.222727340480001</v>
       </c>
       <c r="T25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>12.948120538079998</v>
+        <v>13.456796702075996</v>
       </c>
       <c r="U25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>11.690377461806399</v>
+        <v>12.04590714852</v>
       </c>
       <c r="V25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>8.7066787420199976</v>
+        <v>8.435133810956998</v>
       </c>
       <c r="W25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>10.239598572403201</v>
+        <v>10.451583982408801</v>
       </c>
       <c r="X25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>10.045793197440002</v>
+        <v>10.996042364580001</v>
       </c>
       <c r="Y25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>10.815640747758003</v>
+        <v>11.361885229968003</v>
       </c>
       <c r="Z25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>8.580250748160001</v>
+        <v>8.4908731361999994</v>
       </c>
       <c r="AA25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>9.7989211116720032</v>
+        <v>9.1264461334200035</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.3">
@@ -71785,63 +71786,63 @@
       </c>
       <c r="D26" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>4.6961747784000023</v>
+        <v>5.2910235836640016</v>
       </c>
       <c r="E26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>5.2197299700000004</v>
+        <v>5.164400832318</v>
       </c>
       <c r="F26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.5309759703084795</v>
+        <v>4.354571394431999</v>
       </c>
       <c r="G26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.5521772616319991</v>
+        <v>4.2428059914239995</v>
       </c>
       <c r="H26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>3.5214800785920004</v>
+        <v>3.3806208754483205</v>
       </c>
       <c r="I26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2.7848512918195198</v>
+        <v>2.9536301579903999</v>
       </c>
       <c r="J26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>3.7958878697670007</v>
+        <v>4.1554982995344005</v>
       </c>
       <c r="K26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.59623773511680001</v>
+        <v>0.67969549100879989</v>
       </c>
       <c r="L26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.55752190200000018</v>
+        <v>0.54079624494000023</v>
       </c>
       <c r="M26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.83789161345889984</v>
+        <v>0.76582804903604984</v>
       </c>
       <c r="N26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.47911844516381996</v>
+        <v>0.49363718592636002</v>
       </c>
       <c r="O26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.6677146387674</v>
+        <v>0.6159683128872</v>
       </c>
       <c r="P26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.0849748453107204</v>
+        <v>1.0202322852540002</v>
       </c>
       <c r="Q26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.8103922540550001</v>
+        <v>1.7383422997017002</v>
       </c>
       <c r="R26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.9486685030399999</v>
+        <v>2.1952968604559997</v>
       </c>
       <c r="S26" s="1">
         <f t="shared" ca="1" si="2"/>
@@ -71849,35 +71850,35 @@
       </c>
       <c r="T26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.96366696457500001</v>
+        <v>0.9640604184749999</v>
       </c>
       <c r="U26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>2.2154133455999996</v>
+        <v>1.9235119679999997</v>
       </c>
       <c r="V26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.2704072638950001</v>
+        <v>1.3754785413600004</v>
       </c>
       <c r="W26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.92249841587903969</v>
+        <v>0.93217497268895966</v>
       </c>
       <c r="X26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1.3857752196288002</v>
+        <v>1.3453652794982403</v>
       </c>
       <c r="Y26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0.82391742663551992</v>
+        <v>0.79080717477887996</v>
       </c>
       <c r="Z26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.0671561061403994</v>
+        <v>4.1090855505335995</v>
       </c>
       <c r="AA26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>4.4836836333408003</v>
+        <v>4.5303886711880992</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.3">
@@ -71892,99 +71893,99 @@
       </c>
       <c r="D27" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>-9.8969439491999989</v>
+        <v>-10.072647269999999</v>
       </c>
       <c r="E27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-11.018561917557598</v>
+        <v>-12.312148187792877</v>
       </c>
       <c r="F27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-13.16853813435468</v>
+        <v>-13.836411052463999</v>
       </c>
       <c r="G27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-13.495961911017602</v>
+        <v>-12.835787922800643</v>
       </c>
       <c r="H27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-17.096528357999997</v>
+        <v>-14.849556059520001</v>
       </c>
       <c r="I27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-17.759187019350001</v>
+        <v>-17.414348436449998</v>
       </c>
       <c r="J27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-15.334665354829802</v>
+        <v>-14.879180245280402</v>
       </c>
       <c r="K27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-17.52680710995795</v>
+        <v>-19.004505834717307</v>
       </c>
       <c r="L27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-17.057512323411835</v>
+        <v>-16.550853541528312</v>
       </c>
       <c r="M27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-25.054690856196956</v>
+        <v>-26.359622671623882</v>
       </c>
       <c r="N27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-21.347075531900163</v>
+        <v>-22.912709260323968</v>
       </c>
       <c r="O27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-20.299179078097922</v>
+        <v>-21.529432355558402</v>
       </c>
       <c r="P27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-22.644255695766429</v>
+        <v>-19.481839104946175</v>
       </c>
       <c r="Q27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-18.797740764909118</v>
+        <v>-17.86715953892352</v>
       </c>
       <c r="R27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-18.451114564313979</v>
+        <v>-17.880918104630705</v>
       </c>
       <c r="S27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-16.627568365471134</v>
+        <v>-16.785546062712839</v>
       </c>
       <c r="T27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-16.16205320858419</v>
+        <v>-16.661910524313594</v>
       </c>
       <c r="U27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-14.915065102898691</v>
+        <v>-15.685915823361002</v>
       </c>
       <c r="V27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-8.7494056439327981</v>
+        <v>-9.8539098217559982</v>
       </c>
       <c r="W27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-9.2928641567222989</v>
+        <v>-8.5710882998894959</v>
       </c>
       <c r="X27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-10.975594886847361</v>
+        <v>-11.8832987569086</v>
       </c>
       <c r="Y27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-10.976341870352247</v>
+        <v>-10.883236466648698</v>
       </c>
       <c r="Z27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-8.8107365953152001</v>
+        <v>-9.2689499940710398</v>
       </c>
       <c r="AA27" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>-10.467904252085281</v>
+        <v>-10.465949826347398</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.3">
@@ -71999,99 +72000,99 @@
       </c>
       <c r="D28" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>10.023121012097652</v>
+        <v>9.9240088107021105</v>
       </c>
       <c r="E28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>11.979748934899197</v>
+        <v>11.984356530643391</v>
       </c>
       <c r="F28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>12.527983120384199</v>
+        <v>12.535429910429999</v>
       </c>
       <c r="G28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>12.79743774656256</v>
+        <v>12.668226237628414</v>
       </c>
       <c r="H28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16.169146802430294</v>
+        <v>17.139107268737995</v>
       </c>
       <c r="I28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.043762334600999</v>
+        <v>15.680288914289999</v>
       </c>
       <c r="J28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.374149736400001</v>
+        <v>14.180392227456002</v>
       </c>
       <c r="K28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>18.408847600765444</v>
+        <v>17.360351145446401</v>
       </c>
       <c r="L28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.257767295443681</v>
+        <v>15.392013427594124</v>
       </c>
       <c r="M28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>19.6284705227289</v>
+        <v>20.437891987583697</v>
       </c>
       <c r="N28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>20.602663710599884</v>
+        <v>18.271386345892683</v>
       </c>
       <c r="O28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>17.289437964941833</v>
+        <v>16.79545402308635</v>
       </c>
       <c r="P28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16.734623188499999</v>
+        <v>15.110867671199999</v>
       </c>
       <c r="Q28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>16.430945407383778</v>
+        <v>14.263299268545598</v>
       </c>
       <c r="R28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>15.40644851050906</v>
+        <v>15.881606542593794</v>
       </c>
       <c r="S28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>13.488504160023652</v>
+        <v>12.954305975468257</v>
       </c>
       <c r="T28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>12.41870095648728</v>
+        <v>12.685273691156974</v>
       </c>
       <c r="U28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>12.778298303150013</v>
+        <v>11.809667027743201</v>
       </c>
       <c r="V28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>8.6179051007474037</v>
+        <v>8.6143879473545883</v>
       </c>
       <c r="W28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>9.2628984008816637</v>
+        <v>9.0738596580065263</v>
       </c>
       <c r="X28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>10.778298951420004</v>
+        <v>11.549110634006405</v>
       </c>
       <c r="Y28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>10.920519688342322</v>
+        <v>11.356422785145902</v>
       </c>
       <c r="Z28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>8.6723189026656016</v>
+        <v>8.5820198720256027</v>
       </c>
       <c r="AA28" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>9.7047373068122411</v>
+        <v>9.5049534783218412</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.3">
@@ -72106,99 +72107,99 @@
       </c>
       <c r="D29" s="1">
         <f ca="1">D20*0.95*RANDBETWEEN(95,105)/100</f>
-        <v>4.2940648129995012</v>
+        <v>4.9378321055385008</v>
       </c>
       <c r="E29" s="1">
         <f t="shared" ref="E29:AA37" ca="1" si="4">E20*0.95*RANDBETWEEN(95,105)/100</f>
-        <v>4.9027433704704002</v>
+        <v>4.4825837403847508</v>
       </c>
       <c r="F29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.4345948391202503</v>
+        <v>4.1372825401467006</v>
       </c>
       <c r="G29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>3.959586138815999</v>
+        <v>3.7281460930559991</v>
       </c>
       <c r="H29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>3.4461672440831994</v>
+        <v>3.1479412325760006</v>
       </c>
       <c r="I29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>2.6690588023680011</v>
+        <v>3.2265760193100004</v>
       </c>
       <c r="J29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>3.4369078330471496</v>
+        <v>3.9082613284259997</v>
       </c>
       <c r="K29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.62155102800000006</v>
+        <v>0.60302880736559994</v>
       </c>
       <c r="L29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.51922450944000009</v>
+        <v>0.54571555583999998</v>
       </c>
       <c r="M29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.81159201170774975</v>
+        <v>0.78879822545159994</v>
       </c>
       <c r="N29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.4972957656975</v>
+        <v>0.45994783880430007</v>
       </c>
       <c r="O29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.58566441997349994</v>
+        <v>0.52497180351420003</v>
       </c>
       <c r="P29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.92384738302500025</v>
+        <v>0.88003606383000021</v>
       </c>
       <c r="Q29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.6530300682780503</v>
+        <v>1.7902231292399997</v>
       </c>
       <c r="R29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.7641508572799998</v>
+        <v>1.6749269752319997</v>
       </c>
       <c r="S29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.8423922651658995</v>
+        <v>1.6656444538964996</v>
       </c>
       <c r="T29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.87885305825624993</v>
+        <v>0.93427989278400003</v>
       </c>
       <c r="U29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>2.0435270928533997</v>
+        <v>1.8821564606879995</v>
       </c>
       <c r="V29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.2722485872096001</v>
+        <v>1.1051820070830001</v>
       </c>
       <c r="W29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.92967453762749996</v>
+        <v>0.82464127987499991</v>
       </c>
       <c r="X29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.3179030673536003</v>
+        <v>1.3848844045680002</v>
       </c>
       <c r="Y29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.7595528470991999</v>
+        <v>0.76016426839500018</v>
       </c>
       <c r="Z29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>3.56793659452125</v>
+        <v>3.9446244288360002</v>
       </c>
       <c r="AA29" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.3541894905046998</v>
+        <v>3.8554227022605003</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.3">
@@ -72213,99 +72214,99 @@
       </c>
       <c r="D30" s="1">
         <f t="shared" ref="D30:S37" ca="1" si="5">D21*0.95*RANDBETWEEN(95,105)/100</f>
-        <v>-10.934123681250004</v>
+        <v>-11.256625107</v>
       </c>
       <c r="E30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-10.469752931635201</v>
+        <v>-11.813599332542697</v>
       </c>
       <c r="F30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-12.263413213497602</v>
+        <v>-13.415764789350003</v>
       </c>
       <c r="G30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-12.952202614412254</v>
+        <v>-12.839635283428802</v>
       </c>
       <c r="H30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-14.853756782592002</v>
+        <v>-14.151185848800001</v>
       </c>
       <c r="I30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-15.749471779650001</v>
+        <v>-16.062917149382248</v>
       </c>
       <c r="J30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-15.456844967381999</v>
+        <v>-13.713765363144001</v>
       </c>
       <c r="K30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-17.366972974631278</v>
+        <v>-15.069321073411501</v>
       </c>
       <c r="L30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-15.277465711260472</v>
+        <v>-16.53746288332319</v>
       </c>
       <c r="M30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-21.132126614654993</v>
+        <v>-20.709574875601916</v>
       </c>
       <c r="N30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-22.210117364460487</v>
+        <v>-24.296640512130001</v>
       </c>
       <c r="O30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-20.0994354319878</v>
+        <v>-19.705328854889999</v>
       </c>
       <c r="P30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-21.718768405501443</v>
+        <v>-22.142579214319198</v>
       </c>
       <c r="Q30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-20.368096583759822</v>
+        <v>-19.006969485000003</v>
       </c>
       <c r="R30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-18.435044365290004</v>
+        <v>-16.681027826335953</v>
       </c>
       <c r="S30" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-15.969050806442576</v>
+        <v>-16.624340338221</v>
       </c>
       <c r="T30" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-15.382992360127771</v>
+        <v>-14.033237455408504</v>
       </c>
       <c r="U30" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-13.613315387708399</v>
+        <v>-13.762288614984</v>
       </c>
       <c r="V30" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-8.728404970319998</v>
+        <v>-8.9993492079403499</v>
       </c>
       <c r="W30" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-9.6879802313032197</v>
+        <v>-10.376826518298239</v>
       </c>
       <c r="X30" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-10.652356273038478</v>
+        <v>-10.120750534439999</v>
       </c>
       <c r="Y30" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-10.878925420316101</v>
+        <v>-10.863836758151999</v>
       </c>
       <c r="Z30" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-8.6483592381900003</v>
+        <v>-8.1221444118412514</v>
       </c>
       <c r="AA30" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-8.8276185877572004</v>
+        <v>-9.1730372915999983</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.3">
@@ -72320,99 +72321,99 @@
       </c>
       <c r="D31" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>11.179584697357436</v>
+        <v>11.287080704062795</v>
       </c>
       <c r="E31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>11.279115022895997</v>
+        <v>10.196085812219998</v>
       </c>
       <c r="F31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>11.189665717917748</v>
+        <v>12.752876179767359</v>
       </c>
       <c r="G31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>13.862609097463354</v>
+        <v>14.43112426161588</v>
       </c>
       <c r="H31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>14.3311315244916</v>
+        <v>13.2153717314304</v>
       </c>
       <c r="I31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>13.72540140972</v>
+        <v>15.648611562948002</v>
       </c>
       <c r="J31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>15.205335543216</v>
+        <v>14.345148387149996</v>
       </c>
       <c r="K31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>16.17877147339194</v>
+        <v>18.038489862065397</v>
       </c>
       <c r="L31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>13.81238543740608</v>
+        <v>16.368769768412882</v>
       </c>
       <c r="M31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>16.574947750368</v>
+        <v>18.311761582296</v>
       </c>
       <c r="N31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>18.626170546783801</v>
+        <v>18.276761864088002</v>
       </c>
       <c r="O31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>17.446074547567047</v>
+        <v>15.320292354796274</v>
       </c>
       <c r="P31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>14.35532428764</v>
+        <v>16.37322357195</v>
       </c>
       <c r="Q31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>15.159766212864001</v>
+        <v>16.268324117179681</v>
       </c>
       <c r="R31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>13.247981263440005</v>
+        <v>14.21979397279056</v>
       </c>
       <c r="S31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>13.605695490507122</v>
+        <v>14.151417331034029</v>
       </c>
       <c r="T31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>12.64075830174937</v>
+        <v>11.685678785617197</v>
       </c>
       <c r="U31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>11.222484407064</v>
+        <v>9.7432392882182395</v>
       </c>
       <c r="V31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>9.4011934509517463</v>
+        <v>8.6951446366761882</v>
       </c>
       <c r="W31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>9.709928490662401</v>
+        <v>9.3534794651759992</v>
       </c>
       <c r="X31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>10.43382887180088</v>
+        <v>9.7393441830785115</v>
       </c>
       <c r="Y31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>11.584709711819999</v>
+        <v>10.49545494740358</v>
       </c>
       <c r="Z31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>8.5757818675619983</v>
+        <v>8.3193049779840003</v>
       </c>
       <c r="AA31" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>9.8675167815000027</v>
+        <v>8.6735248756170016</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.3">
@@ -72427,99 +72428,99 @@
       </c>
       <c r="D32" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>4.9302741992545132</v>
+        <v>5.237629054803338</v>
       </c>
       <c r="E32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.9023328057682161</v>
+        <v>4.8079976699664009</v>
       </c>
       <c r="F32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.0455889388712007</v>
+        <v>4.2179573899007998</v>
       </c>
       <c r="G32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.3745097607411196</v>
+        <v>4.376655811447919</v>
       </c>
       <c r="H32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>3.4082972743680005</v>
+        <v>3.3727941777600008</v>
       </c>
       <c r="I32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>2.9271678357599997</v>
+        <v>2.9216578727750395</v>
       </c>
       <c r="J32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>3.5080950639546002</v>
+        <v>3.2013901594745291</v>
       </c>
       <c r="K32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.51781886831807977</v>
+        <v>0.5335558463822998</v>
       </c>
       <c r="L32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.58562100586080013</v>
+        <v>0.56818040894999999</v>
       </c>
       <c r="M32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.72041751654163177</v>
+        <v>0.81207778092304495</v>
       </c>
       <c r="N32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.47843491681864203</v>
+        <v>0.5380840648638</v>
       </c>
       <c r="O32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.60969477452498988</v>
+        <v>0.57380737496627998</v>
       </c>
       <c r="P32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.92419965142919436</v>
+        <v>0.95998999793424034</v>
       </c>
       <c r="Q32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.6643860859808004</v>
+        <v>1.7198726413522503</v>
       </c>
       <c r="R32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.9663587592941603</v>
+        <v>1.8170753829983999</v>
       </c>
       <c r="S32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.7840836184849997</v>
+        <v>1.8600972062399996</v>
       </c>
       <c r="T32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.0531629723037501</v>
+        <v>0.93427989278400003</v>
       </c>
       <c r="U32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.8821564606879995</v>
+        <v>1.9824195220199998</v>
       </c>
       <c r="V32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.2337321247489701</v>
+        <v>1.2592958301000001</v>
       </c>
       <c r="W32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.82479207142331967</v>
+        <v>0.84232291164839979</v>
       </c>
       <c r="X32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.3313510578368</v>
+        <v>1.3572025346880006</v>
       </c>
       <c r="Y32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.83979500204464219</v>
+        <v>0.83148020004420009</v>
       </c>
       <c r="Z32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>3.9009502075721634</v>
+        <v>3.6054938218320003</v>
       </c>
       <c r="AA32" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.0980606969456002</v>
+        <v>4.4333565721502417</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.3">
@@ -72534,99 +72535,99 @@
       </c>
       <c r="D33" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-9.4913116275600018</v>
+        <v>-10.192812184799999</v>
       </c>
       <c r="E33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-11.697665121456048</v>
+        <v>-10.572266562920998</v>
       </c>
       <c r="F33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-12.012133472162208</v>
+        <v>-12.877281544543189</v>
       </c>
       <c r="G33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-14.056887827944269</v>
+        <v>-14.622003667686451</v>
       </c>
       <c r="H33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-15.309010145519997</v>
+        <v>-16.085349714634201</v>
       </c>
       <c r="I33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-16.191213900116068</v>
+        <v>-18.243038655981564</v>
       </c>
       <c r="J33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-15.311193928266286</v>
+        <v>-14.13071923933656</v>
       </c>
       <c r="K33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-18.43727182333415</v>
+        <v>-18.802366314885315</v>
       </c>
       <c r="L33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-14.951661497440407</v>
+        <v>-16.204636707241242</v>
       </c>
       <c r="M33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-21.995207154285119</v>
+        <v>-23.369907601427936</v>
       </c>
       <c r="N33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-22.193879165882432</v>
+        <v>-22.646551526491923</v>
       </c>
       <c r="O33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-20.299179078097918</v>
+        <v>-18.741646883877117</v>
       </c>
       <c r="P33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-19.85917918166945</v>
+        <v>-20.453711449618371</v>
       </c>
       <c r="Q33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-17.49686575941675</v>
+        <v>-17.874604188731407</v>
       </c>
       <c r="R33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-18.999167472164881</v>
+        <v>-20.751276010900366</v>
       </c>
       <c r="S33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-15.311817937046902</v>
+        <v>-14.860745147393249</v>
       </c>
       <c r="T33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-15.360214169474496</v>
+        <v>-15.9871031480789</v>
       </c>
       <c r="U33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-13.472221916483567</v>
+        <v>-13.749448541585485</v>
       </c>
       <c r="V33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-8.9057552488106886</v>
+        <v>-8.818443922841956</v>
       </c>
       <c r="W33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-9.5881844467758874</v>
+        <v>-9.3983194082258699</v>
       </c>
       <c r="X33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-12.095500520424821</v>
+        <v>-10.6387163080849</v>
       </c>
       <c r="Y33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-10.854968319982079</v>
+        <v>-12.134101956646635</v>
       </c>
       <c r="Z33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-9.1596766584959983</v>
+        <v>-10.025993061188831</v>
       </c>
       <c r="AA33" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-9.1721199878708397</v>
+        <v>-8.9048670744713387</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.3">
@@ -72641,99 +72642,99 @@
       </c>
       <c r="D34" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>9.914623310420307</v>
+        <v>10.858120159205654</v>
       </c>
       <c r="E34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>11.496891707421117</v>
+        <v>10.714129364093397</v>
       </c>
       <c r="F34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>11.322658094887752</v>
+        <v>11.663119066147498</v>
       </c>
       <c r="G34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>13.58095434329088</v>
+        <v>11.933560473246718</v>
       </c>
       <c r="H34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>12.562221229291438</v>
+        <v>15.357707383205247</v>
       </c>
       <c r="I34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>15.612644103556502</v>
+        <v>15.030398127965222</v>
       </c>
       <c r="J34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>12.821066952119999</v>
+        <v>14.167278982092601</v>
       </c>
       <c r="K34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>14.471457487513492</v>
+        <v>15.382272673585442</v>
       </c>
       <c r="L34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>17.02512534049924</v>
+        <v>16.022136996846488</v>
       </c>
       <c r="M34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>17.410874880104998</v>
+        <v>18.650529171568479</v>
       </c>
       <c r="N34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>17.547345395123042</v>
+        <v>16.191259284975668</v>
       </c>
       <c r="O34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>17.786308564005775</v>
+        <v>16.281502985081563</v>
       </c>
       <c r="P34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>15.10151688675</v>
+        <v>15.545679148125</v>
       </c>
       <c r="Q34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>15.151870501294798</v>
+        <v>13.550134305118318</v>
       </c>
       <c r="R34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>16.315934819184001</v>
+        <v>15.237085251548162</v>
       </c>
       <c r="S34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>13.873884680464233</v>
+        <v>12.059127334517759</v>
       </c>
       <c r="T34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>12.792743091623038</v>
+        <v>13.039636004311639</v>
       </c>
       <c r="U34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>10.994800002828917</v>
+        <v>12.015792380648699</v>
       </c>
       <c r="V34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>8.5194851490665684</v>
+        <v>7.7729758067968735</v>
       </c>
       <c r="W34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>9.5330662709073799</v>
+        <v>9.9290047832883594</v>
       </c>
       <c r="X34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>9.9252436790707232</v>
+        <v>10.132853038960469</v>
       </c>
       <c r="Y34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>9.7611157748515964</v>
+        <v>10.9017288781543</v>
       </c>
       <c r="Z34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>8.2327505928595208</v>
+        <v>8.3083193637716981</v>
       </c>
       <c r="AA34" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>9.7744238088928235</v>
+        <v>9.0169287798189632</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.3">
@@ -72748,99 +72749,99 @@
       </c>
       <c r="D35" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>4.5059796998748025</v>
+        <v>4.825413508301569</v>
       </c>
       <c r="E35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.7108062979250001</v>
+        <v>5.151489830237205</v>
       </c>
       <c r="F35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.4335599869468476</v>
+        <v>4.2195796812046069</v>
       </c>
       <c r="G35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.1948313465938876</v>
+        <v>3.8291324072601589</v>
       </c>
       <c r="H35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>3.3119520139157768</v>
+        <v>3.2758216283094224</v>
       </c>
       <c r="I35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>2.6985209017731147</v>
+        <v>2.6937107040872443</v>
       </c>
       <c r="J35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>3.6782153458042233</v>
+        <v>4.0266778522488345</v>
       </c>
       <c r="K35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.57209010684456951</v>
+        <v>0.626339394964609</v>
       </c>
       <c r="L35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.52964580690000018</v>
+        <v>0.50348130403914015</v>
       </c>
       <c r="M35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.80395700311381435</v>
+        <v>0.74208737951593218</v>
       </c>
       <c r="N35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.45516252290562886</v>
+        <v>0.46426577336374159</v>
       </c>
       <c r="O35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.64067219589732038</v>
+        <v>0.58516989724283996</v>
       </c>
       <c r="P35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.0204188420147324</v>
+        <v>0.97891287770121305</v>
       </c>
       <c r="Q35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.6854751885252051</v>
+        <v>1.5688539254807841</v>
       </c>
       <c r="R35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.81421037633024</v>
+        <v>2.1480979779561955</v>
       </c>
       <c r="S35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.73233967007024</v>
+        <v>1.8373299531048</v>
       </c>
       <c r="T35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.96125779716356252</v>
+        <v>0.94333311947778742</v>
       </c>
       <c r="U35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>2.1256891051031994</v>
+        <v>1.7907896422079994</v>
       </c>
       <c r="V35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.1465425556652376</v>
+        <v>1.3328387065778404</v>
       </c>
       <c r="W35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.87637349508508766</v>
+        <v>0.92098887301669208</v>
       </c>
       <c r="X35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>1.3296513232338338</v>
+        <v>1.316439925989028</v>
       </c>
       <c r="Y35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>0.78272155530374388</v>
+        <v>0.72121614339833851</v>
       </c>
       <c r="Z35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>3.9797122498583803</v>
+        <v>3.7084497093565734</v>
       </c>
       <c r="AA35" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>4.1743094626402852</v>
+        <v>4.2177918528761209</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.3">
@@ -72855,99 +72856,99 @@
       </c>
       <c r="D36" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>-9.4020967517399985</v>
+        <v>-9.3776346083699984</v>
       </c>
       <c r="E36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-10.991015512763704</v>
+        <v>-11.345644555051136</v>
       </c>
       <c r="F36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-12.635212339913314</v>
+        <v>-13.538928214836023</v>
       </c>
       <c r="G36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-12.949375453621389</v>
+        <v>-11.706238585594187</v>
       </c>
       <c r="H36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-16.566535978901996</v>
+        <v>-14.671361386805762</v>
       </c>
       <c r="I36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-17.20865222175015</v>
+        <v>-16.70906732477377</v>
       </c>
       <c r="J36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-14.859290728830077</v>
+        <v>-13.428460171365561</v>
       </c>
       <c r="K36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-17.482990092183055</v>
+        <v>-18.41536615384107</v>
       </c>
       <c r="L36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-15.718497606024005</v>
+        <v>-15.723310864451896</v>
       </c>
       <c r="M36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-23.563936750253234</v>
+        <v>-24.54080870728183</v>
       </c>
       <c r="N36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-21.293707843070411</v>
+        <v>-21.114061583388537</v>
       </c>
       <c r="O36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-19.091377922951093</v>
+        <v>-21.475608774669503</v>
       </c>
       <c r="P36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-20.866681623648766</v>
+        <v>-18.877902092692842</v>
       </c>
       <c r="Q36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-18.393589338463574</v>
+        <v>-17.313277593216888</v>
       </c>
       <c r="R36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-16.652130894293364</v>
+        <v>-17.496478365381144</v>
       </c>
       <c r="S36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-15.006380449837698</v>
+        <v>-15.467880696789882</v>
       </c>
       <c r="T36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-14.893332031710331</v>
+        <v>-16.30367944804085</v>
       </c>
       <c r="U36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-14.594391203186369</v>
+        <v>-15.050636232514881</v>
       </c>
       <c r="V36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-8.3950547153535187</v>
+        <v>-8.8931536141347873</v>
       </c>
       <c r="W36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-9.1813497868416309</v>
+        <v>-7.9796832071971213</v>
       </c>
       <c r="X36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-10.322546991079941</v>
+        <v>-11.853590510016327</v>
       </c>
       <c r="Y36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-10.218974281297941</v>
+        <v>-10.545856136182588</v>
       </c>
       <c r="Z36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-8.2864977678939447</v>
+        <v>-9.0696675691985131</v>
       </c>
       <c r="AA36" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>-9.6461737682965865</v>
+        <v>-9.9426523350300275</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.3">
@@ -72962,99 +72963,99 @@
       </c>
       <c r="D37" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>9.8076239103375524</v>
+        <v>9.2392522027636659</v>
       </c>
       <c r="E37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>10.925531028628068</v>
+        <v>11.612841478193445</v>
       </c>
       <c r="F37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>11.66355228507769</v>
+        <v>12.146831583206668</v>
       </c>
       <c r="G37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>12.035990200642086</v>
+        <v>11.433074179459643</v>
       </c>
       <c r="H37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>16.128723935424219</v>
+        <v>15.630865829089053</v>
       </c>
       <c r="I37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>14.434489960049659</v>
+        <v>14.151460745146723</v>
       </c>
       <c r="J37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>13.875170137101001</v>
+        <v>12.797803985279041</v>
       </c>
       <c r="K37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>18.187941429556258</v>
+        <v>16.657256924055822</v>
       </c>
       <c r="L37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>15.074674087898357</v>
+        <v>13.891292118403696</v>
       </c>
       <c r="M37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>19.019987936524302</v>
+        <v>19.027677440440424</v>
       </c>
       <c r="N37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>20.159706440821989</v>
+        <v>16.837082517740107</v>
       </c>
       <c r="O37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>17.081964709362531</v>
+        <v>16.753465388028633</v>
       </c>
       <c r="P37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>15.102997427621247</v>
+        <v>14.355324287639998</v>
       </c>
       <c r="Q37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>15.765492118384735</v>
+        <v>13.008128932913586</v>
       </c>
       <c r="R37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>14.782487345833442</v>
+        <v>14.333149904690899</v>
       </c>
       <c r="S37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>13.454782899623591</v>
+        <v>12.67578839699569</v>
       </c>
       <c r="T37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>11.915743567749544</v>
+        <v>11.689479706401151</v>
       </c>
       <c r="U37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>12.260777221872436</v>
+        <v>10.882608166065358</v>
       </c>
       <c r="V37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>7.8595294518816319</v>
+        <v>8.1836685499868587</v>
       </c>
       <c r="W37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>8.8877510156459554</v>
+        <v>8.7063683418572619</v>
       </c>
       <c r="X37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>10.751353204041452</v>
+        <v>10.42307234719078</v>
       </c>
       <c r="Y37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>9.9595139557681982</v>
+        <v>10.788601645888606</v>
       </c>
       <c r="Z37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>8.1563159279569977</v>
+        <v>8.4790356335612937</v>
       </c>
       <c r="AA37" s="1">
         <f t="shared" ca="1" si="4"/>
-        <v>9.6804754635452106</v>
+        <v>8.8491116883176328</v>
       </c>
     </row>
   </sheetData>

--- a/data/CS7/case33_3/case33_3_operational_data.xlsx
+++ b/data/CS7/case33_3/case33_3_operational_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\case33_1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/CS7/case33_3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1BF1AD7-FFA8-4ECA-9F99-53B30C515317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33205F2F-09C2-6A4B-9FF6-2DE23C0AABA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38010" yWindow="-12540" windowWidth="23250" windowHeight="13890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1120" yWindow="620" windowWidth="29400" windowHeight="19120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -442,13 +442,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59B7BE64-82AA-46B6-895E-9570C0781B75}">
   <dimension ref="A1:F35"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -468,15 +468,17 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>4</v>
+        <f>E2*1.25</f>
+        <v>5</v>
       </c>
       <c r="C2" s="1">
-        <v>2.88</v>
+        <f>F2*1</f>
+        <v>2.4</v>
       </c>
       <c r="D2" s="2">
         <v>2.6917900403768499E-2</v>
@@ -488,15 +490,17 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" ref="B3:B33" si="0">E3*1.25</f>
+        <v>4.5</v>
       </c>
       <c r="C3" s="1">
-        <v>1.92</v>
+        <f t="shared" ref="C3:C17" si="1">F3*1</f>
+        <v>1.6</v>
       </c>
       <c r="D3" s="2">
         <v>2.4226110363391645E-2</v>
@@ -508,15 +512,17 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>4.8</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="C4" s="1">
-        <v>3.84</v>
+        <f t="shared" si="1"/>
+        <v>3.2</v>
       </c>
       <c r="D4" s="2">
         <v>3.2301480484522194E-2</v>
@@ -528,15 +534,17 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>1.44</v>
+        <f t="shared" si="1"/>
+        <v>1.2</v>
       </c>
       <c r="D5" s="2">
         <v>1.6150740242261097E-2</v>
@@ -548,15 +556,17 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>0.96</v>
+        <f t="shared" si="1"/>
+        <v>0.8</v>
       </c>
       <c r="D6" s="2">
         <v>1.6150740242261097E-2</v>
@@ -568,15 +578,17 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="C7" s="1">
-        <v>4.8</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="D7" s="2">
         <v>5.3835800807536999E-2</v>
@@ -588,15 +600,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="C8" s="1">
-        <v>4.8</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="D8" s="2">
         <v>5.3835800807536999E-2</v>
@@ -608,15 +622,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="C9" s="1">
-        <v>0.96</v>
+        <f t="shared" si="1"/>
+        <v>0.8</v>
       </c>
       <c r="D9" s="2">
         <v>1.6150740242261097E-2</v>
@@ -628,15 +644,17 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="C10" s="1">
-        <v>0.96</v>
+        <f t="shared" si="1"/>
+        <v>0.8</v>
       </c>
       <c r="D10" s="2">
         <v>1.6150740242261097E-2</v>
@@ -648,15 +666,17 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <v>1.7999999999999998</v>
+        <f t="shared" si="0"/>
+        <v>2.25</v>
       </c>
       <c r="C11" s="1">
-        <v>1.44</v>
+        <f t="shared" si="1"/>
+        <v>1.2</v>
       </c>
       <c r="D11" s="2">
         <v>1.2113055181695823E-2</v>
@@ -668,15 +688,17 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="C12" s="1">
-        <v>1.6800000000000002</v>
+        <f t="shared" si="1"/>
+        <v>1.4000000000000001</v>
       </c>
       <c r="D12" s="2">
         <v>1.6150740242261097E-2</v>
@@ -688,15 +710,17 @@
         <v>1.4000000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="C13" s="1">
-        <v>1.6800000000000002</v>
+        <f t="shared" si="1"/>
+        <v>1.4000000000000001</v>
       </c>
       <c r="D13" s="2">
         <v>1.6150740242261097E-2</v>
@@ -708,15 +732,17 @@
         <v>1.4000000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" s="1">
-        <v>4.8</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="C14" s="1">
-        <v>3.84</v>
+        <f t="shared" si="1"/>
+        <v>3.2</v>
       </c>
       <c r="D14" s="2">
         <v>3.2301480484522194E-2</v>
@@ -728,15 +754,17 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="C15" s="1">
-        <v>0.48</v>
+        <f t="shared" si="1"/>
+        <v>0.4</v>
       </c>
       <c r="D15" s="2">
         <v>1.6150740242261097E-2</v>
@@ -748,15 +776,17 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="C16" s="1">
-        <v>0.96</v>
+        <f t="shared" si="1"/>
+        <v>0.8</v>
       </c>
       <c r="D16" s="2">
         <v>1.6150740242261097E-2</v>
@@ -768,15 +798,17 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="C17" s="1">
-        <v>0.96</v>
+        <f t="shared" si="1"/>
+        <v>0.8</v>
       </c>
       <c r="D17" s="2">
         <v>1.6150740242261097E-2</v>
@@ -788,15 +820,17 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>4.5</v>
       </c>
       <c r="C18" s="1">
-        <v>1.92</v>
+        <f>F18*0.5</f>
+        <v>0.8</v>
       </c>
       <c r="D18" s="2">
         <v>2.4226110363391645E-2</v>
@@ -808,15 +842,17 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>4.5</v>
       </c>
       <c r="C19" s="1">
-        <v>1.92</v>
+        <f t="shared" ref="C19:C33" si="2">F19*0.5</f>
+        <v>0.8</v>
       </c>
       <c r="D19" s="2">
         <v>2.4226110363391645E-2</v>
@@ -828,15 +864,17 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>4.5</v>
       </c>
       <c r="C20" s="1">
-        <v>1.92</v>
+        <f t="shared" si="2"/>
+        <v>0.8</v>
       </c>
       <c r="D20" s="2">
         <v>2.4226110363391645E-2</v>
@@ -848,15 +886,17 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>4.5</v>
       </c>
       <c r="C21" s="1">
-        <v>1.92</v>
+        <f t="shared" si="2"/>
+        <v>0.8</v>
       </c>
       <c r="D21" s="2">
         <v>2.4226110363391645E-2</v>
@@ -868,15 +908,17 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>4.5</v>
       </c>
       <c r="C22" s="1">
-        <v>1.92</v>
+        <f t="shared" si="2"/>
+        <v>0.8</v>
       </c>
       <c r="D22" s="2">
         <v>2.4226110363391645E-2</v>
@@ -888,15 +930,17 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>4.5</v>
       </c>
       <c r="C23" s="1">
-        <v>2.4</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="D23" s="2">
         <v>2.4226110363391645E-2</v>
@@ -908,15 +952,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" s="1">
-        <v>16.8</v>
+        <f t="shared" si="0"/>
+        <v>21</v>
       </c>
       <c r="C24" s="1">
-        <v>9.6</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="D24" s="2">
         <v>0.11305518169582769</v>
@@ -928,15 +974,17 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" s="1">
-        <v>16.8</v>
+        <f t="shared" si="0"/>
+        <v>21</v>
       </c>
       <c r="C25" s="1">
-        <v>9.6</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="D25" s="2">
         <v>0.11305518169582769</v>
@@ -948,15 +996,17 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="C26" s="1">
-        <v>1.2</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="D26" s="2">
         <v>1.6150740242261097E-2</v>
@@ -968,15 +1018,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="C27" s="1">
-        <v>1.2</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="D27" s="2">
         <v>1.6150740242261097E-2</v>
@@ -988,15 +1040,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="C28" s="1">
-        <v>0.96</v>
+        <f t="shared" si="2"/>
+        <v>0.4</v>
       </c>
       <c r="D28" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1008,15 +1062,17 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" s="1">
-        <v>4.8</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="C29" s="1">
-        <v>3.3600000000000003</v>
+        <f t="shared" si="2"/>
+        <v>1.4000000000000001</v>
       </c>
       <c r="D29" s="2">
         <v>3.2301480484522194E-2</v>
@@ -1028,15 +1084,17 @@
         <v>2.8000000000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" s="1">
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="C30" s="1">
-        <v>6</v>
+        <f t="shared" si="2"/>
+        <v>12</v>
       </c>
       <c r="D30" s="2">
         <v>5.3835800807536999E-2</v>
@@ -1048,15 +1106,17 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" s="1">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>7.5</v>
       </c>
       <c r="C31" s="1">
-        <v>3.3600000000000003</v>
+        <f t="shared" si="2"/>
+        <v>1.4000000000000001</v>
       </c>
       <c r="D31" s="2">
         <v>4.0376850605652742E-2</v>
@@ -1068,15 +1128,17 @@
         <v>2.8000000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" s="1">
-        <v>8.4</v>
+        <f t="shared" si="0"/>
+        <v>10.5</v>
       </c>
       <c r="C32" s="1">
-        <v>4.8</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
       <c r="D32" s="2">
         <v>5.6527590847913846E-2</v>
@@ -1088,15 +1150,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="C33" s="1">
-        <v>1.92</v>
+        <f t="shared" si="2"/>
+        <v>0.8</v>
       </c>
       <c r="D33" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1108,11 +1172,11 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
     </row>
@@ -1125,12 +1189,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD68AE75-D6B1-4AA7-B0E5-5751542FB30D}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1138,7 +1202,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1146,7 +1210,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -1154,10 +1218,10 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" s="2"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B7" s="2"/>
     </row>
   </sheetData>
@@ -1168,9 +1232,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{206E5596-3B52-412C-A9A4-71C002FACF4D}">
   <dimension ref="A1:AA385"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1253,7 +1317,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1336,7 +1400,7 @@
         <v>0.30423493001908397</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1419,7 +1483,7 @@
         <v>0.12215315627057644</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1502,7 +1566,7 @@
         <v>0.28807338371711955</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1585,7 +1649,7 @@
         <v>5.140697371227413E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1668,7 +1732,7 @@
         <v>0.31988431141736134</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1751,7 +1815,7 @@
         <v>0.45601221277188941</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1834,7 +1898,7 @@
         <v>0.23212504519623703</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1917,7 +1981,7 @@
         <v>0.16447266993333343</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2000,7 +2064,7 @@
         <v>0.14884669085844837</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2083,7 +2147,7 @@
         <v>0.21182466623223417</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2166,7 +2230,7 @@
         <v>8.8097283050149661E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2249,7 +2313,7 @@
         <v>0.37751283536620156</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2332,7 +2396,7 @@
         <v>0.71253728546098483</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2415,7 +2479,7 @@
         <v>0.29519824892940821</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2498,7 +2562,7 @@
         <v>0.1208807275594246</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2581,7 +2645,7 @@
         <v>0.29717043793976544</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2664,7 +2728,7 @@
         <v>5.090787688011613E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2747,7 +2811,7 @@
         <v>0.33620493955090019</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2830,7 +2894,7 @@
         <v>0.47011568326998909</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2913,7 +2977,7 @@
         <v>0.22743565034378779</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2996,7 +3060,7 @@
         <v>0.16275941295486118</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3079,7 +3143,7 @@
         <v>0.15970009540021024</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3162,7 +3226,7 @@
         <v>0.21390137864627567</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3245,7 +3309,7 @@
         <v>8.3063152590141104E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3328,7 +3392,7 @@
         <v>0.38918849006824902</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3411,7 +3475,7 @@
         <v>0.764493129192515</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3494,7 +3558,7 @@
         <v>0.31025938407886783</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3577,7 +3641,7 @@
         <v>0.12724287111518379</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3660,7 +3724,7 @@
         <v>0.28807338371711955</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3743,7 +3807,7 @@
         <v>5.240516737659013E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3826,7 +3890,7 @@
         <v>0.33620493955090019</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3909,7 +3973,7 @@
         <v>0.47951799693538888</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>1</v>
       </c>
@@ -3992,7 +4056,7 @@
         <v>0.3164043272198474</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>2</v>
       </c>
@@ -4075,7 +4139,7 @@
         <v>0.13497923767898695</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>3</v>
       </c>
@@ -4158,7 +4222,7 @@
         <v>0.32167183731275839</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>4</v>
       </c>
@@ -4241,7 +4305,7 @@
         <v>5.1387009838987807E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>5</v>
       </c>
@@ -4324,7 +4388,7 @@
         <v>0.33607437452583194</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>6</v>
       </c>
@@ -4407,7 +4471,7 @@
         <v>0.47914190438877291</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>7</v>
       </c>
@@ -4490,7 +4554,7 @@
         <v>0.25360247362045452</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>8</v>
       </c>
@@ -4573,7 +4637,7 @@
         <v>0.17105157673066676</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>9</v>
       </c>
@@ -4656,7 +4720,7 @@
         <v>0.15480055849278632</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>10</v>
       </c>
@@ -4739,7 +4803,7 @@
         <v>0.20949874832850765</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>11</v>
       </c>
@@ -4822,7 +4886,7 @@
         <v>9.1621174372155653E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>12</v>
       </c>
@@ -4905,7 +4969,7 @@
         <v>0.40070846937426924</v>
       </c>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>13</v>
       </c>
@@ -4988,7 +5052,7 @@
         <v>0.7796345465085609</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>14</v>
       </c>
@@ -5071,7 +5135,7 @@
         <v>0.32266975944202259</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>15</v>
       </c>
@@ -5154,7 +5218,7 @@
         <v>0.12968593424059532</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>16</v>
       </c>
@@ -5237,7 +5301,7 @@
         <v>0.31851819184890778</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>17</v>
       </c>
@@ -5320,7 +5384,7 @@
         <v>4.9310767017210523E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>18</v>
       </c>
@@ -5403,7 +5467,7 @@
         <v>0.35644251843648839</v>
       </c>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>19</v>
       </c>
@@ -5486,7 +5550,7 @@
         <v>0.51336632613082811</v>
       </c>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>20</v>
       </c>
@@ -5569,7 +5633,7 @@
         <v>0.23653307635753931</v>
       </c>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>21</v>
       </c>
@@ -5652,7 +5716,7 @@
         <v>0.17283336398827787</v>
       </c>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>22</v>
       </c>
@@ -5735,7 +5799,7 @@
         <v>0.16286308758095228</v>
       </c>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>23</v>
       </c>
@@ -5818,7 +5882,7 @@
         <v>0.213818310149714</v>
       </c>
     </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>24</v>
       </c>
@@ -5901,7 +5965,7 @@
         <v>8.2895348241474168E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>25</v>
       </c>
@@ -5984,7 +6048,7 @@
         <v>0.40880358996768879</v>
       </c>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>26</v>
       </c>
@@ -6067,7 +6131,7 @@
         <v>0.81051116221187025</v>
       </c>
     </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>27</v>
       </c>
@@ -6150,7 +6214,7 @@
         <v>0.3070061788865846</v>
       </c>
     </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>28</v>
       </c>
@@ -6233,7 +6297,7 @@
         <v>0.12703928252139948</v>
       </c>
     </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>29</v>
       </c>
@@ -6316,7 +6380,7 @@
         <v>0.30905725545735607</v>
       </c>
     </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>30</v>
       </c>
@@ -6399,7 +6463,7 @@
         <v>5.0867949133543484E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>31</v>
       </c>
@@ -6482,7 +6546,7 @@
         <v>0.32589030257050366</v>
       </c>
     </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>32</v>
       </c>
@@ -6565,7 +6629,7 @@
         <v>0.47425270128276498</v>
       </c>
     </row>
-    <row r="66" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>1</v>
       </c>
@@ -6648,7 +6712,7 @@
         <v>0.28043833648293781</v>
       </c>
     </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>2</v>
       </c>
@@ -6731,7 +6795,7 @@
         <v>0.12594499382980892</v>
       </c>
     </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>3</v>
       </c>
@@ -6814,7 +6878,7 @@
         <v>0.30014214231916309</v>
       </c>
     </row>
-    <row r="69" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>4</v>
       </c>
@@ -6897,7 +6961,7 @@
         <v>5.1357064029058326E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>5</v>
       </c>
@@ -6980,7 +7044,7 @@
         <v>0.3134866251890141</v>
       </c>
     </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>6</v>
       </c>
@@ -7063,7 +7127,7 @@
         <v>0.47914190438877291</v>
       </c>
     </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>7</v>
       </c>
@@ -7146,7 +7210,7 @@
         <v>0.22518474081461215</v>
       </c>
     </row>
-    <row r="73" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>8</v>
       </c>
@@ -7229,7 +7293,7 @@
         <v>0.1729361594069862</v>
       </c>
     </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>9</v>
       </c>
@@ -7312,7 +7376,7 @@
         <v>0.14435028040543274</v>
       </c>
     </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>10</v>
       </c>
@@ -7395,7 +7459,7 @@
         <v>0.2035178165760681</v>
       </c>
     </row>
-    <row r="76" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>11</v>
       </c>
@@ -7478,7 +7542,7 @@
         <v>7.8112924304466036E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>12</v>
       </c>
@@ -7561,7 +7625,7 @@
         <v>0.38903281467222173</v>
       </c>
     </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>13</v>
       </c>
@@ -7644,7 +7708,7 @@
         <v>0.70556035787417926</v>
       </c>
     </row>
-    <row r="79" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>14</v>
       </c>
@@ -7727,7 +7791,7 @@
         <v>0.29224626644011414</v>
       </c>
     </row>
-    <row r="80" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>15</v>
       </c>
@@ -7810,7 +7874,7 @@
         <v>0.13093291437752413</v>
       </c>
     </row>
-    <row r="81" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>16</v>
       </c>
@@ -7893,7 +7957,7 @@
         <v>0.29122702918097015</v>
       </c>
     </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>17</v>
       </c>
@@ -7976,7 +8040,7 @@
         <v>5.0378834238028643E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>18</v>
       </c>
@@ -8059,7 +8123,7 @@
         <v>0.33587852698822945</v>
       </c>
     </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>19</v>
       </c>
@@ -8142,7 +8206,7 @@
         <v>0.4422848348204057</v>
       </c>
     </row>
-    <row r="85" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>20</v>
       </c>
@@ -8225,7 +8289,7 @@
         <v>0.22748254429231229</v>
       </c>
     </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>21</v>
       </c>
@@ -8308,7 +8372,7 @@
         <v>0.17629414308479177</v>
       </c>
     </row>
-    <row r="87" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>22</v>
       </c>
@@ -8391,7 +8455,7 @@
         <v>0.14890871031297273</v>
       </c>
     </row>
-    <row r="88" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>23</v>
       </c>
@@ -8474,7 +8538,7 @@
         <v>0.20555299474182878</v>
       </c>
     </row>
-    <row r="89" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>24</v>
       </c>
@@ -8557,7 +8621,7 @@
         <v>7.8112924304466036E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>25</v>
       </c>
@@ -8640,7 +8704,7 @@
         <v>0.38521876746955291</v>
       </c>
     </row>
-    <row r="91" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>26</v>
       </c>
@@ -8723,7 +8787,7 @@
         <v>0.72010799411900772</v>
       </c>
     </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>27</v>
       </c>
@@ -8806,7 +8870,7 @@
         <v>0.29519824892940821</v>
       </c>
     </row>
-    <row r="93" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>28</v>
       </c>
@@ -8889,7 +8953,7 @@
         <v>0.1184631130082361</v>
       </c>
     </row>
-    <row r="94" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>29</v>
       </c>
@@ -8972,7 +9036,7 @@
         <v>0.30311384669856073</v>
       </c>
     </row>
-    <row r="95" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>30</v>
       </c>
@@ -9055,7 +9119,7 @@
         <v>4.9889719342513801E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>31</v>
       </c>
@@ -9138,7 +9202,7 @@
         <v>0.3134866251890141</v>
       </c>
     </row>
-    <row r="97" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>32</v>
       </c>
@@ -9221,7 +9285,7 @@
         <v>0.47914190438877291</v>
       </c>
     </row>
-    <row r="98" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>1</v>
       </c>
@@ -9304,7 +9368,7 @@
         <v>0.40460512983649527</v>
       </c>
     </row>
-    <row r="99" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>2</v>
       </c>
@@ -9387,7 +9451,7 @@
         <v>0.12531670023913216</v>
       </c>
     </row>
-    <row r="100" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>3</v>
       </c>
@@ -9470,7 +9534,7 @@
         <v>0.29869072399109714</v>
       </c>
     </row>
-    <row r="101" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>4</v>
       </c>
@@ -9553,7 +9617,7 @@
         <v>4.4140186966755215E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>5</v>
       </c>
@@ -9636,7 +9700,7 @@
         <v>0.31506655879445489</v>
       </c>
     </row>
-    <row r="103" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>6</v>
       </c>
@@ -9719,7 +9783,7 @@
         <v>0.44456052640476812</v>
       </c>
     </row>
-    <row r="104" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>7</v>
       </c>
@@ -9802,7 +9866,7 @@
         <v>0.24397437503436967</v>
       </c>
     </row>
-    <row r="105" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>8</v>
       </c>
@@ -9885,7 +9949,7 @@
         <v>0.15382663214631914</v>
       </c>
     </row>
-    <row r="106" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>9</v>
       </c>
@@ -9968,7 +10032,7 @@
         <v>0.14269317780774657</v>
       </c>
     </row>
-    <row r="107" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>10</v>
       </c>
@@ -10051,7 +10115,7 @@
         <v>0.21685736810291287</v>
       </c>
     </row>
-    <row r="108" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>11</v>
       </c>
@@ -10134,7 +10198,7 @@
         <v>7.9818120109252197E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>12</v>
       </c>
@@ -10217,7 +10281,7 @@
         <v>0.45025918839909279</v>
       </c>
     </row>
-    <row r="110" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>13</v>
       </c>
@@ -10300,7 +10364,7 @@
         <v>0.78440506467065618</v>
       </c>
     </row>
-    <row r="111" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>14</v>
       </c>
@@ -10383,7 +10447,7 @@
         <v>0.4349917738149664</v>
       </c>
     </row>
-    <row r="112" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>15</v>
       </c>
@@ -10466,7 +10530,7 @@
         <v>0.12151477012193317</v>
       </c>
     </row>
-    <row r="113" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>16</v>
       </c>
@@ -10549,7 +10613,7 @@
         <v>0.29988121067334794</v>
       </c>
     </row>
-    <row r="114" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>17</v>
       </c>
@@ -10632,7 +10696,7 @@
         <v>4.4687934013653223E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>18</v>
       </c>
@@ -10715,7 +10779,7 @@
         <v>0.33018527981719359</v>
       </c>
     </row>
-    <row r="116" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>19</v>
       </c>
@@ -10798,7 +10862,7 @@
         <v>0.42311155071818235</v>
       </c>
     </row>
-    <row r="117" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>20</v>
       </c>
@@ -10881,7 +10945,7 @@
         <v>0.23439270222739572</v>
       </c>
     </row>
-    <row r="118" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>21</v>
       </c>
@@ -10964,7 +11028,7 @@
         <v>0.15708373083840152</v>
       </c>
     </row>
-    <row r="119" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>22</v>
       </c>
@@ -11047,7 +11111,7 @@
         <v>0.14033793264830885</v>
       </c>
     </row>
-    <row r="120" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>23</v>
       </c>
@@ -11130,7 +11194,7 @@
         <v>0.19882125121158906</v>
       </c>
     </row>
-    <row r="121" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>24</v>
       </c>
@@ -11213,7 +11277,7 @@
         <v>7.9720383742063805E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>25</v>
       </c>
@@ -11296,7 +11360,7 @@
         <v>0.42271478599915069</v>
       </c>
     </row>
-    <row r="123" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>26</v>
       </c>
@@ -11379,7 +11443,7 @@
         <v>0.7719433123864361</v>
       </c>
     </row>
-    <row r="124" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>27</v>
       </c>
@@ -11462,7 +11526,7 @@
         <v>0.42260815392379569</v>
       </c>
     </row>
-    <row r="125" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>28</v>
       </c>
@@ -11545,7 +11609,7 @@
         <v>0.12503041680988139</v>
       </c>
     </row>
-    <row r="126" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>29</v>
       </c>
@@ -11628,7 +11692,7 @@
         <v>0.30983513447948846</v>
       </c>
     </row>
-    <row r="127" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>30</v>
       </c>
@@ -11711,7 +11775,7 @@
         <v>4.7369169177349381E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>31</v>
       </c>
@@ -11794,7 +11858,7 @@
         <v>0.29376889231153613</v>
       </c>
     </row>
-    <row r="129" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>32</v>
       </c>
@@ -11877,7 +11941,7 @@
         <v>0.40276293406267627</v>
       </c>
     </row>
-    <row r="130" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>1</v>
       </c>
@@ -11960,7 +12024,7 @@
         <v>0.42689047219041887</v>
       </c>
     </row>
-    <row r="131" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>2</v>
       </c>
@@ -12043,7 +12107,7 @@
         <v>0.12033783871790973</v>
       </c>
     </row>
-    <row r="132" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>3</v>
       </c>
@@ -12126,7 +12190,7 @@
         <v>0.29665445719231714</v>
       </c>
     </row>
-    <row r="133" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>4</v>
       </c>
@@ -12209,7 +12273,7 @@
         <v>4.2953112347665981E-2</v>
       </c>
     </row>
-    <row r="134" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>5</v>
       </c>
@@ -12292,7 +12356,7 @@
         <v>0.3215536643614364</v>
       </c>
     </row>
-    <row r="135" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>6</v>
       </c>
@@ -12375,7 +12439,7 @@
         <v>0.44732388733607209</v>
       </c>
     </row>
-    <row r="136" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>7</v>
       </c>
@@ -12458,7 +12522,7 @@
         <v>0.21766051836345818</v>
       </c>
     </row>
-    <row r="137" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>8</v>
       </c>
@@ -12541,7 +12605,7 @@
         <v>0.13917647670381256</v>
       </c>
     </row>
-    <row r="138" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>9</v>
       </c>
@@ -12624,7 +12688,7 @@
         <v>0.13581314695342595</v>
       </c>
     </row>
-    <row r="139" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>10</v>
       </c>
@@ -12707,7 +12771,7 @@
         <v>0.18744030886223878</v>
       </c>
     </row>
-    <row r="140" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>11</v>
       </c>
@@ -12790,7 +12854,7 @@
         <v>7.5711443802736714E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>12</v>
       </c>
@@ -12873,7 +12937,7 @@
         <v>0.45877795420658402</v>
       </c>
     </row>
-    <row r="142" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>13</v>
       </c>
@@ -12956,7 +13020,7 @@
         <v>0.72691636268398796</v>
       </c>
     </row>
-    <row r="143" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>14</v>
       </c>
@@ -13039,7 +13103,7 @@
         <v>0.40804281413635179</v>
       </c>
     </row>
-    <row r="144" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>15</v>
       </c>
@@ -13122,7 +13186,7 @@
         <v>0.11968020682142257</v>
       </c>
     </row>
-    <row r="145" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>16</v>
       </c>
@@ -13205,7 +13269,7 @@
         <v>0.2817710283800931</v>
       </c>
     </row>
-    <row r="146" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>17</v>
       </c>
@@ -13288,7 +13352,7 @@
         <v>4.7180765681348061E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>18</v>
       </c>
@@ -13371,7 +13435,7 @@
         <v>0.3246823184506501</v>
       </c>
     </row>
-    <row r="148" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>19</v>
       </c>
@@ -13454,7 +13518,7 @@
         <v>0.4378654235287498</v>
       </c>
     </row>
-    <row r="149" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>20</v>
       </c>
@@ -13537,7 +13601,7 @@
         <v>0.2315525622208352</v>
       </c>
     </row>
-    <row r="150" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>21</v>
       </c>
@@ -13620,7 +13684,7 @@
         <v>0.15065394992841988</v>
       </c>
     </row>
-    <row r="151" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>22</v>
       </c>
@@ -13703,7 +13767,7 @@
         <v>0.13333519255883414</v>
       </c>
     </row>
-    <row r="152" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>23</v>
       </c>
@@ -13786,7 +13850,7 @@
         <v>0.2201848013021738</v>
       </c>
     </row>
-    <row r="153" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>24</v>
       </c>
@@ -13869,7 +13933,7 @@
         <v>7.5208128585683348E-2</v>
       </c>
     </row>
-    <row r="154" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>25</v>
       </c>
@@ -13952,7 +14016,7 @@
         <v>0.42885448722957481</v>
       </c>
     </row>
-    <row r="155" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>26</v>
       </c>
@@ -14035,7 +14099,7 @@
         <v>0.75957708235256871</v>
       </c>
     </row>
-    <row r="156" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>27</v>
       </c>
@@ -14118,7 +14182,7 @@
         <v>0.41003335984872546</v>
       </c>
     </row>
-    <row r="157" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>28</v>
       </c>
@@ -14201,7 +14265,7 @@
         <v>0.12746094767742908</v>
       </c>
     </row>
-    <row r="158" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>29</v>
       </c>
@@ -14284,7 +14348,7 @@
         <v>0.31004400592124742</v>
       </c>
     </row>
-    <row r="159" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>30</v>
       </c>
@@ -14367,7 +14431,7 @@
         <v>4.6176909736852456E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>31</v>
       </c>
@@ -14450,7 +14514,7 @@
         <v>0.31071405402795677</v>
       </c>
     </row>
-    <row r="161" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>32</v>
       </c>
@@ -14533,7 +14597,7 @@
         <v>0.44091942255282457</v>
       </c>
     </row>
-    <row r="162" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>1</v>
       </c>
@@ -14616,7 +14680,7 @@
         <v>0.42965036203221812</v>
       </c>
     </row>
-    <row r="163" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>2</v>
       </c>
@@ -14699,7 +14763,7 @@
         <v>0.12289737753343244</v>
       </c>
     </row>
-    <row r="164" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>3</v>
       </c>
@@ -14782,7 +14846,7 @@
         <v>0.28273252588643172</v>
       </c>
     </row>
-    <row r="165" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>4</v>
       </c>
@@ -14865,7 +14929,7 @@
         <v>4.083949069934821E-2</v>
       </c>
     </row>
-    <row r="166" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>5</v>
       </c>
@@ -14948,7 +15012,7 @@
         <v>0.32221764217060544</v>
       </c>
     </row>
-    <row r="167" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>6</v>
       </c>
@@ -15031,7 +15095,7 @@
         <v>0.46171304926561546</v>
       </c>
     </row>
-    <row r="168" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>7</v>
       </c>
@@ -15114,7 +15178,7 @@
         <v>0.24146630603376001</v>
       </c>
     </row>
-    <row r="169" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>8</v>
       </c>
@@ -15197,7 +15261,7 @@
         <v>0.16428246479929443</v>
       </c>
     </row>
-    <row r="170" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>9</v>
       </c>
@@ -15280,7 +15344,7 @@
         <v>0.13144036344599996</v>
       </c>
     </row>
-    <row r="171" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>10</v>
       </c>
@@ -15363,7 +15427,7 @@
         <v>0.19702677154429635</v>
       </c>
     </row>
-    <row r="172" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>11</v>
       </c>
@@ -15446,7 +15510,7 @@
         <v>7.2314319481827663E-2</v>
       </c>
     </row>
-    <row r="173" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>12</v>
       </c>
@@ -15529,7 +15593,7 @@
         <v>0.46001998724932369</v>
       </c>
     </row>
-    <row r="174" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>13</v>
       </c>
@@ -15612,7 +15676,7 @@
         <v>0.72622447296762938</v>
       </c>
     </row>
-    <row r="175" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>14</v>
       </c>
@@ -15695,7 +15759,7 @@
         <v>0.4010627508493424</v>
       </c>
     </row>
-    <row r="176" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>15</v>
       </c>
@@ -15778,7 +15842,7 @@
         <v>0.12537432575955593</v>
       </c>
     </row>
-    <row r="177" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>16</v>
       </c>
@@ -15861,7 +15925,7 @@
         <v>0.31273459745725996</v>
       </c>
     </row>
-    <row r="178" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>17</v>
       </c>
@@ -15944,7 +16008,7 @@
         <v>4.4051037967967832E-2</v>
       </c>
     </row>
-    <row r="179" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>18</v>
       </c>
@@ -16027,7 +16091,7 @@
         <v>0.29278258429582177</v>
       </c>
     </row>
-    <row r="180" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>19</v>
       </c>
@@ -16110,7 +16174,7 @@
         <v>0.43040774612253258</v>
       </c>
     </row>
-    <row r="181" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>20</v>
       </c>
@@ -16193,7 +16257,7 @@
         <v>0.22549174696111235</v>
       </c>
     </row>
-    <row r="182" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>21</v>
       </c>
@@ -16276,7 +16340,7 @@
         <v>0.14289138994230252</v>
       </c>
     </row>
-    <row r="183" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>22</v>
       </c>
@@ -16359,7 +16423,7 @@
         <v>0.13544434056330421</v>
       </c>
     </row>
-    <row r="184" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>23</v>
       </c>
@@ -16442,7 +16506,7 @@
         <v>0.21582499841669786</v>
       </c>
     </row>
-    <row r="185" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>24</v>
       </c>
@@ -16525,7 +16589,7 @@
         <v>8.3930712813533967E-2</v>
       </c>
     </row>
-    <row r="186" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>25</v>
       </c>
@@ -16608,7 +16672,7 @@
         <v>0.45973303128551724</v>
       </c>
     </row>
-    <row r="187" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>26</v>
       </c>
@@ -16691,7 +16755,7 @@
         <v>0.73190418906602639</v>
       </c>
     </row>
-    <row r="188" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>27</v>
       </c>
@@ -16774,7 +16838,7 @@
         <v>0.39427768777634509</v>
       </c>
     </row>
-    <row r="189" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>28</v>
       </c>
@@ -16857,7 +16921,7 @@
         <v>0.12672797661677199</v>
       </c>
     </row>
-    <row r="190" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>29</v>
       </c>
@@ -16940,7 +17004,7 @@
         <v>0.29363456677379773</v>
       </c>
     </row>
-    <row r="191" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>30</v>
       </c>
@@ -17023,7 +17087,7 @@
         <v>4.8685903486685111E-2</v>
       </c>
     </row>
-    <row r="192" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>31</v>
       </c>
@@ -17106,7 +17170,7 @@
         <v>0.31338468480191034</v>
       </c>
     </row>
-    <row r="193" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>32</v>
       </c>
@@ -17189,7 +17253,7 @@
         <v>0.45918880408260448</v>
       </c>
     </row>
-    <row r="194" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>1</v>
       </c>
@@ -17272,7 +17336,7 @@
         <v>0.56850363147764293</v>
       </c>
     </row>
-    <row r="195" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>2</v>
       </c>
@@ -17355,7 +17419,7 @@
         <v>0.1409055153001664</v>
       </c>
     </row>
-    <row r="196" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>3</v>
       </c>
@@ -17438,7 +17502,7 @@
         <v>0.33597021620982936</v>
       </c>
     </row>
-    <row r="197" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>4</v>
       </c>
@@ -17521,7 +17585,7 @@
         <v>4.6885646565674503E-2</v>
       </c>
     </row>
-    <row r="198" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>5</v>
       </c>
@@ -17604,7 +17668,7 @@
         <v>0.32717567035626965</v>
       </c>
     </row>
-    <row r="199" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>6</v>
       </c>
@@ -17687,7 +17751,7 @@
         <v>0.45982461493547749</v>
       </c>
     </row>
-    <row r="200" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>7</v>
       </c>
@@ -17770,7 +17834,7 @@
         <v>0.23184769316557399</v>
       </c>
     </row>
-    <row r="201" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>8</v>
       </c>
@@ -17853,7 +17917,7 @@
         <v>0.15918020101075309</v>
       </c>
     </row>
-    <row r="202" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>9</v>
       </c>
@@ -17936,7 +18000,7 @@
         <v>0.13313519014660974</v>
       </c>
     </row>
-    <row r="203" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>10</v>
       </c>
@@ -18019,7 +18083,7 @@
         <v>0.22892824212080104</v>
       </c>
     </row>
-    <row r="204" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>11</v>
       </c>
@@ -18102,7 +18166,7 @@
         <v>7.7288570783292224E-2</v>
       </c>
     </row>
-    <row r="205" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>12</v>
       </c>
@@ -18185,7 +18249,7 @@
         <v>0.55794241306146164</v>
       </c>
     </row>
-    <row r="206" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>13</v>
       </c>
@@ -18268,7 +18332,7 @@
         <v>0.81989931552599016</v>
       </c>
     </row>
-    <row r="207" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>14</v>
       </c>
@@ -18351,7 +18415,7 @@
         <v>0.55226067057828165</v>
       </c>
     </row>
-    <row r="208" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>15</v>
       </c>
@@ -18434,7 +18498,7 @@
         <v>0.13819579385208627</v>
       </c>
     </row>
-    <row r="209" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>16</v>
       </c>
@@ -18517,7 +18581,7 @@
         <v>0.33597021620982936</v>
       </c>
     </row>
-    <row r="210" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>17</v>
       </c>
@@ -18600,7 +18664,7 @@
         <v>4.6425983364050238E-2</v>
       </c>
     </row>
-    <row r="211" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>18</v>
       </c>
@@ -18683,7 +18747,7 @@
         <v>0.33699094046695777</v>
       </c>
     </row>
-    <row r="212" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>19</v>
       </c>
@@ -18766,7 +18830,7 @@
         <v>0.4733488683159327</v>
       </c>
     </row>
-    <row r="213" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>20</v>
       </c>
@@ -18849,7 +18913,7 @@
         <v>0.25137170943214865</v>
       </c>
     </row>
-    <row r="214" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>21</v>
       </c>
@@ -18932,7 +18996,7 @@
         <v>0.15454388447645931</v>
       </c>
     </row>
-    <row r="215" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>22</v>
       </c>
@@ -19015,7 +19079,7 @@
         <v>0.13176266241313953</v>
       </c>
     </row>
-    <row r="216" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>23</v>
       </c>
@@ -19098,7 +19162,7 @@
         <v>0.22443945305960886</v>
       </c>
     </row>
-    <row r="217" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>24</v>
       </c>
@@ -19181,7 +19245,7 @@
         <v>8.0542826395220313E-2</v>
       </c>
     </row>
-    <row r="218" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>25</v>
       </c>
@@ -19264,7 +19328,7 @@
         <v>0.56341243671892705</v>
       </c>
     </row>
-    <row r="219" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>26</v>
       </c>
@@ -19347,7 +19411,7 @@
         <v>0.75621781529096177</v>
       </c>
     </row>
-    <row r="220" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>27</v>
       </c>
@@ -19430,7 +19494,7 @@
         <v>0.52518906907934626</v>
       </c>
     </row>
-    <row r="221" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>28</v>
       </c>
@@ -19513,7 +19577,7 @@
         <v>0.14226037602420646</v>
       </c>
     </row>
-    <row r="222" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>29</v>
       </c>
@@ -19596,7 +19660,7 @@
         <v>0.30717276910612967</v>
       </c>
     </row>
-    <row r="223" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>30</v>
       </c>
@@ -19679,7 +19743,7 @@
         <v>4.5046993759177457E-2</v>
       </c>
     </row>
-    <row r="224" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>31</v>
       </c>
@@ -19762,7 +19826,7 @@
         <v>0.33044742705983238</v>
       </c>
     </row>
-    <row r="225" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>32</v>
       </c>
@@ -19845,7 +19909,7 @@
         <v>0.46884078385578098</v>
       </c>
     </row>
-    <row r="226" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>1</v>
       </c>
@@ -19928,7 +19992,7 @@
         <v>0.53601770967892048</v>
       </c>
     </row>
-    <row r="227" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>2</v>
       </c>
@@ -20011,7 +20075,7 @@
         <v>0.13006662950784589</v>
       </c>
     </row>
-    <row r="228" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>3</v>
       </c>
@@ -20094,7 +20158,7 @@
         <v>0.31037248545098522</v>
       </c>
     </row>
-    <row r="229" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>4</v>
       </c>
@@ -20177,7 +20241,7 @@
         <v>4.5506656960801722E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>5</v>
       </c>
@@ -20260,7 +20324,7 @@
         <v>0.33699094046695777</v>
       </c>
     </row>
-    <row r="231" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>6</v>
       </c>
@@ -20343,7 +20407,7 @@
         <v>0.450808446015174</v>
       </c>
     </row>
-    <row r="232" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>7</v>
       </c>
@@ -20426,7 +20490,7 @@
         <v>0.24405020333218316</v>
       </c>
     </row>
-    <row r="233" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>8</v>
       </c>
@@ -20509,7 +20573,7 @@
         <v>0.15454388447645931</v>
       </c>
     </row>
-    <row r="234" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>9</v>
       </c>
@@ -20592,7 +20656,7 @@
         <v>0.14137035654743096</v>
       </c>
     </row>
-    <row r="235" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>10</v>
       </c>
@@ -20675,7 +20739,7 @@
         <v>0.22892824212080104</v>
       </c>
     </row>
-    <row r="236" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>11</v>
       </c>
@@ -20758,7 +20822,7 @@
         <v>8.0542826395220313E-2</v>
       </c>
     </row>
-    <row r="237" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>12</v>
       </c>
@@ -20841,7 +20905,7 @@
         <v>0.53606231843160046</v>
       </c>
     </row>
-    <row r="238" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>13</v>
       </c>
@@ -20924,7 +20988,7 @@
         <v>0.78009837787909742</v>
       </c>
     </row>
-    <row r="239" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>14</v>
       </c>
@@ -21007,7 +21071,7 @@
         <v>0.52518906907934626</v>
       </c>
     </row>
-    <row r="240" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>15</v>
       </c>
@@ -21090,7 +21154,7 @@
         <v>0.1409055153001664</v>
       </c>
     </row>
-    <row r="241" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>16</v>
       </c>
@@ -21173,7 +21237,7 @@
         <v>0.30397305276127418</v>
       </c>
     </row>
-    <row r="242" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>17</v>
       </c>
@@ -21256,7 +21320,7 @@
         <v>4.5046993759177457E-2</v>
       </c>
     </row>
-    <row r="243" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>18</v>
       </c>
@@ -21339,7 +21403,7 @@
         <v>0.32390391365270693</v>
       </c>
     </row>
-    <row r="244" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>19</v>
       </c>
@@ -21422,7 +21486,7 @@
         <v>0.4282680237144153</v>
       </c>
     </row>
-    <row r="245" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>20</v>
       </c>
@@ -21505,7 +21569,7 @@
         <v>0.23916919926553951</v>
       </c>
     </row>
-    <row r="246" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>21</v>
       </c>
@@ -21588,7 +21652,7 @@
         <v>0.15918020101075309</v>
       </c>
     </row>
-    <row r="247" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>22</v>
       </c>
@@ -21671,7 +21735,7 @@
         <v>0.13999782881396075</v>
       </c>
     </row>
-    <row r="248" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>23</v>
       </c>
@@ -21754,7 +21818,7 @@
         <v>0.2177062694678206</v>
       </c>
     </row>
-    <row r="249" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>24</v>
       </c>
@@ -21837,7 +21901,7 @@
         <v>8.1356390298202338E-2</v>
       </c>
     </row>
-    <row r="250" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>25</v>
       </c>
@@ -21920,7 +21984,7 @@
         <v>0.54700236574653105</v>
       </c>
     </row>
-    <row r="251" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>26</v>
       </c>
@@ -22003,7 +22067,7 @@
         <v>0.79601875293785451</v>
       </c>
     </row>
-    <row r="252" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>27</v>
       </c>
@@ -22086,7 +22150,7 @@
         <v>0.5197747487795592</v>
       </c>
     </row>
-    <row r="253" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>28</v>
       </c>
@@ -22169,7 +22233,7 @@
         <v>0.13006662950784589</v>
       </c>
     </row>
-    <row r="254" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>29</v>
       </c>
@@ -22252,7 +22316,7 @@
         <v>0.31997163448555177</v>
       </c>
     </row>
-    <row r="255" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>30</v>
       </c>
@@ -22335,7 +22399,7 @@
         <v>4.7345309767298761E-2</v>
       </c>
     </row>
-    <row r="256" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>31</v>
       </c>
@@ -22418,7 +22482,7 @@
         <v>0.31736040024558154</v>
       </c>
     </row>
-    <row r="257" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>32</v>
       </c>
@@ -22501,7 +22565,7 @@
         <v>0.4282680237144153</v>
       </c>
     </row>
-    <row r="258" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>1</v>
       </c>
@@ -22584,7 +22648,7 @@
         <v>0.52979124133416533</v>
       </c>
     </row>
-    <row r="259" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>2</v>
       </c>
@@ -22667,7 +22731,7 @@
         <v>0.1299988864716439</v>
       </c>
     </row>
-    <row r="260" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>3</v>
       </c>
@@ -22750,7 +22814,7 @@
         <v>0.30701278328888693</v>
       </c>
     </row>
-    <row r="261" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>4</v>
       </c>
@@ -22833,7 +22897,7 @@
         <v>4.1921283988132489E-2</v>
       </c>
     </row>
-    <row r="262" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>5</v>
       </c>
@@ -22916,7 +22980,7 @@
         <v>0.31081688683845615</v>
       </c>
     </row>
-    <row r="263" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>6</v>
       </c>
@@ -22999,7 +23063,7 @@
         <v>0.41970266324012701</v>
       </c>
     </row>
-    <row r="264" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>7</v>
       </c>
@@ -23082,7 +23146,7 @@
         <v>0.23416617009722973</v>
       </c>
     </row>
-    <row r="265" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>8</v>
       </c>
@@ -23165,7 +23229,7 @@
         <v>0.14975302405768906</v>
       </c>
     </row>
-    <row r="266" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>9</v>
       </c>
@@ -23248,7 +23312,7 @@
         <v>0.13169403602646604</v>
       </c>
     </row>
-    <row r="267" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>10</v>
       </c>
@@ -23331,7 +23395,7 @@
         <v>0.20682095599442957</v>
       </c>
     </row>
-    <row r="268" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>11</v>
       </c>
@@ -23414,7 +23478,7 @@
         <v>7.9607227906790992E-2</v>
       </c>
     </row>
-    <row r="269" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>12</v>
       </c>
@@ -23497,7 +23561,7 @@
         <v>0.51965224745920446</v>
       </c>
     </row>
-    <row r="270" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>13</v>
       </c>
@@ -23580,7 +23644,7 @@
         <v>0.76377999344387137</v>
       </c>
     </row>
-    <row r="271" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A271">
         <v>14</v>
       </c>
@@ -23663,7 +23727,7 @@
         <v>0.52979124133416533</v>
       </c>
     </row>
-    <row r="272" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>15</v>
       </c>
@@ -23746,7 +23810,7 @@
         <v>0.13257312184732001</v>
       </c>
     </row>
-    <row r="273" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>16</v>
       </c>
@@ -23829,7 +23893,7 @@
         <v>0.30397305276127418</v>
       </c>
     </row>
-    <row r="274" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>17</v>
       </c>
@@ -23912,7 +23976,7 @@
         <v>4.1484603946589441E-2</v>
       </c>
     </row>
-    <row r="275" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>18</v>
       </c>
@@ -23995,7 +24059,7 @@
         <v>0.32324956231199442</v>
       </c>
     </row>
-    <row r="276" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>19</v>
       </c>
@@ -24078,7 +24142,7 @@
         <v>0.44968142490013607</v>
       </c>
     </row>
-    <row r="277" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>20</v>
       </c>
@@ -24161,7 +24225,7 @@
         <v>0.23648464702888547</v>
       </c>
     </row>
-    <row r="278" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>21</v>
       </c>
@@ -24244,7 +24308,7 @@
         <v>0.15122119096021541</v>
       </c>
     </row>
-    <row r="279" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>22</v>
       </c>
@@ -24327,7 +24391,7 @@
         <v>0.13169403602646604</v>
       </c>
     </row>
-    <row r="280" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>23</v>
       </c>
@@ -24410,7 +24474,7 @@
         <v>0.21748183001476099</v>
       </c>
     </row>
-    <row r="281" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A281">
         <v>24</v>
       </c>
@@ -24493,7 +24557,7 @@
         <v>7.5742799367626373E-2</v>
       </c>
     </row>
-    <row r="282" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A282">
         <v>25</v>
       </c>
@@ -24576,7 +24640,7 @@
         <v>0.5300452924083886</v>
       </c>
     </row>
-    <row r="283" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>26</v>
       </c>
@@ -24659,7 +24723,7 @@
         <v>0.77134217159678098</v>
       </c>
     </row>
-    <row r="284" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A284">
         <v>27</v>
       </c>
@@ -24742,7 +24806,7 @@
         <v>0.50921682419497438</v>
       </c>
     </row>
-    <row r="285" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>28</v>
       </c>
@@ -24825,7 +24889,7 @@
         <v>0.13386023953515808</v>
       </c>
     </row>
-    <row r="286" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A286">
         <v>29</v>
       </c>
@@ -24908,7 +24972,7 @@
         <v>0.29789359170604868</v>
       </c>
     </row>
-    <row r="287" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>30</v>
       </c>
@@ -24991,7 +25055,7 @@
         <v>4.4978044278933815E-2</v>
       </c>
     </row>
-    <row r="288" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>31</v>
       </c>
@@ -25074,7 +25138,7 @@
         <v>0.31392505570684071</v>
       </c>
     </row>
-    <row r="289" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>32</v>
       </c>
@@ -25157,7 +25221,7 @@
         <v>0.40685462252869453</v>
       </c>
     </row>
-    <row r="290" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>1</v>
       </c>
@@ -25240,7 +25304,7 @@
         <v>0.38991367175680802</v>
       </c>
     </row>
-    <row r="291" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>2</v>
       </c>
@@ -25323,7 +25387,7 @@
         <v>0.12626746373434408</v>
       </c>
     </row>
-    <row r="292" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>3</v>
       </c>
@@ -25406,7 +25470,7 @@
         <v>0.29748174575997999</v>
       </c>
     </row>
-    <row r="293" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>4</v>
       </c>
@@ -25489,7 +25553,7 @@
         <v>4.5989104722610467E-2</v>
       </c>
     </row>
-    <row r="294" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>5</v>
       </c>
@@ -25572,7 +25636,7 @@
         <v>0.29758364319182595</v>
       </c>
     </row>
-    <row r="295" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>6</v>
       </c>
@@ -25655,7 +25719,7 @@
         <v>0.46963632109024683</v>
       </c>
     </row>
-    <row r="296" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>7</v>
       </c>
@@ -25738,7 +25802,7 @@
         <v>0.23346439779015135</v>
       </c>
     </row>
-    <row r="297" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>8</v>
       </c>
@@ -25821,7 +25885,7 @@
         <v>0.1479600323897812</v>
       </c>
     </row>
-    <row r="298" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>9</v>
       </c>
@@ -25904,7 +25968,7 @@
         <v>0.14914807358193835</v>
       </c>
     </row>
-    <row r="299" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>10</v>
       </c>
@@ -25987,7 +26051,7 @@
         <v>0.21630483374172366</v>
       </c>
     </row>
-    <row r="300" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>11</v>
       </c>
@@ -26070,7 +26134,7 @@
         <v>7.7467480970060482E-2</v>
       </c>
     </row>
-    <row r="301" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>12</v>
       </c>
@@ -26153,7 +26217,7 @@
         <v>0.42050493603836914</v>
       </c>
     </row>
-    <row r="302" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A302">
         <v>13</v>
       </c>
@@ -26236,7 +26300,7 @@
         <v>0.71913619665267769</v>
       </c>
     </row>
-    <row r="303" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>14</v>
       </c>
@@ -26319,7 +26383,7 @@
         <v>0.38462437459764404</v>
       </c>
     </row>
-    <row r="304" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A304">
         <v>15</v>
       </c>
@@ -26402,7 +26466,7 @@
         <v>0.11771851435202564</v>
       </c>
     </row>
-    <row r="305" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A305">
         <v>16</v>
       </c>
@@ -26485,7 +26549,7 @@
         <v>0.30105279375407817</v>
       </c>
     </row>
-    <row r="306" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A306">
         <v>17</v>
       </c>
@@ -26568,7 +26632,7 @@
         <v>4.6766775035971847E-2</v>
       </c>
     </row>
-    <row r="307" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A307">
         <v>18</v>
       </c>
@@ -26651,7 +26715,7 @@
         <v>0.30864966612628669</v>
       </c>
     </row>
-    <row r="308" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A308">
         <v>19</v>
       </c>
@@ -26734,7 +26798,7 @@
         <v>0.46092865073350575</v>
       </c>
     </row>
-    <row r="309" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A309">
         <v>20</v>
       </c>
@@ -26817,7 +26881,7 @@
         <v>0.22107520885198301</v>
       </c>
     </row>
-    <row r="310" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A310">
         <v>21</v>
       </c>
@@ -26900,7 +26964,7 @@
         <v>0.14942932593407893</v>
       </c>
     </row>
-    <row r="311" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A311">
         <v>22</v>
       </c>
@@ -26983,7 +27047,7 @@
         <v>0.14580624846449972</v>
       </c>
     </row>
-    <row r="312" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A312">
         <v>23</v>
       </c>
@@ -27066,7 +27130,7 @@
         <v>0.20833483292938207</v>
       </c>
     </row>
-    <row r="313" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A313">
         <v>24</v>
       </c>
@@ -27149,7 +27213,7 @@
         <v>7.6075164377009091E-2</v>
       </c>
     </row>
-    <row r="314" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A314">
         <v>25</v>
       </c>
@@ -27232,7 +27296,7 @@
         <v>0.46772855744554459</v>
       </c>
     </row>
-    <row r="315" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A315">
         <v>26</v>
       </c>
@@ -27315,7 +27379,7 @@
         <v>0.69763343251953736</v>
       </c>
     </row>
-    <row r="316" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A316">
         <v>27</v>
       </c>
@@ -27398,7 +27462,7 @@
         <v>0.38316213563756696</v>
       </c>
     </row>
-    <row r="317" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A317">
         <v>28</v>
       </c>
@@ -27481,7 +27545,7 @@
         <v>0.1289304828276106</v>
       </c>
     </row>
-    <row r="318" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A318">
         <v>29</v>
       </c>
@@ -27564,7 +27628,7 @@
         <v>0.28713789806851081</v>
       </c>
     </row>
-    <row r="319" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A319">
         <v>30</v>
       </c>
@@ -27647,7 +27711,7 @@
         <v>4.4676910970780283E-2</v>
       </c>
     </row>
-    <row r="320" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A320">
         <v>31</v>
       </c>
@@ -27730,7 +27794,7 @@
         <v>0.30928644336699423</v>
       </c>
     </row>
-    <row r="321" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A321">
         <v>32</v>
       </c>
@@ -27813,7 +27877,7 @@
         <v>0.45203518990861852</v>
       </c>
     </row>
-    <row r="322" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A322">
         <v>1</v>
       </c>
@@ -27896,7 +27960,7 @@
         <v>0.37538367038182924</v>
       </c>
     </row>
-    <row r="323" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A323">
         <v>2</v>
       </c>
@@ -27979,7 +28043,7 @@
         <v>0.12018811300212001</v>
       </c>
     </row>
-    <row r="324" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A324">
         <v>3</v>
       </c>
@@ -28062,7 +28126,7 @@
         <v>0.28154725817896198</v>
       </c>
     </row>
-    <row r="325" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A325">
         <v>4</v>
       </c>
@@ -28145,7 +28209,7 @@
         <v>4.6882367854616955E-2</v>
       </c>
     </row>
-    <row r="326" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A326">
         <v>5</v>
       </c>
@@ -28228,7 +28292,7 @@
         <v>0.30259669914399334</v>
       </c>
     </row>
-    <row r="327" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A327">
         <v>6</v>
       </c>
@@ -28311,7 +28375,7 @@
         <v>0.43565833319397973</v>
       </c>
     </row>
-    <row r="328" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A328">
         <v>7</v>
       </c>
@@ -28394,7 +28458,7 @@
         <v>0.21772304768995185</v>
       </c>
     </row>
-    <row r="329" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A329">
         <v>8</v>
       </c>
@@ -28477,7 +28541,7 @@
         <v>0.16035307422661751</v>
       </c>
     </row>
-    <row r="330" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A330">
         <v>9</v>
       </c>
@@ -28560,7 +28624,7 @@
         <v>0.1386796906061204</v>
       </c>
     </row>
-    <row r="331" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A331">
         <v>10</v>
       </c>
@@ -28643,7 +28707,7 @@
         <v>0.2130218266585143</v>
       </c>
     </row>
-    <row r="332" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A332">
         <v>11</v>
       </c>
@@ -28726,7 +28790,7 @@
         <v>7.7051441060587519E-2</v>
       </c>
     </row>
-    <row r="333" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A333">
         <v>12</v>
       </c>
@@ -28809,7 +28873,7 @@
         <v>0.41695009600600685</v>
       </c>
     </row>
-    <row r="334" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A334">
         <v>13</v>
       </c>
@@ -28892,7 +28956,7 @@
         <v>0.71830057796525593</v>
       </c>
     </row>
-    <row r="335" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A335">
         <v>14</v>
       </c>
@@ -28975,7 +29039,7 @@
         <v>0.35771485362760636</v>
       </c>
     </row>
-    <row r="336" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A336">
         <v>15</v>
       </c>
@@ -29058,7 +29122,7 @@
         <v>0.11720366727689044</v>
       </c>
     </row>
-    <row r="337" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A337">
         <v>16</v>
       </c>
@@ -29141,7 +29205,7 @@
         <v>0.29742669809320632</v>
       </c>
     </row>
-    <row r="338" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A338">
         <v>17</v>
       </c>
@@ -29224,7 +29288,7 @@
         <v>4.3774702556512855E-2</v>
       </c>
     </row>
-    <row r="339" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A339">
         <v>18</v>
       </c>
@@ -29307,7 +29371,7 @@
         <v>0.31479827545539374</v>
       </c>
     </row>
-    <row r="340" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A340">
         <v>19</v>
       </c>
@@ -29390,7 +29454,7 @@
         <v>0.4436653899862828</v>
       </c>
     </row>
-    <row r="341" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A341">
         <v>20</v>
       </c>
@@ -29473,7 +29537,7 @@
         <v>0.23657711677899329</v>
       </c>
     </row>
-    <row r="342" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A342">
         <v>21</v>
       </c>
@@ -29556,7 +29620,7 @@
         <v>0.15822983535940957</v>
       </c>
     </row>
-    <row r="343" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A343">
         <v>22</v>
       </c>
@@ -29639,7 +29703,7 @@
         <v>0.14485334106993131</v>
       </c>
     </row>
-    <row r="344" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A344">
         <v>23</v>
       </c>
@@ -29722,7 +29786,7 @@
         <v>0.20046621042375082</v>
       </c>
     </row>
-    <row r="345" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A345">
         <v>24</v>
       </c>
@@ -29805,7 +29869,7 @@
         <v>8.1244140608213222E-2</v>
       </c>
     </row>
-    <row r="346" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A346">
         <v>25</v>
       </c>
@@ -29888,7 +29952,7 @@
         <v>0.42038347631675754</v>
       </c>
     </row>
-    <row r="347" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A347">
         <v>26</v>
       </c>
@@ -29971,7 +30035,7 @@
         <v>0.76319264462658776</v>
       </c>
     </row>
-    <row r="348" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A348">
         <v>27</v>
       </c>
@@ -30054,7 +30118,7 @@
         <v>0.40699492683503591</v>
       </c>
     </row>
-    <row r="349" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A349">
         <v>28</v>
       </c>
@@ -30137,7 +30201,7 @@
         <v>0.12384606230212507</v>
       </c>
     </row>
-    <row r="350" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A350">
         <v>29</v>
       </c>
@@ -30220,7 +30284,7 @@
         <v>0.29237113682890775</v>
       </c>
     </row>
-    <row r="351" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A351">
         <v>30</v>
       </c>
@@ -30303,7 +30367,7 @@
         <v>5.043452388991345E-2</v>
       </c>
     </row>
-    <row r="352" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A352">
         <v>31</v>
       </c>
@@ -30386,7 +30450,7 @@
         <v>0.33298126403136252</v>
       </c>
     </row>
-    <row r="353" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A353">
         <v>32</v>
       </c>
@@ -30469,7 +30533,7 @@
         <v>0.43966360856781511</v>
       </c>
     </row>
-    <row r="354" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A354">
         <v>1</v>
       </c>
@@ -30552,7 +30616,7 @@
         <v>0.36542259844303537</v>
       </c>
     </row>
-    <row r="355" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A355">
         <v>2</v>
       </c>
@@ -30635,7 +30699,7 @@
         <v>0.11993956495672245</v>
       </c>
     </row>
-    <row r="356" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A356">
         <v>3</v>
       </c>
@@ -30718,7 +30782,7 @@
         <v>0.29133395395230999</v>
       </c>
     </row>
-    <row r="357" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A357">
         <v>4</v>
       </c>
@@ -30801,7 +30865,7 @@
         <v>4.6491627052506763E-2</v>
       </c>
     </row>
-    <row r="358" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A358">
         <v>5</v>
       </c>
@@ -30884,7 +30948,7 @@
         <v>0.33094444964029684</v>
       </c>
     </row>
-    <row r="359" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A359">
         <v>6</v>
       </c>
@@ -30967,7 +31031,7 @@
         <v>0.44131775373106019</v>
       </c>
     </row>
-    <row r="360" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A360">
         <v>7</v>
       </c>
@@ -31050,7 +31114,7 @@
         <v>0.21940458410267669</v>
       </c>
     </row>
-    <row r="361" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A361">
         <v>8</v>
       </c>
@@ -31133,7 +31197,7 @@
         <v>0.14882351390693122</v>
       </c>
     </row>
-    <row r="362" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A362">
         <v>9</v>
       </c>
@@ -31216,7 +31280,7 @@
         <v>0.14232419957901937</v>
       </c>
     </row>
-    <row r="363" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A363">
         <v>10</v>
       </c>
@@ -31299,7 +31363,7 @@
         <v>0.1987066051117635</v>
       </c>
     </row>
-    <row r="364" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A364">
         <v>11</v>
       </c>
@@ -31382,7 +31446,7 @@
         <v>8.2968124911176055E-2</v>
       </c>
     </row>
-    <row r="365" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A365">
         <v>12</v>
       </c>
@@ -31465,7 +31529,7 @@
         <v>0.44534195487828471</v>
       </c>
     </row>
-    <row r="366" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A366">
         <v>13</v>
       </c>
@@ -31548,7 +31612,7 @@
         <v>0.72046342351678183</v>
       </c>
     </row>
-    <row r="367" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A367">
         <v>14</v>
       </c>
@@ -31631,7 +31695,7 @@
         <v>0.3905046989223474</v>
       </c>
     </row>
-    <row r="368" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A368">
         <v>15</v>
       </c>
@@ -31714,7 +31778,7 @@
         <v>0.12557691115573524</v>
       </c>
     </row>
-    <row r="369" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A369">
         <v>16</v>
       </c>
@@ -31797,7 +31861,7 @@
         <v>0.29689256902968525</v>
       </c>
     </row>
-    <row r="370" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A370">
         <v>17</v>
       </c>
@@ -31880,7 +31944,7 @@
         <v>4.5766371175294397E-2</v>
       </c>
     </row>
-    <row r="371" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A371">
         <v>18</v>
       </c>
@@ -31963,7 +32027,7 @@
         <v>0.32149215231149958</v>
       </c>
     </row>
-    <row r="372" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A372">
         <v>19</v>
       </c>
@@ -32046,7 +32110,7 @@
         <v>0.43026063286055011</v>
       </c>
     </row>
-    <row r="373" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A373">
         <v>20</v>
       </c>
@@ -32129,7 +32193,7 @@
         <v>0.21739521351587132</v>
       </c>
     </row>
-    <row r="374" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A374">
         <v>21</v>
       </c>
@@ -32212,7 +32276,7 @@
         <v>0.14757998683067833</v>
       </c>
     </row>
-    <row r="375" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A375">
         <v>22</v>
       </c>
@@ -32295,7 +32359,7 @@
         <v>0.13246396666318053</v>
       </c>
     </row>
-    <row r="376" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A376">
         <v>23</v>
       </c>
@@ -32378,7 +32442,7 @@
         <v>0.19190004695921983</v>
       </c>
     </row>
-    <row r="377" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A377">
         <v>24</v>
       </c>
@@ -32461,7 +32525,7 @@
         <v>8.0102468745015948E-2</v>
       </c>
     </row>
-    <row r="378" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A378">
         <v>25</v>
       </c>
@@ -32544,7 +32608,7 @@
         <v>0.41896012228240564</v>
       </c>
     </row>
-    <row r="379" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A379">
         <v>26</v>
       </c>
@@ -32627,7 +32691,7 @@
         <v>0.68614524604916194</v>
       </c>
     </row>
-    <row r="380" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A380">
         <v>27</v>
       </c>
@@ -32710,7 +32774,7 @@
         <v>0.38248935213953739</v>
       </c>
     </row>
-    <row r="381" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A381">
         <v>28</v>
       </c>
@@ -32793,7 +32857,7 @@
         <v>0.12614241732230266</v>
       </c>
     </row>
-    <row r="382" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A382">
         <v>29</v>
       </c>
@@ -32876,7 +32940,7 @@
         <v>0.30007397257087931</v>
       </c>
     </row>
-    <row r="383" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A383">
         <v>30</v>
       </c>
@@ -32959,7 +33023,7 @@
         <v>4.6078634270013533E-2</v>
       </c>
     </row>
-    <row r="384" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A384">
         <v>31</v>
       </c>
@@ -33042,7 +33106,7 @@
         <v>0.29177639938549099</v>
       </c>
     </row>
-    <row r="385" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A385">
         <v>32</v>
       </c>
@@ -33133,9 +33197,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBB35780-D2A8-4868-BC60-ED161DD3DC9F}">
   <dimension ref="A1:AA385"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -33218,7 +33282,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -33301,7 +33365,7 @@
         <v>0.10440066304416196</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -33384,7 +33448,7 @@
         <v>-0.10503458241230207</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -33467,7 +33531,7 @@
         <v>-0.28973750613877669</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -33550,7 +33614,7 @@
         <v>-0.29715603926547057</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -33633,7 +33697,7 @@
         <v>-0.25022140873816789</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -33716,7 +33780,7 @@
         <v>0.22534376338021103</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -33799,7 +33863,7 @@
         <v>-0.22749198791228348</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -33882,7 +33946,7 @@
         <v>-0.72083640057428056</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -33965,7 +34029,7 @@
         <v>-2.726202685746134E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -34048,7 +34112,7 @@
         <v>-0.28544317332426927</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -34131,7 +34195,7 @@
         <v>-0.17665658184026775</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -34214,7 +34278,7 @@
         <v>0.29053667590828686</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -34297,7 +34361,7 @@
         <v>0.16425412952137319</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -34380,7 +34444,7 @@
         <v>0.10239295798562037</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -34463,7 +34527,7 @@
         <v>-0.10503458241230207</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -34546,7 +34610,7 @@
         <v>-0.27318107721656087</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -34629,7 +34693,7 @@
         <v>-0.32843562234604645</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -34712,7 +34776,7 @@
         <v>-0.26827862380174705</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -34795,7 +34859,7 @@
         <v>0.2392825528676468</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -34878,7 +34942,7 @@
         <v>-0.21882562646800599</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -34961,7 +35025,7 @@
         <v>-0.75118740691425023</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -35044,7 +35108,7 @@
         <v>-2.4902812994796415E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -35127,7 +35191,7 @@
         <v>-0.30309945208659528</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -35210,7 +35274,7 @@
         <v>-0.17308776200511083</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -35293,7 +35357,7 @@
         <v>0.27925369820311069</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -35376,7 +35440,7 @@
         <v>0.16267476289135999</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -35459,7 +35523,7 @@
         <v>9.9381400397808003E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -35542,7 +35606,7 @@
         <v>-0.10003293563076388</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -35625,7 +35689,7 @@
         <v>-0.27318107721656087</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -35708,7 +35772,7 @@
         <v>-0.32843562234604645</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -35791,7 +35855,7 @@
         <v>-0.25796021519398754</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -35874,7 +35938,7 @@
         <v>0.2346362897051682</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>1</v>
       </c>
@@ -35957,7 +36021,7 @@
         <v>0.10546474672518899</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>2</v>
       </c>
@@ -36040,7 +36104,7 @@
         <v>-9.9942905988696193E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>3</v>
       </c>
@@ -36123,7 +36187,7 @@
         <v>-0.2842186964980381</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>4</v>
       </c>
@@ -36206,7 +36270,7 @@
         <v>-0.3060707204434347</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>5</v>
       </c>
@@ -36289,7 +36353,7 @@
         <v>-0.26569902164980719</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>6</v>
       </c>
@@ -36372,7 +36436,7 @@
         <v>0.24646102945367621</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>7</v>
       </c>
@@ -36455,7 +36519,7 @@
         <v>-0.21869563104634182</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>8</v>
       </c>
@@ -36538,7 +36602,7 @@
         <v>-0.75027687672405119</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>9</v>
       </c>
@@ -36621,7 +36685,7 @@
         <v>-2.5919896304478624E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>10</v>
       </c>
@@ -36704,7 +36768,7 @@
         <v>-0.30916144112832716</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>11</v>
       </c>
@@ -36787,7 +36851,7 @@
         <v>-0.18747010594079325</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>12</v>
       </c>
@@ -36870,7 +36934,7 @@
         <v>0.29053667590828686</v>
       </c>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>13</v>
       </c>
@@ -36953,7 +37017,7 @@
         <v>0.15454102474679199</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>14</v>
       </c>
@@ -37036,7 +37100,7 @@
         <v>0.10753268293548682</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>15</v>
       </c>
@@ -37119,7 +37183,7 @@
         <v>-0.10715528064767427</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>16</v>
       </c>
@@ -37202,7 +37266,7 @@
         <v>-0.27284994863811657</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>17</v>
       </c>
@@ -37285,7 +37349,7 @@
         <v>-0.31895790867263196</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>18</v>
       </c>
@@ -37368,7 +37432,7 @@
         <v>-0.26038504121681105</v>
       </c>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>19</v>
       </c>
@@ -37451,7 +37515,7 @@
         <v>0.22731842522426446</v>
       </c>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>20</v>
       </c>
@@ -37534,7 +37598,7 @@
         <v>-0.22762198333394762</v>
       </c>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>21</v>
       </c>
@@ -37617,7 +37681,7 @@
         <v>-0.75027687672405119</v>
       </c>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>22</v>
       </c>
@@ -37700,7 +37764,7 @@
         <v>-2.7539889823508541E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>23</v>
       </c>
@@ -37783,7 +37847,7 @@
         <v>-0.29703746304486339</v>
       </c>
     </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>24</v>
       </c>
@@ -37866,7 +37930,7 @@
         <v>-0.17644245265015834</v>
       </c>
     </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>25</v>
       </c>
@@ -37949,7 +38013,7 @@
         <v>0.27891520887195537</v>
       </c>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>26</v>
       </c>
@@ -38032,7 +38096,7 @@
         <v>0.16592825814918719</v>
       </c>
     </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>27</v>
       </c>
@@ -38115,7 +38179,7 @@
         <v>0.10029490619944442</v>
       </c>
     </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>28</v>
       </c>
@@ -38198,7 +38262,7 @@
         <v>-0.10715528064767427</v>
       </c>
     </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>29</v>
       </c>
@@ -38281,7 +38345,7 @@
         <v>-0.27284994863811657</v>
       </c>
     </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>30</v>
       </c>
@@ -38364,7 +38428,7 @@
         <v>-0.32217970572993126</v>
       </c>
     </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>31</v>
       </c>
@@ -38447,7 +38511,7 @@
         <v>-0.25772805100031299</v>
       </c>
     </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>32</v>
       </c>
@@ -38530,7 +38594,7 @@
         <v>0.23210407628161739</v>
       </c>
     </row>
-    <row r="66" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>1</v>
       </c>
@@ -38613,7 +38677,7 @@
         <v>0.10329642526196409</v>
       </c>
     </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>2</v>
       </c>
@@ -38696,7 +38760,7 @@
         <v>-9.9012599687330088E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>3</v>
       </c>
@@ -38779,7 +38843,7 @@
         <v>-0.26230902222430585</v>
       </c>
     </row>
-    <row r="69" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>4</v>
       </c>
@@ -38862,7 +38926,7 @@
         <v>-0.30347451504774686</v>
       </c>
     </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>5</v>
       </c>
@@ -38945,7 +39009,7 @@
         <v>-0.25280101089010776</v>
       </c>
     </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>6</v>
       </c>
@@ -39028,7 +39092,7 @@
         <v>0.23677357075990837</v>
       </c>
     </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>7</v>
       </c>
@@ -39111,7 +39175,7 @@
         <v>-0.21869563104634185</v>
       </c>
     </row>
-    <row r="73" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>8</v>
       </c>
@@ -39194,7 +39258,7 @@
         <v>-0.75847164843584303</v>
       </c>
     </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>9</v>
       </c>
@@ -39277,7 +39341,7 @@
         <v>-2.5175433263371027E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>10</v>
       </c>
@@ -39360,7 +39424,7 @@
         <v>-0.29703746304486334</v>
       </c>
     </row>
-    <row r="76" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>11</v>
       </c>
@@ -39443,7 +39507,7 @@
         <v>-0.17662089364191619</v>
       </c>
     </row>
-    <row r="77" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>12</v>
       </c>
@@ -39526,7 +39590,7 @@
         <v>0.26813996516351213</v>
       </c>
     </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>13</v>
       </c>
@@ -39609,7 +39673,7 @@
         <v>0.14703903325422923</v>
       </c>
     </row>
-    <row r="79" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>14</v>
       </c>
@@ -39692,7 +39756,7 @@
         <v>9.7393772389851849E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>15</v>
       </c>
@@ -39775,7 +39839,7 @@
         <v>-0.10195356799487455</v>
       </c>
     </row>
-    <row r="81" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>16</v>
       </c>
@@ -39858,7 +39922,7 @@
         <v>-0.27853432256807731</v>
       </c>
     </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>17</v>
       </c>
@@ -39941,7 +40005,7 @@
         <v>-0.30960531333153979</v>
       </c>
     </row>
-    <row r="83" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>18</v>
       </c>
@@ -40024,7 +40088,7 @@
         <v>-0.25280101089010776</v>
       </c>
     </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>19</v>
       </c>
@@ -40107,7 +40171,7 @@
         <v>0.23222023286067936</v>
       </c>
     </row>
-    <row r="85" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>20</v>
       </c>
@@ -40190,7 +40254,7 @@
         <v>-0.21444911393864588</v>
       </c>
     </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>21</v>
       </c>
@@ -40273,7 +40337,7 @@
         <v>-0.72872766222267271</v>
       </c>
     </row>
-    <row r="87" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>22</v>
       </c>
@@ -40356,7 +40420,7 @@
         <v>-2.5689217615684722E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>23</v>
       </c>
@@ -40439,7 +40503,7 @@
         <v>-0.29703746304486334</v>
       </c>
     </row>
-    <row r="89" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>24</v>
       </c>
@@ -40522,7 +40586,7 @@
         <v>-0.17137472848423552</v>
       </c>
     </row>
-    <row r="90" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>25</v>
       </c>
@@ -40605,7 +40669,7 @@
         <v>0.26813996516351213</v>
       </c>
     </row>
-    <row r="91" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>26</v>
       </c>
@@ -40688,7 +40752,7 @@
         <v>0.14703903325422923</v>
       </c>
     </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>27</v>
       </c>
@@ -40771,7 +40835,7 @@
         <v>0.10231264978327871</v>
       </c>
     </row>
-    <row r="93" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>28</v>
       </c>
@@ -40854,7 +40918,7 @@
         <v>-9.6071631379785624E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>29</v>
       </c>
@@ -40937,7 +41001,7 @@
         <v>-0.27042167239619158</v>
       </c>
     </row>
-    <row r="95" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>30</v>
       </c>
@@ -41020,7 +41084,7 @@
         <v>-0.31573611161533266</v>
       </c>
     </row>
-    <row r="96" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>31</v>
       </c>
@@ -41103,7 +41167,7 @@
         <v>-0.25785703110790992</v>
       </c>
     </row>
-    <row r="97" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>32</v>
       </c>
@@ -41186,7 +41250,7 @@
         <v>0.22311355706222133</v>
       </c>
     </row>
-    <row r="98" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>1</v>
       </c>
@@ -41269,7 +41333,7 @@
         <v>0.23760749463551797</v>
       </c>
     </row>
-    <row r="99" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>2</v>
       </c>
@@ -41352,7 +41416,7 @@
         <v>-3.5905771033493038E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>3</v>
       </c>
@@ -41435,7 +41499,7 @@
         <v>-0.20578658689322218</v>
       </c>
     </row>
-    <row r="101" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>4</v>
       </c>
@@ -41518,7 +41582,7 @@
         <v>-0.28962811170780051</v>
       </c>
     </row>
-    <row r="102" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>5</v>
       </c>
@@ -41601,7 +41665,7 @@
         <v>-0.12389553246065828</v>
       </c>
     </row>
-    <row r="103" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>6</v>
       </c>
@@ -41684,7 +41748,7 @@
         <v>0.33237688508273816</v>
       </c>
     </row>
-    <row r="104" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>7</v>
       </c>
@@ -41767,7 +41831,7 @@
         <v>-0.15590387379103984</v>
       </c>
     </row>
-    <row r="105" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>8</v>
       </c>
@@ -41850,7 +41914,7 @@
         <v>-0.828655542709546</v>
       </c>
     </row>
-    <row r="106" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>9</v>
       </c>
@@ -41933,7 +41997,7 @@
         <v>-1.6089547589897894E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>10</v>
       </c>
@@ -42016,7 +42080,7 @@
         <v>-0.15731781796771568</v>
       </c>
     </row>
-    <row r="108" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>11</v>
       </c>
@@ -42099,7 +42163,7 @@
         <v>-0.13524649072189965</v>
       </c>
     </row>
-    <row r="109" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>12</v>
       </c>
@@ -42182,7 +42246,7 @@
         <v>0.38975295617822353</v>
       </c>
     </row>
-    <row r="110" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>13</v>
       </c>
@@ -42265,7 +42329,7 @@
         <v>0.18031544078576742</v>
       </c>
     </row>
-    <row r="111" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>14</v>
       </c>
@@ -42348,7 +42412,7 @@
         <v>0.22202818712711603</v>
       </c>
     </row>
-    <row r="112" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>15</v>
       </c>
@@ -42431,7 +42495,7 @@
         <v>-3.5986237224313211E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>16</v>
       </c>
@@ -42514,7 +42578,7 @@
         <v>-0.19719024690254594</v>
       </c>
     </row>
-    <row r="114" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>17</v>
       </c>
@@ -42597,7 +42661,7 @@
         <v>-0.26353988069316525</v>
       </c>
     </row>
-    <row r="115" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>18</v>
       </c>
@@ -42680,7 +42744,7 @@
         <v>-0.114817589943775</v>
       </c>
     </row>
-    <row r="116" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>19</v>
       </c>
@@ -42763,7 +42827,7 @@
         <v>0.34470553774825213</v>
       </c>
     </row>
-    <row r="117" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>20</v>
       </c>
@@ -42846,7 +42910,7 @@
         <v>-0.16614510917506134</v>
       </c>
     </row>
-    <row r="118" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>21</v>
       </c>
@@ -42929,7 +42993,7 @@
         <v>-0.75903892741456302</v>
       </c>
     </row>
-    <row r="119" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>22</v>
       </c>
@@ -43012,7 +43076,7 @@
         <v>-1.4912564087038236E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>23</v>
       </c>
@@ -43095,7 +43159,7 @@
         <v>-0.17396207697380037</v>
       </c>
     </row>
-    <row r="121" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>24</v>
       </c>
@@ -43178,7 +43242,7 @@
         <v>-0.13971909935658441</v>
       </c>
     </row>
-    <row r="122" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>25</v>
       </c>
@@ -43261,7 +43325,7 @@
         <v>0.40211757717383378</v>
       </c>
     </row>
-    <row r="123" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>26</v>
       </c>
@@ -43344,7 +43408,7 @@
         <v>0.18313533440208066</v>
       </c>
     </row>
-    <row r="124" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>27</v>
       </c>
@@ -43427,7 +43491,7 @@
         <v>0.22566608737329294</v>
       </c>
     </row>
-    <row r="125" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>28</v>
       </c>
@@ -43510,7 +43574,7 @@
         <v>-3.7456848986658464E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>29</v>
       </c>
@@ -43593,7 +43657,7 @@
         <v>-0.21267994555977024</v>
       </c>
     </row>
-    <row r="127" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>30</v>
       </c>
@@ -43676,7 +43740,7 @@
         <v>-0.2674527790746834</v>
       </c>
     </row>
-    <row r="128" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>31</v>
       </c>
@@ -43759,7 +43823,7 @@
         <v>-0.11245437744379867</v>
       </c>
     </row>
-    <row r="129" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>32</v>
       </c>
@@ -43842,7 +43906,7 @@
         <v>0.3109013348788397</v>
       </c>
     </row>
-    <row r="130" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>1</v>
       </c>
@@ -43925,7 +43989,7 @@
         <v>0.2307535183084562</v>
       </c>
     </row>
-    <row r="131" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>2</v>
       </c>
@@ -44008,7 +44072,7 @@
         <v>-3.531095206826363E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>3</v>
       </c>
@@ -44091,7 +44155,7 @@
         <v>-0.2146930384344056</v>
       </c>
     </row>
-    <row r="133" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>4</v>
       </c>
@@ -44174,7 +44238,7 @@
         <v>-0.2546406723509716</v>
       </c>
     </row>
-    <row r="134" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>5</v>
       </c>
@@ -44257,7 +44321,7 @@
         <v>-0.12220395679471781</v>
       </c>
     </row>
-    <row r="135" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>6</v>
       </c>
@@ -44340,7 +44404,7 @@
         <v>0.30166028657189642</v>
       </c>
     </row>
-    <row r="136" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>7</v>
       </c>
@@ -44423,7 +44487,7 @@
         <v>-0.18167805818432164</v>
       </c>
     </row>
-    <row r="137" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>8</v>
       </c>
@@ -44506,7 +44570,7 @@
         <v>-0.73052453371612514</v>
       </c>
     </row>
-    <row r="138" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>9</v>
       </c>
@@ -44589,7 +44653,7 @@
         <v>-1.5009826760444123E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>10</v>
       </c>
@@ -44672,7 +44736,7 @@
         <v>-0.15860070411137861</v>
       </c>
     </row>
-    <row r="140" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>11</v>
       </c>
@@ -44755,7 +44819,7 @@
         <v>-0.13730456798862051</v>
       </c>
     </row>
-    <row r="141" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>12</v>
       </c>
@@ -44838,7 +44902,7 @@
         <v>0.36839082356962832</v>
       </c>
     </row>
-    <row r="142" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>13</v>
       </c>
@@ -44921,7 +44985,7 @@
         <v>0.18245761903417482</v>
       </c>
     </row>
-    <row r="143" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>14</v>
       </c>
@@ -45004,7 +45068,7 @@
         <v>0.22742473480474143</v>
       </c>
     </row>
-    <row r="144" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>15</v>
       </c>
@@ -45087,7 +45151,7 @@
         <v>-3.2943145724916648E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>16</v>
       </c>
@@ -45170,7 +45234,7 @@
         <v>-0.22637920635014494</v>
       </c>
     </row>
-    <row r="146" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>17</v>
       </c>
@@ -45253,7 +45317,7 @@
         <v>-0.26054650878898294</v>
       </c>
     </row>
-    <row r="147" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>18</v>
       </c>
@@ -45336,7 +45400,7 @@
         <v>-0.11699798865364913</v>
       </c>
     </row>
-    <row r="148" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>19</v>
       </c>
@@ -45419,7 +45483,7 @@
         <v>0.34963630090064257</v>
       </c>
     </row>
-    <row r="149" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>20</v>
       </c>
@@ -45502,7 +45566,7 @@
         <v>-0.17279007194861853</v>
       </c>
     </row>
-    <row r="150" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>21</v>
       </c>
@@ -45585,7 +45649,7 @@
         <v>-0.78430854703951447</v>
       </c>
     </row>
-    <row r="151" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>22</v>
       </c>
@@ -45668,7 +45732,7 @@
         <v>-1.5923976692796063E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>23</v>
       </c>
@@ -45751,7 +45815,7 @@
         <v>-0.16803320521638915</v>
       </c>
     </row>
-    <row r="153" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>24</v>
       </c>
@@ -45834,7 +45898,7 @@
         <v>-0.13354300735013738</v>
       </c>
     </row>
-    <row r="154" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>25</v>
       </c>
@@ -45917,7 +45981,7 @@
         <v>0.40066736701528766</v>
       </c>
     </row>
-    <row r="155" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>26</v>
       </c>
@@ -46000,7 +46064,7 @@
         <v>0.18382947054603144</v>
       </c>
     </row>
-    <row r="156" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>27</v>
       </c>
@@ -46083,7 +46147,7 @@
         <v>0.2406992658908256</v>
       </c>
     </row>
-    <row r="157" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>28</v>
       </c>
@@ -46166,7 +46230,7 @@
         <v>-3.5585336327689121E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>29</v>
       </c>
@@ -46249,7 +46313,7 @@
         <v>-0.20896388103592764</v>
       </c>
     </row>
-    <row r="159" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>30</v>
       </c>
@@ -46332,7 +46396,7 @@
         <v>-0.27406735598634852</v>
       </c>
     </row>
-    <row r="160" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>31</v>
       </c>
@@ -46415,7 +46479,7 @@
         <v>-0.11233777161752428</v>
       </c>
     </row>
-    <row r="161" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>32</v>
       </c>
@@ -46498,7 +46562,7 @@
         <v>0.32548686065234889</v>
       </c>
     </row>
-    <row r="162" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>1</v>
       </c>
@@ -46581,7 +46645,7 @@
         <v>0.21888830163862186</v>
       </c>
     </row>
-    <row r="163" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>2</v>
       </c>
@@ -46664,7 +46728,7 @@
         <v>-3.5272270856435729E-2</v>
       </c>
     </row>
-    <row r="164" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>3</v>
       </c>
@@ -46747,7 +46811,7 @@
         <v>-0.20031496104475072</v>
       </c>
     </row>
-    <row r="165" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>4</v>
       </c>
@@ -46830,7 +46894,7 @@
         <v>-0.28323005944518853</v>
       </c>
     </row>
-    <row r="166" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>5</v>
       </c>
@@ -46913,7 +46977,7 @@
         <v>-0.12143617811566067</v>
       </c>
     </row>
-    <row r="167" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>6</v>
       </c>
@@ -46996,7 +47060,7 @@
         <v>0.33277688952051449</v>
       </c>
     </row>
-    <row r="168" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>7</v>
       </c>
@@ -47079,7 +47143,7 @@
         <v>-0.16502112180551265</v>
       </c>
     </row>
-    <row r="169" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>8</v>
       </c>
@@ -47162,7 +47226,7 @@
         <v>-0.80624253037920024</v>
       </c>
     </row>
-    <row r="170" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>9</v>
       </c>
@@ -47245,7 +47309,7 @@
         <v>-1.5421612694464655E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>10</v>
       </c>
@@ -47328,7 +47392,7 @@
         <v>-0.16208131145492288</v>
       </c>
     </row>
-    <row r="172" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>11</v>
       </c>
@@ -47411,7 +47475,7 @@
         <v>-0.13091245446272495</v>
       </c>
     </row>
-    <row r="173" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>12</v>
       </c>
@@ -47494,7 +47558,7 @@
         <v>0.35947356602414998</v>
       </c>
     </row>
-    <row r="174" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>13</v>
       </c>
@@ -47577,7 +47641,7 @@
         <v>0.16985537032829737</v>
       </c>
     </row>
-    <row r="175" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>14</v>
       </c>
@@ -47660,7 +47724,7 @@
         <v>0.22507598645748134</v>
       </c>
     </row>
-    <row r="176" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>15</v>
       </c>
@@ -47743,7 +47807,7 @@
         <v>-3.1997908184051932E-2</v>
       </c>
     </row>
-    <row r="177" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>16</v>
       </c>
@@ -47826,7 +47890,7 @@
         <v>-0.20988415174255701</v>
       </c>
     </row>
-    <row r="178" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>17</v>
       </c>
@@ -47909,7 +47973,7 @@
         <v>-0.2796749754294815</v>
       </c>
     </row>
-    <row r="179" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>18</v>
       </c>
@@ -47992,7 +48056,7 @@
         <v>-0.11288777572189508</v>
       </c>
     </row>
-    <row r="180" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>19</v>
       </c>
@@ -48075,7 +48139,7 @@
         <v>0.32229740285695407</v>
       </c>
     </row>
-    <row r="181" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>20</v>
       </c>
@@ -48158,7 +48222,7 @@
         <v>-0.16773482769106485</v>
       </c>
     </row>
-    <row r="182" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>21</v>
       </c>
@@ -48241,7 +48305,7 @@
         <v>-0.82928999105755041</v>
       </c>
     </row>
-    <row r="183" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>22</v>
       </c>
@@ -48324,7 +48388,7 @@
         <v>-1.4860788120205935E-2</v>
       </c>
     </row>
-    <row r="184" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>23</v>
       </c>
@@ -48407,7 +48471,7 @@
         <v>-0.16161192709571529</v>
       </c>
     </row>
-    <row r="185" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>24</v>
       </c>
@@ -48490,7 +48554,7 @@
         <v>-0.13035772393242473</v>
       </c>
     </row>
-    <row r="186" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>25</v>
       </c>
@@ -48573,7 +48637,7 @@
         <v>0.36650325620326013</v>
       </c>
     </row>
-    <row r="187" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>26</v>
       </c>
@@ -48656,7 +48720,7 @@
         <v>0.19318789433785161</v>
       </c>
     </row>
-    <row r="188" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>27</v>
       </c>
@@ -48739,7 +48803,7 @@
         <v>0.22473047552438052</v>
       </c>
     </row>
-    <row r="189" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>28</v>
       </c>
@@ -48822,7 +48886,7 @@
         <v>-3.206094483016203E-2</v>
       </c>
     </row>
-    <row r="190" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>29</v>
       </c>
@@ -48905,7 +48969,7 @@
         <v>-0.20327853343157756</v>
       </c>
     </row>
-    <row r="191" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>30</v>
       </c>
@@ -48988,7 +49052,7 @@
         <v>-0.26648446469407749</v>
       </c>
     </row>
-    <row r="192" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>31</v>
       </c>
@@ -49071,7 +49135,7 @@
         <v>-0.1122573573137703</v>
       </c>
     </row>
-    <row r="193" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>32</v>
       </c>
@@ -49154,7 +49218,7 @@
         <v>0.33023862951028665</v>
       </c>
     </row>
-    <row r="194" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>1</v>
       </c>
@@ -49237,7 +49301,7 @@
         <v>0.34129538164225937</v>
       </c>
     </row>
-    <row r="195" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>2</v>
       </c>
@@ -49320,7 +49384,7 @@
         <v>5.3833481319321141E-3</v>
       </c>
     </row>
-    <row r="196" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>3</v>
       </c>
@@ -49403,7 +49467,7 @@
         <v>-0.178702442907301</v>
       </c>
     </row>
-    <row r="197" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>4</v>
       </c>
@@ -49486,7 +49550,7 @@
         <v>-0.25843427198662428</v>
       </c>
     </row>
-    <row r="198" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>5</v>
       </c>
@@ -49569,7 +49633,7 @@
         <v>-3.3323073312274763E-2</v>
       </c>
     </row>
-    <row r="199" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>6</v>
       </c>
@@ -49652,7 +49716,7 @@
         <v>0.40320032542354517</v>
       </c>
     </row>
-    <row r="200" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>7</v>
       </c>
@@ -49735,7 +49799,7 @@
         <v>-0.15263910926371257</v>
       </c>
     </row>
-    <row r="201" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>8</v>
       </c>
@@ -49818,7 +49882,7 @@
         <v>-0.82565871664279178</v>
       </c>
     </row>
-    <row r="202" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>9</v>
       </c>
@@ -49901,7 +49965,7 @@
         <v>-9.0170305740912161E-3</v>
       </c>
     </row>
-    <row r="203" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>10</v>
       </c>
@@ -49984,7 +50048,7 @@
         <v>-8.9625737462220023E-2</v>
       </c>
     </row>
-    <row r="204" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>11</v>
       </c>
@@ -50067,7 +50131,7 @@
         <v>-0.12162824610174412</v>
       </c>
     </row>
-    <row r="205" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>12</v>
       </c>
@@ -50150,7 +50214,7 @@
         <v>0.46297428949727881</v>
       </c>
     </row>
-    <row r="206" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>13</v>
       </c>
@@ -50233,7 +50297,7 @@
         <v>0.20938376872673248</v>
       </c>
     </row>
-    <row r="207" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>14</v>
       </c>
@@ -50316,7 +50380,7 @@
         <v>0.32791124902883739</v>
       </c>
     </row>
-    <row r="208" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>15</v>
       </c>
@@ -50399,7 +50463,7 @@
         <v>5.6053418693313766E-3</v>
       </c>
     </row>
-    <row r="209" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>16</v>
       </c>
@@ -50482,7 +50546,7 @@
         <v>-0.18246459960008629</v>
       </c>
     </row>
-    <row r="210" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>17</v>
       </c>
@@ -50565,7 +50629,7 @@
         <v>-0.25316010317057075</v>
       </c>
     </row>
-    <row r="211" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>18</v>
       </c>
@@ -50648,7 +50712,7 @@
         <v>-3.0784172488482395E-2</v>
       </c>
     </row>
-    <row r="212" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>19</v>
       </c>
@@ -50731,7 +50795,7 @@
         <v>0.42377177059821586</v>
       </c>
     </row>
-    <row r="213" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>20</v>
       </c>
@@ -50814,7 +50878,7 @@
         <v>-0.14522944376547409</v>
       </c>
     </row>
-    <row r="214" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>21</v>
       </c>
@@ -50897,7 +50961,7 @@
         <v>-0.8686617748012706</v>
       </c>
     </row>
-    <row r="215" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>22</v>
       </c>
@@ -50980,7 +51044,7 @@
         <v>-8.7569239229155077E-3</v>
       </c>
     </row>
-    <row r="216" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>23</v>
       </c>
@@ -51063,7 +51127,7 @@
         <v>-9.6027575852378602E-2</v>
       </c>
     </row>
-    <row r="217" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>24</v>
       </c>
@@ -51146,7 +51210,7 @@
         <v>-0.11461123190356658</v>
       </c>
     </row>
-    <row r="218" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>25</v>
       </c>
@@ -51229,7 +51293,7 @@
         <v>0.49604388160422735</v>
       </c>
     </row>
-    <row r="219" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>26</v>
       </c>
@@ -51312,7 +51376,7 @@
         <v>0.20523755548461897</v>
       </c>
     </row>
-    <row r="220" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>27</v>
       </c>
@@ -51395,7 +51459,7 @@
         <v>0.32791124902883739</v>
       </c>
     </row>
-    <row r="221" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>28</v>
       </c>
@@ -51478,7 +51542,7 @@
         <v>5.6608403036811925E-3</v>
       </c>
     </row>
-    <row r="222" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>29</v>
       </c>
@@ -51561,7 +51625,7 @@
         <v>-0.19751322637122745</v>
       </c>
     </row>
-    <row r="223" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>30</v>
       </c>
@@ -51644,7 +51708,7 @@
         <v>-0.27425677843478496</v>
       </c>
     </row>
-    <row r="224" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>31</v>
       </c>
@@ -51727,7 +51791,7 @@
         <v>-3.0784172488482395E-2</v>
       </c>
     </row>
-    <row r="225" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>32</v>
       </c>
@@ -51810,7 +51874,7 @@
         <v>0.4196574815632817</v>
       </c>
     </row>
-    <row r="226" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>1</v>
       </c>
@@ -51893,7 +51957,7 @@
         <v>0.34119500064765867</v>
       </c>
     </row>
-    <row r="227" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>2</v>
       </c>
@@ -51976,7 +52040,7 @@
         <v>5.4876851885097668E-3</v>
       </c>
     </row>
-    <row r="228" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>3</v>
       </c>
@@ -52059,7 +52123,7 @@
         <v>-0.19181355898165775</v>
       </c>
     </row>
-    <row r="229" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>4</v>
       </c>
@@ -52142,7 +52206,7 @@
         <v>-0.28248448178782853</v>
       </c>
     </row>
-    <row r="230" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>5</v>
       </c>
@@ -52225,7 +52289,7 @@
         <v>-3.1053930701010334E-2</v>
       </c>
     </row>
-    <row r="231" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>6</v>
       </c>
@@ -52308,7 +52372,7 @@
         <v>0.43648492371616232</v>
       </c>
     </row>
-    <row r="232" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>7</v>
       </c>
@@ -52391,7 +52455,7 @@
         <v>-0.15569189144898682</v>
       </c>
     </row>
-    <row r="233" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>8</v>
       </c>
@@ -52474,7 +52538,7 @@
         <v>-0.92129751798724857</v>
       </c>
     </row>
-    <row r="234" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>9</v>
       </c>
@@ -52557,7 +52621,7 @@
         <v>-8.4838119391810133E-3</v>
       </c>
     </row>
-    <row r="235" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>10</v>
       </c>
@@ -52640,7 +52704,7 @@
         <v>-9.6082448752865673E-2</v>
       </c>
     </row>
-    <row r="236" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>11</v>
       </c>
@@ -52723,7 +52787,7 @@
         <v>-0.12166333117273501</v>
       </c>
     </row>
-    <row r="237" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>12</v>
       </c>
@@ -52806,7 +52870,7 @@
         <v>0.46713160964786665</v>
       </c>
     </row>
-    <row r="238" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>13</v>
       </c>
@@ -52889,7 +52953,7 @@
         <v>0.21780058160822294</v>
       </c>
     </row>
-    <row r="239" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>14</v>
       </c>
@@ -52972,7 +53036,7 @@
         <v>0.33774858649970252</v>
       </c>
     </row>
-    <row r="240" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>15</v>
       </c>
@@ -53055,7 +53119,7 @@
         <v>5.4876851885097668E-3</v>
       </c>
     </row>
-    <row r="241" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>16</v>
       </c>
@@ -53138,7 +53202,7 @@
         <v>-0.19375106967844216</v>
       </c>
     </row>
-    <row r="242" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>17</v>
       </c>
@@ -53221,7 +53285,7 @@
         <v>-0.26618730014622299</v>
       </c>
     </row>
-    <row r="243" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>18</v>
       </c>
@@ -53304,7 +53368,7 @@
         <v>-3.1707697663136865E-2</v>
       </c>
     </row>
-    <row r="244" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>19</v>
       </c>
@@ -53387,7 +53451,7 @@
         <v>0.43648492371616232</v>
       </c>
     </row>
-    <row r="245" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>20</v>
       </c>
@@ -53470,7 +53534,7 @@
         <v>-0.14653354489316406</v>
       </c>
     </row>
-    <row r="246" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>21</v>
       </c>
@@ -53553,7 +53617,7 @@
         <v>-0.93015614796789525</v>
       </c>
     </row>
-    <row r="247" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>22</v>
       </c>
@@ -53636,7 +53700,7 @@
         <v>-8.4838119391810133E-3</v>
       </c>
     </row>
-    <row r="248" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>23</v>
       </c>
@@ -53719,7 +53783,7 @@
         <v>-9.7024433544560432E-2</v>
       </c>
     </row>
-    <row r="249" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>24</v>
       </c>
@@ -53802,7 +53866,7 @@
         <v>-0.12407250604744263</v>
       </c>
     </row>
-    <row r="250" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>25</v>
       </c>
@@ -53885,7 +53949,7 @@
         <v>0.49632733525085837</v>
       </c>
     </row>
-    <row r="251" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>26</v>
       </c>
@@ -53968,7 +54032,7 @@
         <v>0.21352998196884601</v>
       </c>
     </row>
-    <row r="252" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>27</v>
       </c>
@@ -54051,7 +54115,7 @@
         <v>0.3549806572394833</v>
       </c>
     </row>
-    <row r="253" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>28</v>
       </c>
@@ -54134,7 +54198,7 @@
         <v>5.8878289001719382E-3</v>
       </c>
     </row>
-    <row r="254" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>29</v>
       </c>
@@ -54217,7 +54281,7 @@
         <v>-0.19181355898165775</v>
       </c>
     </row>
-    <row r="255" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>30</v>
       </c>
@@ -54300,7 +54364,7 @@
         <v>-0.28248448178782853</v>
       </c>
     </row>
-    <row r="256" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>31</v>
       </c>
@@ -54383,7 +54447,7 @@
         <v>-3.33421150684532E-2</v>
       </c>
     </row>
-    <row r="257" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>32</v>
       </c>
@@ -54466,7 +54530,7 @@
         <v>0.4068208997742872</v>
       </c>
     </row>
-    <row r="258" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>1</v>
       </c>
@@ -54549,7 +54613,7 @@
         <v>0.33446947400941418</v>
       </c>
     </row>
-    <row r="259" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>2</v>
       </c>
@@ -54632,7 +54696,7 @@
         <v>5.6042319006443797E-3</v>
       </c>
     </row>
-    <row r="260" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>3</v>
       </c>
@@ -54715,7 +54779,7 @@
         <v>-0.182276491765447</v>
       </c>
     </row>
-    <row r="261" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>4</v>
       </c>
@@ -54798,7 +54862,7 @@
         <v>-0.27699934621913286</v>
       </c>
     </row>
-    <row r="262" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>5</v>
       </c>
@@ -54881,7 +54945,7 @@
         <v>-3.2361464625263403E-2</v>
       </c>
     </row>
-    <row r="263" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>6</v>
       </c>
@@ -54964,7 +55028,7 @@
         <v>0.39908603638861101</v>
       </c>
     </row>
-    <row r="264" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>7</v>
       </c>
@@ -55047,7 +55111,7 @@
         <v>-0.15115717616406488</v>
       </c>
     </row>
-    <row r="265" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>8</v>
       </c>
@@ -55130,7 +55194,7 @@
         <v>-0.80914554230993596</v>
       </c>
     </row>
-    <row r="266" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>9</v>
       </c>
@@ -55213,7 +55277,7 @@
         <v>-8.406646965998887E-3</v>
       </c>
     </row>
-    <row r="267" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>10</v>
       </c>
@@ -55296,7 +55360,7 @@
         <v>-8.7824077229561093E-2</v>
       </c>
     </row>
-    <row r="268" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>11</v>
       </c>
@@ -55379,7 +55443,7 @@
         <v>-0.12048213378270846</v>
       </c>
     </row>
-    <row r="269" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>12</v>
       </c>
@@ -55462,7 +55526,7 @@
         <v>0.46769851694112857</v>
       </c>
     </row>
-    <row r="270" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>13</v>
       </c>
@@ -55545,7 +55609,7 @@
         <v>0.1970280532652342</v>
       </c>
     </row>
-    <row r="271" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A271">
         <v>14</v>
       </c>
@@ -55628,7 +55692,7 @@
         <v>0.33125728218219291</v>
       </c>
     </row>
-    <row r="272" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>15</v>
       </c>
@@ -55711,7 +55775,7 @@
         <v>5.6042319006443797E-3</v>
       </c>
     </row>
-    <row r="273" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>16</v>
       </c>
@@ -55794,7 +55858,7 @@
         <v>-0.18611389159208799</v>
       </c>
     </row>
-    <row r="274" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>17</v>
       </c>
@@ -55877,7 +55941,7 @@
         <v>-0.25068124382702556</v>
       </c>
     </row>
-    <row r="275" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>18</v>
       </c>
@@ -55960,7 +56024,7 @@
         <v>-3.2688348106326669E-2</v>
       </c>
     </row>
-    <row r="276" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>19</v>
       </c>
@@ -56043,7 +56107,7 @@
         <v>0.39497174735367691</v>
       </c>
     </row>
-    <row r="277" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>20</v>
       </c>
@@ -56126,7 +56190,7 @@
         <v>-0.148178490633773</v>
       </c>
     </row>
-    <row r="278" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>21</v>
       </c>
@@ -56209,7 +56273,7 @@
         <v>-0.85971713870430699</v>
       </c>
     </row>
-    <row r="279" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>22</v>
       </c>
@@ -56292,7 +56356,7 @@
         <v>-8.6667536171745954E-3</v>
       </c>
     </row>
-    <row r="280" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>23</v>
       </c>
@@ -56375,7 +56439,7 @@
         <v>-8.8674607187110732E-2</v>
       </c>
     </row>
-    <row r="281" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A281">
         <v>24</v>
       </c>
@@ -56458,7 +56522,7 @@
         <v>-0.1134651195845309</v>
       </c>
     </row>
-    <row r="282" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A282">
         <v>25</v>
       </c>
@@ -56541,7 +56605,7 @@
         <v>0.46741506329449761</v>
       </c>
     </row>
-    <row r="283" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>26</v>
       </c>
@@ -56624,7 +56688,7 @@
         <v>0.20731066210567572</v>
       </c>
     </row>
-    <row r="284" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A284">
         <v>27</v>
       </c>
@@ -56707,7 +56771,7 @@
         <v>0.33105652019299159</v>
       </c>
     </row>
-    <row r="285" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>28</v>
       </c>
@@ -56790,7 +56854,7 @@
         <v>5.6042319006443797E-3</v>
       </c>
     </row>
-    <row r="286" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A286">
         <v>29</v>
       </c>
@@ -56873,7 +56937,7 @@
         <v>-0.18434567794647894</v>
       </c>
     </row>
-    <row r="287" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>30</v>
       </c>
@@ -56956,7 +57020,7 @@
         <v>-0.25068124382702556</v>
       </c>
     </row>
-    <row r="288" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>31</v>
       </c>
@@ -57039,7 +57103,7 @@
         <v>-3.265661184602927E-2</v>
       </c>
     </row>
-    <row r="289" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>32</v>
       </c>
@@ -57122,7 +57186,7 @@
         <v>0.41126433193201606</v>
       </c>
     </row>
-    <row r="290" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>1</v>
       </c>
@@ -57205,7 +57269,7 @@
         <v>0.19741312877482328</v>
       </c>
     </row>
-    <row r="291" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>2</v>
       </c>
@@ -57288,7 +57352,7 @@
         <v>-5.5509142443077385E-2</v>
       </c>
     </row>
-    <row r="292" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>3</v>
       </c>
@@ -57371,7 +57435,7 @@
         <v>-0.23134604557356478</v>
       </c>
     </row>
-    <row r="293" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>4</v>
       </c>
@@ -57454,7 +57518,7 @@
         <v>-0.25544176041861333</v>
       </c>
     </row>
-    <row r="294" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>5</v>
       </c>
@@ -57537,7 +57601,7 @@
         <v>-0.16270967775809597</v>
       </c>
     </row>
-    <row r="295" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>6</v>
       </c>
@@ -57620,7 +57684,7 @@
         <v>0.28175225412934646</v>
       </c>
     </row>
-    <row r="296" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>7</v>
       </c>
@@ -57703,7 +57767,7 @@
         <v>-0.16598751427602706</v>
       </c>
     </row>
-    <row r="297" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>8</v>
       </c>
@@ -57786,7 +57850,7 @@
         <v>-0.78959093885493115</v>
       </c>
     </row>
-    <row r="298" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>9</v>
       </c>
@@ -57869,7 +57933,7 @@
         <v>-1.7461412185552319E-2</v>
       </c>
     </row>
-    <row r="299" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>10</v>
       </c>
@@ -57952,7 +58016,7 @@
         <v>-0.20535899678772981</v>
       </c>
     </row>
-    <row r="300" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>11</v>
       </c>
@@ -58035,7 +58099,7 @@
         <v>-0.15839849252461777</v>
       </c>
     </row>
-    <row r="301" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>12</v>
       </c>
@@ -58118,7 +58182,7 @@
         <v>0.35245854912687019</v>
       </c>
     </row>
-    <row r="302" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A302">
         <v>13</v>
       </c>
@@ -58201,7 +58265,7 @@
         <v>0.16081225716204761</v>
       </c>
     </row>
-    <row r="303" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>14</v>
       </c>
@@ -58284,7 +58348,7 @@
         <v>0.18153397104662145</v>
       </c>
     </row>
-    <row r="304" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A304">
         <v>15</v>
       </c>
@@ -58367,7 +58431,7 @@
         <v>-5.3909329683069378E-2</v>
       </c>
     </row>
-    <row r="305" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A305">
         <v>16</v>
       </c>
@@ -58450,7 +58514,7 @@
         <v>-0.23080100618241389</v>
       </c>
     </row>
-    <row r="306" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A306">
         <v>17</v>
       </c>
@@ -58533,7 +58597,7 @@
         <v>-0.27885065903039274</v>
       </c>
     </row>
-    <row r="307" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A307">
         <v>18</v>
       </c>
@@ -58616,7 +58680,7 @@
         <v>-0.16569544452305959</v>
       </c>
     </row>
-    <row r="308" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A308">
         <v>19</v>
       </c>
@@ -58699,7 +58763,7 @@
         <v>0.28621185639236219</v>
       </c>
     </row>
-    <row r="309" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A309">
         <v>20</v>
       </c>
@@ -58782,7 +58846,7 @@
         <v>-0.17556626662073285</v>
       </c>
     </row>
-    <row r="310" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A310">
         <v>21</v>
       </c>
@@ -58865,7 +58929,7 @@
         <v>-0.81163218696209283</v>
       </c>
     </row>
-    <row r="311" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A311">
         <v>22</v>
       </c>
@@ -58948,7 +59012,7 @@
         <v>-1.8636473990565453E-2</v>
       </c>
     </row>
-    <row r="312" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A312">
         <v>23</v>
       </c>
@@ -59031,7 +59095,7 @@
         <v>-0.20315565508373407</v>
       </c>
     </row>
-    <row r="313" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A313">
         <v>24</v>
       </c>
@@ -59114,7 +59178,7 @@
         <v>-0.1452795221048481</v>
       </c>
     </row>
-    <row r="314" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A314">
         <v>25</v>
       </c>
@@ -59197,7 +59261,7 @@
         <v>0.33261161368040337</v>
       </c>
     </row>
-    <row r="315" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A315">
         <v>26</v>
       </c>
@@ -59280,7 +59344,7 @@
         <v>0.15937158615163902</v>
       </c>
     </row>
-    <row r="316" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A316">
         <v>27</v>
       </c>
@@ -59363,7 +59427,7 @@
         <v>0.18582768868086444</v>
       </c>
     </row>
-    <row r="317" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A317">
         <v>28</v>
       </c>
@@ -59446,7 +59510,7 @@
         <v>-5.5020829672942043E-2</v>
       </c>
     </row>
-    <row r="318" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A318">
         <v>29</v>
       </c>
@@ -59529,7 +59593,7 @@
         <v>-0.23222911792352124</v>
       </c>
     </row>
-    <row r="319" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A319">
         <v>30</v>
       </c>
@@ -59612,7 +59676,7 @@
         <v>-0.30671134309338133</v>
       </c>
     </row>
-    <row r="320" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A320">
         <v>31</v>
       </c>
@@ -59695,7 +59759,7 @@
         <v>-0.14803193051300698</v>
       </c>
     </row>
-    <row r="321" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A321">
         <v>32</v>
       </c>
@@ -59778,7 +59842,7 @@
         <v>0.28914801574595983</v>
       </c>
     </row>
-    <row r="322" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A322">
         <v>1</v>
       </c>
@@ -59861,7 +59925,7 @@
         <v>0.17598171361019971</v>
       </c>
     </row>
-    <row r="323" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A323">
         <v>2</v>
       </c>
@@ -59944,7 +60008,7 @@
         <v>-4.9841411421543011E-2</v>
       </c>
     </row>
-    <row r="324" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A324">
         <v>3</v>
       </c>
@@ -60027,7 +60091,7 @@
         <v>-0.22467411938961626</v>
       </c>
     </row>
-    <row r="325" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A325">
         <v>4</v>
       </c>
@@ -60110,7 +60174,7 @@
         <v>-0.26521910394337467</v>
       </c>
     </row>
-    <row r="326" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A326">
         <v>5</v>
       </c>
@@ -60193,7 +60257,7 @@
         <v>-0.15892035534779669</v>
       </c>
     </row>
-    <row r="327" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A327">
         <v>6</v>
       </c>
@@ -60276,7 +60340,7 @@
         <v>0.28807906682082157</v>
       </c>
     </row>
-    <row r="328" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A328">
         <v>7</v>
       </c>
@@ -60359,7 +60423,7 @@
         <v>-0.18183163125384061</v>
       </c>
     </row>
-    <row r="329" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A329">
         <v>8</v>
       </c>
@@ -60442,7 +60506,7 @@
         <v>-0.77397826887815169</v>
       </c>
     </row>
-    <row r="330" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A330">
         <v>9</v>
       </c>
@@ -60525,7 +60589,7 @@
         <v>-1.7694522489840651E-2</v>
       </c>
     </row>
-    <row r="331" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A331">
         <v>10</v>
       </c>
@@ -60608,7 +60672,7 @@
         <v>-0.21201497421934132</v>
       </c>
     </row>
-    <row r="332" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A332">
         <v>11</v>
       </c>
@@ -60691,7 +60755,7 @@
         <v>-0.14546822093702438</v>
       </c>
     </row>
-    <row r="333" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A333">
         <v>12</v>
       </c>
@@ -60774,7 +60838,7 @@
         <v>0.33574541709400801</v>
       </c>
     </row>
-    <row r="334" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A334">
         <v>13</v>
       </c>
@@ -60857,7 +60921,7 @@
         <v>0.17012409886981447</v>
       </c>
     </row>
-    <row r="335" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A335">
         <v>14</v>
       </c>
@@ -60940,7 +61004,7 @@
         <v>0.19069977867171825</v>
       </c>
     </row>
-    <row r="336" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A336">
         <v>15</v>
       </c>
@@ -61023,7 +61087,7 @@
         <v>-5.7210265799620144E-2</v>
       </c>
     </row>
-    <row r="337" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A337">
         <v>16</v>
       </c>
@@ -61106,7 +61170,7 @@
         <v>-0.21563720722343019</v>
       </c>
     </row>
-    <row r="338" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A338">
         <v>17</v>
       </c>
@@ -61189,7 +61253,7 @@
         <v>-0.26837877793199727</v>
       </c>
     </row>
-    <row r="339" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A339">
         <v>18</v>
       </c>
@@ -61272,7 +61336,7 @@
         <v>-0.14771910888517525</v>
       </c>
     </row>
-    <row r="340" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A340">
         <v>19</v>
       </c>
@@ -61355,7 +61419,7 @@
         <v>0.28083148365021204</v>
       </c>
     </row>
-    <row r="341" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A341">
         <v>20</v>
       </c>
@@ -61438,7 +61502,7 @@
         <v>-0.17585624758952306</v>
       </c>
     </row>
-    <row r="342" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A342">
         <v>21</v>
       </c>
@@ -61521,7 +61585,7 @@
         <v>-0.78804596031672758</v>
       </c>
     </row>
-    <row r="343" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A343">
         <v>22</v>
       </c>
@@ -61604,7 +61668,7 @@
         <v>-1.835223675063001E-2</v>
       </c>
     </row>
-    <row r="344" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A344">
         <v>23</v>
       </c>
@@ -61687,7 +61751,7 @@
         <v>-0.21786598903212359</v>
       </c>
     </row>
-    <row r="345" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A345">
         <v>24</v>
       </c>
@@ -61770,7 +61834,7 @@
         <v>-0.14572406395195864</v>
       </c>
     </row>
-    <row r="346" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A346">
         <v>25</v>
       </c>
@@ -61853,7 +61917,7 @@
         <v>0.31752753790946048</v>
       </c>
     </row>
-    <row r="347" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A347">
         <v>26</v>
       </c>
@@ -61936,7 +62000,7 @@
         <v>0.17169500899641987</v>
       </c>
     </row>
-    <row r="348" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A348">
         <v>27</v>
       </c>
@@ -62019,7 +62083,7 @@
         <v>0.18796596099810325</v>
       </c>
     </row>
-    <row r="349" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A349">
         <v>28</v>
       </c>
@@ -62102,7 +62166,7 @@
         <v>-5.952263758544904E-2</v>
       </c>
     </row>
-    <row r="350" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A350">
         <v>29</v>
       </c>
@@ -62185,7 +62249,7 @@
         <v>-0.23767692657785158</v>
       </c>
     </row>
-    <row r="351" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A351">
         <v>30</v>
       </c>
@@ -62268,7 +62332,7 @@
         <v>-0.28650404464498619</v>
       </c>
     </row>
-    <row r="352" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A352">
         <v>31</v>
       </c>
@@ -62351,7 +62415,7 @@
         <v>-0.15915432150812536</v>
       </c>
     </row>
-    <row r="353" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A353">
         <v>32</v>
       </c>
@@ -62434,7 +62498,7 @@
         <v>0.2731966527474296</v>
       </c>
     </row>
-    <row r="354" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A354">
         <v>1</v>
       </c>
@@ -62517,7 +62581,7 @@
         <v>0.19501476988237185</v>
       </c>
     </row>
-    <row r="355" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A355">
         <v>2</v>
       </c>
@@ -62600,7 +62664,7 @@
         <v>-5.0348330939479588E-2</v>
       </c>
     </row>
-    <row r="356" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A356">
         <v>3</v>
       </c>
@@ -62683,7 +62747,7 @@
         <v>-0.22990682674428603</v>
       </c>
     </row>
-    <row r="357" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A357">
         <v>4</v>
       </c>
@@ -62766,7 +62830,7 @@
         <v>-0.28824220798069622</v>
       </c>
     </row>
-    <row r="358" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A358">
         <v>5</v>
       </c>
@@ -62849,7 +62913,7 @@
         <v>-0.16801064454174258</v>
       </c>
     </row>
-    <row r="359" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A359">
         <v>6</v>
       </c>
@@ -62932,7 +62996,7 @@
         <v>0.28146715869081351</v>
       </c>
     </row>
-    <row r="360" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A360">
         <v>7</v>
       </c>
@@ -63015,7 +63079,7 @@
         <v>-0.19289441956836567</v>
       </c>
     </row>
-    <row r="361" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A361">
         <v>8</v>
       </c>
@@ -63098,7 +63162,7 @@
         <v>-0.69388881502398359</v>
       </c>
     </row>
-    <row r="362" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A362">
         <v>9</v>
       </c>
@@ -63181,7 +63245,7 @@
         <v>-1.9607210627353693E-2</v>
       </c>
     </row>
-    <row r="363" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A363">
         <v>10</v>
       </c>
@@ -63264,7 +63328,7 @@
         <v>-0.20218513468733235</v>
       </c>
     </row>
-    <row r="364" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A364">
         <v>11</v>
       </c>
@@ -63347,7 +63411,7 @@
         <v>-0.15405864171055272</v>
       </c>
     </row>
-    <row r="365" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A365">
         <v>12</v>
       </c>
@@ -63430,7 +63494,7 @@
         <v>0.35124673238676496</v>
       </c>
     </row>
-    <row r="366" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A366">
         <v>13</v>
       </c>
@@ -63513,7 +63577,7 @@
         <v>0.17259242942294106</v>
       </c>
     </row>
-    <row r="367" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A367">
         <v>14</v>
       </c>
@@ -63596,7 +63660,7 @@
         <v>0.18638460350136357</v>
       </c>
     </row>
-    <row r="368" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A368">
         <v>15</v>
       </c>
@@ -63679,7 +63743,7 @@
         <v>-5.2206519974136147E-2</v>
       </c>
     </row>
-    <row r="369" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A369">
         <v>16</v>
       </c>
@@ -63762,7 +63826,7 @@
         <v>-0.22911942200885815</v>
       </c>
     </row>
-    <row r="370" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A370">
         <v>17</v>
       </c>
@@ -63845,7 +63909,7 @@
         <v>-0.27316100913376912</v>
       </c>
     </row>
-    <row r="371" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A371">
         <v>18</v>
       </c>
@@ -63928,7 +63992,7 @@
         <v>-0.16040620618731405</v>
       </c>
     </row>
-    <row r="372" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A372">
         <v>19</v>
       </c>
@@ -64011,7 +64075,7 @@
         <v>0.2995399215497494</v>
       </c>
     </row>
-    <row r="373" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A373">
         <v>20</v>
       </c>
@@ -64094,7 +64158,7 @@
         <v>-0.1733083373249055</v>
       </c>
     </row>
-    <row r="374" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A374">
         <v>21</v>
       </c>
@@ -64177,7 +64241,7 @@
         <v>-0.74294745728710343</v>
       </c>
     </row>
-    <row r="375" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A375">
         <v>22</v>
       </c>
@@ -64260,7 +64324,7 @@
         <v>-1.7942174565296207E-2</v>
       </c>
     </row>
-    <row r="376" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A376">
         <v>23</v>
       </c>
@@ -64343,7 +64407,7 @@
         <v>-0.21312340680918018</v>
       </c>
     </row>
-    <row r="377" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A377">
         <v>24</v>
       </c>
@@ -64426,7 +64490,7 @@
         <v>-0.14504668087687686</v>
       </c>
     </row>
-    <row r="378" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A378">
         <v>25</v>
       </c>
@@ -64509,7 +64573,7 @@
         <v>0.35652131667585779</v>
       </c>
     </row>
-    <row r="379" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A379">
         <v>26</v>
       </c>
@@ -64592,7 +64656,7 @@
         <v>0.17599845361741759</v>
       </c>
     </row>
-    <row r="380" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A380">
         <v>27</v>
       </c>
@@ -64675,7 +64739,7 @@
         <v>0.17351496840262656</v>
       </c>
     </row>
-    <row r="381" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A381">
         <v>28</v>
       </c>
@@ -64758,7 +64822,7 @@
         <v>-5.3810493598558315E-2</v>
       </c>
     </row>
-    <row r="382" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A382">
         <v>29</v>
       </c>
@@ -64841,7 +64905,7 @@
         <v>-0.22489861421211996</v>
       </c>
     </row>
-    <row r="383" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A383">
         <v>30</v>
       </c>
@@ -64924,7 +64988,7 @@
         <v>-0.27287552780237123</v>
       </c>
     </row>
-    <row r="384" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A384">
         <v>31</v>
       </c>
@@ -65007,7 +65071,7 @@
         <v>-0.15444732521633295</v>
       </c>
     </row>
-    <row r="385" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A385">
         <v>32</v>
       </c>
@@ -65098,9 +65162,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FC7B88F-64DB-4C68-8FFC-305A2A41AB55}">
   <dimension ref="A1:AA25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -65183,7 +65247,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -65266,7 +65330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -65349,7 +65413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -65432,7 +65496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -65515,7 +65579,7 @@
         <v>0.5335206744279406</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -65598,7 +65662,7 @@
         <v>0.49739060618225611</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -65681,7 +65745,7 @@
         <v>0.40405459654757125</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -65764,7 +65828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -65847,7 +65911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -65930,7 +65994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -66013,7 +66077,7 @@
         <v>0.36852669610598154</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -66096,7 +66160,7 @@
         <v>0.23966278602970695</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -66179,7 +66243,7 @@
         <v>0.30931352870333201</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -66262,7 +66326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -66345,7 +66409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -66428,7 +66492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -66511,7 +66575,7 @@
         <v>0.4676836611802489</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -66594,7 +66658,7 @@
         <v>0.17442794058611</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -66677,7 +66741,7 @@
         <v>0.34263348052990766</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>14</v>
       </c>
@@ -66760,7 +66824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -66843,7 +66907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -66926,7 +66990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -67009,7 +67073,7 @@
         <v>0.44439983942191891</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -67092,7 +67156,7 @@
         <v>0.50040144520272978</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -67183,9 +67247,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CBBB125-439E-474E-9960-563C78F44B33}">
   <dimension ref="A1:AA25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -67268,7 +67332,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -67351,7 +67415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -67434,7 +67498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -67517,7 +67581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -67600,7 +67664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -67683,7 +67747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -67766,7 +67830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -67849,7 +67913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -67932,7 +67996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -68015,7 +68079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -68098,7 +68162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -68181,7 +68245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -68264,7 +68328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -68347,7 +68411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -68430,7 +68494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -68513,7 +68577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -68596,7 +68660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -68679,7 +68743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -68762,7 +68826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>14</v>
       </c>
@@ -68845,7 +68909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -68928,7 +68992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -69011,7 +69075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -69094,7 +69158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -69177,7 +69241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -69268,13 +69332,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8D12B52-98C9-449E-BF4A-23F7CAD72921}">
   <dimension ref="A1:AA37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.88671875" customWidth="1"/>
+    <col min="1" max="1" width="27.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -69357,7 +69421,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -69440,7 +69504,7 @@
         <v>4.5052000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -69523,7 +69587,7 @@
         <v>-9.797600000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -69606,7 +69670,7 @@
         <v>9.4448000000000025</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -69689,7 +69753,7 @@
         <v>4.5052000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -69772,7 +69836,7 @@
         <v>-9.4056960000000007</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -69855,7 +69919,7 @@
         <v>9.4448000000000025</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -69938,7 +70002,7 @@
         <v>4.3249919999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -70021,7 +70085,7 @@
         <v>-9.8759808000000007</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -70104,7 +70168,7 @@
         <v>9.9170400000000036</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -70187,7 +70251,7 @@
         <v>4.2799399999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -70270,7 +70334,7 @@
         <v>-9.6784611839999997</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -70353,7 +70417,7 @@
         <v>10.115380800000004</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -70436,7 +70500,7 @@
         <v>4.1943412000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -70519,7 +70583,7 @@
         <v>-10.06559963136</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -70602,7 +70666,7 @@
         <v>9.7107655680000047</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -70685,7 +70749,7 @@
         <v>4.1104543759999999</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -70768,7 +70832,7 @@
         <v>-10.06559963136</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -70851,7 +70915,7 @@
         <v>9.4194426009600036</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -70934,7 +70998,7 @@
         <v>4.7079339999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -71017,7 +71081,7 @@
         <v>-10.367567620300798</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -71100,7 +71164,7 @@
         <v>9.5136370269696027</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -71183,7 +71247,7 @@
         <v>4.8020926800000003</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -71266,7 +71330,7 @@
         <v>-10.263891944097791</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -71349,7 +71413,7 @@
         <v>9.7990461377786904</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>16</v>
       </c>
@@ -71432,7 +71496,7 @@
         <v>4.9461554604</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>17</v>
       </c>
@@ -71515,7 +71579,7 @@
         <v>-10.469169782979748</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -71598,7 +71662,7 @@
         <v>9.5050747536453297</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>16</v>
       </c>
@@ -71681,7 +71745,7 @@
         <v>4.4725372999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -71764,7 +71828,7 @@
         <v>-10.992628272128735</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -71847,7 +71911,7 @@
         <v>9.6001255011817825</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>16</v>
       </c>
@@ -71930,7 +71994,7 @@
         <v>4.4725372999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>17</v>
       </c>
@@ -72013,7 +72077,7 @@
         <v>-10.552923141243587</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -72096,7 +72160,7 @@
         <v>9.888129266217236</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>16</v>
       </c>
@@ -72179,7 +72243,7 @@
         <v>4.4278119270000005</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>17</v>
       </c>
@@ -72262,7 +72326,7 @@
         <v>-10.341864678418714</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>18</v>
       </c>

--- a/data/CS7/case33_3/case33_3_operational_data.xlsx
+++ b/data/CS7/case33_3/case33_3_operational_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/CS7/case33_3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33205F2F-09C2-6A4B-9FF6-2DE23C0AABA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F4CF60-E9FE-F942-B36A-D63A9FC943AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1120" yWindow="620" windowWidth="29400" windowHeight="19120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -473,12 +473,12 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <f>E2*1.25</f>
-        <v>5</v>
+        <f>E2*1.5</f>
+        <v>6</v>
       </c>
       <c r="C2" s="1">
-        <f>F2*1</f>
-        <v>2.4</v>
+        <f>F2*1.5</f>
+        <v>3.5999999999999996</v>
       </c>
       <c r="D2" s="2">
         <v>2.6917900403768499E-2</v>
@@ -495,12 +495,12 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <f t="shared" ref="B3:B33" si="0">E3*1.25</f>
-        <v>4.5</v>
+        <f t="shared" ref="B3:B33" si="0">E3*1.5</f>
+        <v>5.3999999999999995</v>
       </c>
       <c r="C3" s="1">
-        <f t="shared" ref="C3:C17" si="1">F3*1</f>
-        <v>1.6</v>
+        <f t="shared" ref="C3:C17" si="1">F3*1.5</f>
+        <v>2.4000000000000004</v>
       </c>
       <c r="D3" s="2">
         <v>2.4226110363391645E-2</v>
@@ -518,11 +518,11 @@
       </c>
       <c r="B4" s="1">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" si="1"/>
-        <v>3.2</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="D4" s="2">
         <v>3.2301480484522194E-2</v>
@@ -540,11 +540,11 @@
       </c>
       <c r="B5" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C5" s="1">
         <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="D5" s="2">
         <v>1.6150740242261097E-2</v>
@@ -562,11 +562,11 @@
       </c>
       <c r="B6" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="D6" s="2">
         <v>1.6150740242261097E-2</v>
@@ -584,11 +584,11 @@
       </c>
       <c r="B7" s="1">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D7" s="2">
         <v>5.3835800807536999E-2</v>
@@ -606,11 +606,11 @@
       </c>
       <c r="B8" s="1">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D8" s="2">
         <v>5.3835800807536999E-2</v>
@@ -628,11 +628,11 @@
       </c>
       <c r="B9" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="D9" s="2">
         <v>1.6150740242261097E-2</v>
@@ -650,11 +650,11 @@
       </c>
       <c r="B10" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C10" s="1">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="D10" s="2">
         <v>1.6150740242261097E-2</v>
@@ -672,11 +672,11 @@
       </c>
       <c r="B11" s="1">
         <f t="shared" si="0"/>
-        <v>2.25</v>
+        <v>2.6999999999999997</v>
       </c>
       <c r="C11" s="1">
         <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="D11" s="2">
         <v>1.2113055181695823E-2</v>
@@ -694,11 +694,11 @@
       </c>
       <c r="B12" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C12" s="1">
         <f t="shared" si="1"/>
-        <v>1.4000000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="D12" s="2">
         <v>1.6150740242261097E-2</v>
@@ -716,11 +716,11 @@
       </c>
       <c r="B13" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C13" s="1">
         <f t="shared" si="1"/>
-        <v>1.4000000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="D13" s="2">
         <v>1.6150740242261097E-2</v>
@@ -738,11 +738,11 @@
       </c>
       <c r="B14" s="1">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" si="1"/>
-        <v>3.2</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="D14" s="2">
         <v>3.2301480484522194E-2</v>
@@ -760,11 +760,11 @@
       </c>
       <c r="B15" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" si="1"/>
-        <v>0.4</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="D15" s="2">
         <v>1.6150740242261097E-2</v>
@@ -782,11 +782,11 @@
       </c>
       <c r="B16" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C16" s="1">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="D16" s="2">
         <v>1.6150740242261097E-2</v>
@@ -804,11 +804,11 @@
       </c>
       <c r="B17" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="D17" s="2">
         <v>1.6150740242261097E-2</v>
@@ -826,11 +826,11 @@
       </c>
       <c r="B18" s="1">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>5.3999999999999995</v>
       </c>
       <c r="C18" s="1">
-        <f>F18*0.5</f>
-        <v>0.8</v>
+        <f>F18*0.75</f>
+        <v>1.2000000000000002</v>
       </c>
       <c r="D18" s="2">
         <v>2.4226110363391645E-2</v>
@@ -848,11 +848,11 @@
       </c>
       <c r="B19" s="1">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>5.3999999999999995</v>
       </c>
       <c r="C19" s="1">
-        <f t="shared" ref="C19:C33" si="2">F19*0.5</f>
-        <v>0.8</v>
+        <f t="shared" ref="C19:C33" si="2">F19*0.75</f>
+        <v>1.2000000000000002</v>
       </c>
       <c r="D19" s="2">
         <v>2.4226110363391645E-2</v>
@@ -870,11 +870,11 @@
       </c>
       <c r="B20" s="1">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>5.3999999999999995</v>
       </c>
       <c r="C20" s="1">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="D20" s="2">
         <v>2.4226110363391645E-2</v>
@@ -892,11 +892,11 @@
       </c>
       <c r="B21" s="1">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>5.3999999999999995</v>
       </c>
       <c r="C21" s="1">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="D21" s="2">
         <v>2.4226110363391645E-2</v>
@@ -914,11 +914,11 @@
       </c>
       <c r="B22" s="1">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>5.3999999999999995</v>
       </c>
       <c r="C22" s="1">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="D22" s="2">
         <v>2.4226110363391645E-2</v>
@@ -936,11 +936,11 @@
       </c>
       <c r="B23" s="1">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>5.3999999999999995</v>
       </c>
       <c r="C23" s="1">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D23" s="2">
         <v>2.4226110363391645E-2</v>
@@ -958,11 +958,11 @@
       </c>
       <c r="B24" s="1">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>25.200000000000003</v>
       </c>
       <c r="C24" s="1">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D24" s="2">
         <v>0.11305518169582769</v>
@@ -980,11 +980,11 @@
       </c>
       <c r="B25" s="1">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>25.200000000000003</v>
       </c>
       <c r="C25" s="1">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D25" s="2">
         <v>0.11305518169582769</v>
@@ -1002,11 +1002,11 @@
       </c>
       <c r="B26" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C26" s="1">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="D26" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1024,11 +1024,11 @@
       </c>
       <c r="B27" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C27" s="1">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="D27" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1046,11 +1046,11 @@
       </c>
       <c r="B28" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C28" s="1">
         <f t="shared" si="2"/>
-        <v>0.4</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="D28" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1068,11 +1068,11 @@
       </c>
       <c r="B29" s="1">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="C29" s="1">
         <f t="shared" si="2"/>
-        <v>1.4000000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="D29" s="2">
         <v>3.2301480484522194E-2</v>
@@ -1090,11 +1090,11 @@
       </c>
       <c r="B30" s="1">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C30" s="1">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D30" s="2">
         <v>5.3835800807536999E-2</v>
@@ -1112,11 +1112,11 @@
       </c>
       <c r="B31" s="1">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="C31" s="1">
         <f t="shared" si="2"/>
-        <v>1.4000000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="D31" s="2">
         <v>4.0376850605652742E-2</v>
@@ -1134,11 +1134,11 @@
       </c>
       <c r="B32" s="1">
         <f t="shared" si="0"/>
-        <v>10.5</v>
+        <v>12.600000000000001</v>
       </c>
       <c r="C32" s="1">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D32" s="2">
         <v>5.6527590847913846E-2</v>
@@ -1156,11 +1156,11 @@
       </c>
       <c r="B33" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C33" s="1">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="D33" s="2">
         <v>1.6150740242261097E-2</v>
